--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118557661</v>
+        <v>118556365</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589635</v>
+        <v>589354</v>
       </c>
       <c r="R6" t="n">
-        <v>7032058</v>
+        <v>7031906</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118556365</v>
+        <v>118557154</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589354</v>
+        <v>589647</v>
       </c>
       <c r="R7" t="n">
-        <v>7031906</v>
+        <v>7031952</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118557154</v>
+        <v>118557661</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589647</v>
+        <v>589635</v>
       </c>
       <c r="R8" t="n">
-        <v>7031952</v>
+        <v>7032058</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118553096</v>
+        <v>118555409</v>
       </c>
       <c r="B10" t="n">
-        <v>82263</v>
+        <v>90847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589204</v>
+        <v>589487</v>
       </c>
       <c r="R10" t="n">
-        <v>7031942</v>
+        <v>7031784</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118552378</v>
+        <v>118553096</v>
       </c>
       <c r="B11" t="n">
-        <v>90788</v>
+        <v>82263</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589267</v>
+        <v>589204</v>
       </c>
       <c r="R11" t="n">
-        <v>7031984</v>
+        <v>7031942</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118554028</v>
+        <v>118552378</v>
       </c>
       <c r="B12" t="n">
-        <v>90469</v>
+        <v>90788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,25 +1756,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589341</v>
+        <v>589267</v>
       </c>
       <c r="R12" t="n">
-        <v>7031857</v>
+        <v>7031984</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118551947</v>
+        <v>118554028</v>
       </c>
       <c r="B13" t="n">
         <v>90469</v>
@@ -1882,14 +1882,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589423</v>
+        <v>589341</v>
       </c>
       <c r="R13" t="n">
-        <v>7032113</v>
+        <v>7031857</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118557914</v>
+        <v>118551947</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589694</v>
+        <v>589423</v>
       </c>
       <c r="R14" t="n">
-        <v>7032099</v>
+        <v>7032113</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118555409</v>
+        <v>118557454</v>
       </c>
       <c r="B15" t="n">
-        <v>90847</v>
+        <v>78484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,38 +2062,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589487</v>
+        <v>589632</v>
       </c>
       <c r="R15" t="n">
-        <v>7031784</v>
+        <v>7032019</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118557454</v>
+        <v>118557914</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589632</v>
+        <v>589694</v>
       </c>
       <c r="R16" t="n">
-        <v>7032019</v>
+        <v>7032099</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118555355</v>
+        <v>118556301</v>
       </c>
       <c r="B31" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589463</v>
+        <v>589298</v>
       </c>
       <c r="R31" t="n">
-        <v>7031785</v>
+        <v>7031829</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118552663</v>
+        <v>118555355</v>
       </c>
       <c r="B32" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,25 +3819,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589275</v>
+        <v>589463</v>
       </c>
       <c r="R32" t="n">
-        <v>7031984</v>
+        <v>7031785</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118556301</v>
+        <v>118552663</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3921,25 +3921,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589298</v>
+        <v>589275</v>
       </c>
       <c r="R33" t="n">
-        <v>7031829</v>
+        <v>7031984</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118553061</v>
+        <v>118552498</v>
       </c>
       <c r="B42" t="n">
-        <v>86820</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4847,38 +4847,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589254</v>
+        <v>589280</v>
       </c>
       <c r="R42" t="n">
-        <v>7031953</v>
+        <v>7031976</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4937,10 +4946,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118552498</v>
+        <v>118553061</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>86820</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4949,47 +4958,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589280</v>
+        <v>589254</v>
       </c>
       <c r="R43" t="n">
-        <v>7031976</v>
+        <v>7031953</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -7612,10 +7612,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118555030</v>
+        <v>118552764</v>
       </c>
       <c r="B69" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7624,38 +7624,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589414</v>
+        <v>589297</v>
       </c>
       <c r="R69" t="n">
-        <v>7031799</v>
+        <v>7031952</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7714,10 +7718,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118554689</v>
+        <v>118552820</v>
       </c>
       <c r="B70" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,38 +7730,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589412</v>
+        <v>589311</v>
       </c>
       <c r="R70" t="n">
-        <v>7031811</v>
+        <v>7031954</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7816,10 +7829,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118552764</v>
+        <v>118555030</v>
       </c>
       <c r="B71" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7828,42 +7841,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589297</v>
+        <v>589414</v>
       </c>
       <c r="R71" t="n">
-        <v>7031952</v>
+        <v>7031799</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7922,10 +7931,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118552820</v>
+        <v>118554689</v>
       </c>
       <c r="B72" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7934,47 +7943,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589311</v>
+        <v>589412</v>
       </c>
       <c r="R72" t="n">
-        <v>7031954</v>
+        <v>7031811</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -10291,10 +10291,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118587901</v>
+        <v>118589918</v>
       </c>
       <c r="B95" t="n">
-        <v>90504</v>
+        <v>79469</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10303,25 +10303,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10331,10 +10331,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589438</v>
+        <v>589675</v>
       </c>
       <c r="R95" t="n">
-        <v>7032058</v>
+        <v>7031964</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10393,10 +10393,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118589918</v>
+        <v>118587901</v>
       </c>
       <c r="B96" t="n">
-        <v>79469</v>
+        <v>90504</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10405,25 +10405,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589675</v>
+        <v>589438</v>
       </c>
       <c r="R96" t="n">
-        <v>7031964</v>
+        <v>7032058</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10495,10 +10495,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118586696</v>
+        <v>118594520</v>
       </c>
       <c r="B97" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10507,38 +10507,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589736</v>
+        <v>589534</v>
       </c>
       <c r="R97" t="n">
-        <v>7032064</v>
+        <v>7031764</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10597,10 +10606,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118594520</v>
+        <v>118586696</v>
       </c>
       <c r="B98" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10609,47 +10618,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589534</v>
+        <v>589736</v>
       </c>
       <c r="R98" t="n">
-        <v>7031764</v>
+        <v>7032064</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118588420</v>
+        <v>118596677</v>
       </c>
       <c r="B103" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11133,38 +11133,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589421</v>
+        <v>589425</v>
       </c>
       <c r="R103" t="n">
-        <v>7032124</v>
+        <v>7031806</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11223,10 +11227,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118596677</v>
+        <v>118588420</v>
       </c>
       <c r="B104" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11235,42 +11239,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589425</v>
+        <v>589421</v>
       </c>
       <c r="R104" t="n">
-        <v>7031806</v>
+        <v>7032124</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -13184,10 +13184,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118597176</v>
+        <v>118587754</v>
       </c>
       <c r="B123" t="n">
-        <v>97763</v>
+        <v>90518</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13196,38 +13196,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219790</v>
+        <v>1204</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589501</v>
+        <v>589443</v>
       </c>
       <c r="R123" t="n">
-        <v>7031949</v>
+        <v>7032086</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13286,10 +13286,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118597023</v>
+        <v>118594452</v>
       </c>
       <c r="B124" t="n">
-        <v>57443</v>
+        <v>90469</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13298,42 +13298,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589517</v>
+        <v>589534</v>
       </c>
       <c r="R124" t="n">
-        <v>7031811</v>
+        <v>7031791</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13392,10 +13388,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118589613</v>
+        <v>118597176</v>
       </c>
       <c r="B125" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13404,42 +13400,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589740</v>
+        <v>589501</v>
       </c>
       <c r="R125" t="n">
-        <v>7032026</v>
+        <v>7031949</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13498,10 +13490,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118587754</v>
+        <v>118589613</v>
       </c>
       <c r="B126" t="n">
-        <v>90518</v>
+        <v>97846</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13510,38 +13502,42 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589443</v>
+        <v>589740</v>
       </c>
       <c r="R126" t="n">
-        <v>7032086</v>
+        <v>7032026</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13600,10 +13596,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118594452</v>
+        <v>118597023</v>
       </c>
       <c r="B127" t="n">
-        <v>90469</v>
+        <v>57443</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13612,38 +13608,42 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>589534</v>
+        <v>589517</v>
       </c>
       <c r="R127" t="n">
-        <v>7031791</v>
+        <v>7031811</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118555409</v>
+        <v>118553096</v>
       </c>
       <c r="B10" t="n">
-        <v>90847</v>
+        <v>82263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589487</v>
+        <v>589204</v>
       </c>
       <c r="R10" t="n">
-        <v>7031784</v>
+        <v>7031942</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118553096</v>
+        <v>118552378</v>
       </c>
       <c r="B11" t="n">
-        <v>82263</v>
+        <v>90788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589204</v>
+        <v>589267</v>
       </c>
       <c r="R11" t="n">
-        <v>7031942</v>
+        <v>7031984</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118552378</v>
+        <v>118554028</v>
       </c>
       <c r="B12" t="n">
-        <v>90788</v>
+        <v>90469</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,25 +1756,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589267</v>
+        <v>589341</v>
       </c>
       <c r="R12" t="n">
-        <v>7031984</v>
+        <v>7031857</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118554028</v>
+        <v>118551947</v>
       </c>
       <c r="B13" t="n">
         <v>90469</v>
@@ -1882,14 +1882,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589341</v>
+        <v>589423</v>
       </c>
       <c r="R13" t="n">
-        <v>7031857</v>
+        <v>7032113</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118551947</v>
+        <v>118557914</v>
       </c>
       <c r="B14" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589423</v>
+        <v>589694</v>
       </c>
       <c r="R14" t="n">
-        <v>7032113</v>
+        <v>7032099</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118557454</v>
+        <v>118555409</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>90847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,38 +2062,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589632</v>
+        <v>589487</v>
       </c>
       <c r="R15" t="n">
-        <v>7032019</v>
+        <v>7031784</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118557914</v>
+        <v>118557454</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589694</v>
+        <v>589632</v>
       </c>
       <c r="R16" t="n">
-        <v>7032099</v>
+        <v>7032019</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118555659</v>
+        <v>118552007</v>
       </c>
       <c r="B26" t="n">
-        <v>57306</v>
+        <v>90504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,39 +3206,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589466</v>
+        <v>589378</v>
       </c>
       <c r="R26" t="n">
-        <v>7031640</v>
+        <v>7032143</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3297,10 +3292,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118552007</v>
+        <v>118555659</v>
       </c>
       <c r="B27" t="n">
-        <v>90504</v>
+        <v>57306</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,34 +3308,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589378</v>
+        <v>589466</v>
       </c>
       <c r="R27" t="n">
-        <v>7032143</v>
+        <v>7031640</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -6480,10 +6480,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118558184</v>
+        <v>118555302</v>
       </c>
       <c r="B58" t="n">
-        <v>97763</v>
+        <v>90788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589713</v>
+        <v>589472</v>
       </c>
       <c r="R58" t="n">
-        <v>7032063</v>
+        <v>7031796</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6582,10 +6582,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118555302</v>
+        <v>118554548</v>
       </c>
       <c r="B59" t="n">
-        <v>90788</v>
+        <v>90469</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6594,25 +6594,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589472</v>
+        <v>589348</v>
       </c>
       <c r="R59" t="n">
-        <v>7031796</v>
+        <v>7031858</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118554548</v>
+        <v>118552101</v>
       </c>
       <c r="B60" t="n">
         <v>90469</v>
@@ -6720,14 +6720,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589348</v>
+        <v>589319</v>
       </c>
       <c r="R60" t="n">
-        <v>7031858</v>
+        <v>7032043</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118552101</v>
+        <v>118554878</v>
       </c>
       <c r="B61" t="n">
-        <v>90469</v>
+        <v>79525</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6802,34 +6802,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589319</v>
+        <v>589437</v>
       </c>
       <c r="R61" t="n">
-        <v>7032043</v>
+        <v>7031771</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6995,10 +6995,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118554878</v>
+        <v>118558184</v>
       </c>
       <c r="B63" t="n">
-        <v>79525</v>
+        <v>97763</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589437</v>
+        <v>589713</v>
       </c>
       <c r="R63" t="n">
-        <v>7031771</v>
+        <v>7032063</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -10495,10 +10495,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118594520</v>
+        <v>118586696</v>
       </c>
       <c r="B97" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10507,47 +10507,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589534</v>
+        <v>589736</v>
       </c>
       <c r="R97" t="n">
-        <v>7031764</v>
+        <v>7032064</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10606,10 +10597,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118586696</v>
+        <v>118594520</v>
       </c>
       <c r="B98" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10618,38 +10609,47 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589736</v>
+        <v>589534</v>
       </c>
       <c r="R98" t="n">
-        <v>7032064</v>
+        <v>7031764</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10912,10 +10912,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118590215</v>
+        <v>118596031</v>
       </c>
       <c r="B101" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10928,39 +10928,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589598</v>
+        <v>589279</v>
       </c>
       <c r="R101" t="n">
-        <v>7031977</v>
+        <v>7031737</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11019,10 +11014,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118596031</v>
+        <v>118590215</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11035,34 +11030,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589279</v>
+        <v>589598</v>
       </c>
       <c r="R102" t="n">
-        <v>7031737</v>
+        <v>7031977</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -12563,10 +12563,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118587264</v>
+        <v>118587499</v>
       </c>
       <c r="B117" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12579,21 +12579,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589634</v>
+        <v>589524</v>
       </c>
       <c r="R117" t="n">
-        <v>7032061</v>
+        <v>7032087</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12665,10 +12665,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118587499</v>
+        <v>118587264</v>
       </c>
       <c r="B118" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12681,21 +12681,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12705,10 +12705,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589524</v>
+        <v>589634</v>
       </c>
       <c r="R118" t="n">
-        <v>7032087</v>
+        <v>7032061</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -13184,10 +13184,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118587754</v>
+        <v>118597176</v>
       </c>
       <c r="B123" t="n">
-        <v>90518</v>
+        <v>97763</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13196,38 +13196,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1204</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589443</v>
+        <v>589501</v>
       </c>
       <c r="R123" t="n">
-        <v>7032086</v>
+        <v>7031949</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13286,10 +13286,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118594452</v>
+        <v>118587754</v>
       </c>
       <c r="B124" t="n">
-        <v>90469</v>
+        <v>90518</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13298,38 +13298,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589534</v>
+        <v>589443</v>
       </c>
       <c r="R124" t="n">
-        <v>7031791</v>
+        <v>7032086</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13388,10 +13388,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118597176</v>
+        <v>118594452</v>
       </c>
       <c r="B125" t="n">
-        <v>97763</v>
+        <v>90469</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13404,21 +13404,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13428,10 +13428,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589501</v>
+        <v>589534</v>
       </c>
       <c r="R125" t="n">
-        <v>7031949</v>
+        <v>7031791</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118551972</v>
+        <v>118552853</v>
       </c>
       <c r="B4" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589404</v>
+        <v>589290</v>
       </c>
       <c r="R4" t="n">
-        <v>7032115</v>
+        <v>7031929</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118551872</v>
+        <v>118552350</v>
       </c>
       <c r="B5" t="n">
-        <v>90788</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589417</v>
+        <v>589284</v>
       </c>
       <c r="R5" t="n">
-        <v>7032126</v>
+        <v>7031972</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118556365</v>
+        <v>118551431</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589354</v>
+        <v>589557</v>
       </c>
       <c r="R6" t="n">
-        <v>7031906</v>
+        <v>7032281</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118557154</v>
+        <v>118551872</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>90788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589647</v>
+        <v>589417</v>
       </c>
       <c r="R7" t="n">
-        <v>7031952</v>
+        <v>7032126</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118557661</v>
+        <v>118554689</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,38 +1339,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589635</v>
+        <v>589412</v>
       </c>
       <c r="R8" t="n">
-        <v>7032058</v>
+        <v>7031811</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118552802</v>
+        <v>118551796</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,47 +1441,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589313</v>
+        <v>589417</v>
       </c>
       <c r="R9" t="n">
-        <v>7031955</v>
+        <v>7032141</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1540,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118553096</v>
+        <v>118552748</v>
       </c>
       <c r="B10" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,38 +1543,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589204</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>7031942</v>
+        <v>7031953</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1642,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118552378</v>
+        <v>118552820</v>
       </c>
       <c r="B11" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,38 +1649,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589267</v>
+        <v>589311</v>
       </c>
       <c r="R11" t="n">
-        <v>7031984</v>
+        <v>7031954</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1744,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118554028</v>
+        <v>118556301</v>
       </c>
       <c r="B12" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589341</v>
+        <v>589298</v>
       </c>
       <c r="R12" t="n">
-        <v>7031857</v>
+        <v>7031829</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1846,7 +1850,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118551947</v>
+        <v>118552051</v>
       </c>
       <c r="B13" t="n">
         <v>90469</v>
@@ -1886,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589423</v>
+        <v>589348</v>
       </c>
       <c r="R13" t="n">
-        <v>7032113</v>
+        <v>7032078</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1948,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118557914</v>
+        <v>118556472</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>79469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,38 +1964,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589694</v>
+        <v>589408</v>
       </c>
       <c r="R14" t="n">
-        <v>7032099</v>
+        <v>7031876</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2050,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118555409</v>
+        <v>118555622</v>
       </c>
       <c r="B15" t="n">
-        <v>90847</v>
+        <v>78484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589487</v>
+        <v>589490</v>
       </c>
       <c r="R15" t="n">
-        <v>7031784</v>
+        <v>7031668</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2152,7 +2156,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118557454</v>
+        <v>118556986</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2188,14 +2192,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589632</v>
+        <v>589680</v>
       </c>
       <c r="R16" t="n">
-        <v>7032019</v>
+        <v>7031886</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2254,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118554184</v>
+        <v>118557914</v>
       </c>
       <c r="B17" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2270,34 +2274,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589360</v>
+        <v>589694</v>
       </c>
       <c r="R17" t="n">
-        <v>7031856</v>
+        <v>7032099</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2356,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118556574</v>
+        <v>118553615</v>
       </c>
       <c r="B18" t="n">
-        <v>90788</v>
+        <v>79469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,25 +2372,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2396,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589407</v>
+        <v>589180</v>
       </c>
       <c r="R18" t="n">
-        <v>7031827</v>
+        <v>7031880</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2458,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118552694</v>
+        <v>118556821</v>
       </c>
       <c r="B19" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2498,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589282</v>
+        <v>589651</v>
       </c>
       <c r="R19" t="n">
-        <v>7031935</v>
+        <v>7031856</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2560,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118554168</v>
+        <v>118552007</v>
       </c>
       <c r="B20" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,38 +2576,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589359</v>
+        <v>589378</v>
       </c>
       <c r="R20" t="n">
-        <v>7031857</v>
+        <v>7032143</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2764,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118552200</v>
+        <v>118557229</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,47 +2780,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589314</v>
+        <v>589650</v>
       </c>
       <c r="R22" t="n">
-        <v>7032037</v>
+        <v>7031972</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2875,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118557265</v>
+        <v>118554184</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,47 +2882,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589642</v>
+        <v>589360</v>
       </c>
       <c r="R23" t="n">
-        <v>7031970</v>
+        <v>7031856</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2986,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118554223</v>
+        <v>118551992</v>
       </c>
       <c r="B24" t="n">
-        <v>90666</v>
+        <v>90469</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2998,38 +2984,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589368</v>
+        <v>589373</v>
       </c>
       <c r="R24" t="n">
-        <v>7031862</v>
+        <v>7032142</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3088,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118552219</v>
+        <v>118552992</v>
       </c>
       <c r="B25" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3100,25 +3086,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3128,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589268</v>
+        <v>589298</v>
       </c>
       <c r="R25" t="n">
-        <v>7031998</v>
+        <v>7031917</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3190,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118552007</v>
+        <v>118556574</v>
       </c>
       <c r="B26" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,34 +3192,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589378</v>
+        <v>589407</v>
       </c>
       <c r="R26" t="n">
-        <v>7032143</v>
+        <v>7031827</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3292,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118555659</v>
+        <v>118552101</v>
       </c>
       <c r="B27" t="n">
-        <v>57306</v>
+        <v>90469</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3304,43 +3290,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589466</v>
+        <v>589319</v>
       </c>
       <c r="R27" t="n">
-        <v>7031640</v>
+        <v>7032043</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3399,10 +3380,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118556472</v>
+        <v>118553096</v>
       </c>
       <c r="B28" t="n">
-        <v>79469</v>
+        <v>82263</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,25 +3392,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3420,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589408</v>
+        <v>589204</v>
       </c>
       <c r="R28" t="n">
-        <v>7031876</v>
+        <v>7031942</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3501,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118553087</v>
+        <v>118552657</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,38 +3494,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589202</v>
+        <v>589282</v>
       </c>
       <c r="R29" t="n">
-        <v>7031945</v>
+        <v>7031970</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3603,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118556986</v>
+        <v>118552163</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,38 +3600,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589680</v>
+        <v>589309</v>
       </c>
       <c r="R30" t="n">
-        <v>7031886</v>
+        <v>7032040</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3705,10 +3690,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118556301</v>
+        <v>118551972</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,34 +3706,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589298</v>
+        <v>589404</v>
       </c>
       <c r="R31" t="n">
-        <v>7031829</v>
+        <v>7032115</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3807,10 +3792,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118555355</v>
+        <v>118552378</v>
       </c>
       <c r="B32" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3823,21 +3808,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3847,10 +3832,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589463</v>
+        <v>589267</v>
       </c>
       <c r="R32" t="n">
-        <v>7031785</v>
+        <v>7031984</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3909,10 +3894,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118552663</v>
+        <v>118553087</v>
       </c>
       <c r="B33" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3921,25 +3906,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,10 +3934,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589275</v>
+        <v>589202</v>
       </c>
       <c r="R33" t="n">
-        <v>7031984</v>
+        <v>7031945</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4011,10 +3996,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118557174</v>
+        <v>118551771</v>
       </c>
       <c r="B34" t="n">
-        <v>79469</v>
+        <v>90469</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4027,21 +4012,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4036,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589654</v>
+        <v>589423</v>
       </c>
       <c r="R34" t="n">
-        <v>7031957</v>
+        <v>7032117</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4113,10 +4098,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118552657</v>
+        <v>118554252</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,42 +4110,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589282</v>
+        <v>589368</v>
       </c>
       <c r="R35" t="n">
-        <v>7031970</v>
+        <v>7031862</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4219,7 +4200,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118551771</v>
+        <v>118557448</v>
       </c>
       <c r="B36" t="n">
         <v>90469</v>
@@ -4259,10 +4240,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589423</v>
+        <v>589632</v>
       </c>
       <c r="R36" t="n">
-        <v>7032117</v>
+        <v>7032018</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4321,10 +4302,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118552992</v>
+        <v>118553989</v>
       </c>
       <c r="B37" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4337,34 +4318,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589298</v>
+        <v>589352</v>
       </c>
       <c r="R37" t="n">
-        <v>7031917</v>
+        <v>7031849</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4423,10 +4409,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118553615</v>
+        <v>118557154</v>
       </c>
       <c r="B38" t="n">
-        <v>79469</v>
+        <v>79565</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4435,38 +4421,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589180</v>
+        <v>589647</v>
       </c>
       <c r="R38" t="n">
-        <v>7031880</v>
+        <v>7031952</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4525,10 +4511,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118557229</v>
+        <v>118554822</v>
       </c>
       <c r="B39" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4537,38 +4523,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589650</v>
+        <v>589399</v>
       </c>
       <c r="R39" t="n">
-        <v>7031972</v>
+        <v>7031814</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4627,10 +4613,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118557253</v>
+        <v>118551947</v>
       </c>
       <c r="B40" t="n">
-        <v>58133</v>
+        <v>90469</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4643,21 +4629,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208249</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4667,10 +4653,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589648</v>
+        <v>589423</v>
       </c>
       <c r="R40" t="n">
-        <v>7031970</v>
+        <v>7032113</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4729,7 +4715,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118552748</v>
+        <v>118552985</v>
       </c>
       <c r="B41" t="n">
         <v>97846</v>
@@ -4764,7 +4750,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4773,10 +4759,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589291</v>
+        <v>589293</v>
       </c>
       <c r="R41" t="n">
-        <v>7031953</v>
+        <v>7031918</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4835,10 +4821,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118552498</v>
+        <v>118555445</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4847,47 +4833,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589280</v>
+        <v>589487</v>
       </c>
       <c r="R42" t="n">
-        <v>7031976</v>
+        <v>7031784</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4946,10 +4923,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118553061</v>
+        <v>118557940</v>
       </c>
       <c r="B43" t="n">
-        <v>86820</v>
+        <v>79565</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4962,34 +4939,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589254</v>
+        <v>589730</v>
       </c>
       <c r="R43" t="n">
-        <v>7031953</v>
+        <v>7032086</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5048,10 +5025,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118557448</v>
+        <v>118552764</v>
       </c>
       <c r="B44" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5060,38 +5037,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589632</v>
+        <v>589297</v>
       </c>
       <c r="R44" t="n">
-        <v>7032018</v>
+        <v>7031952</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5150,10 +5131,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118557202</v>
+        <v>118554028</v>
       </c>
       <c r="B45" t="n">
-        <v>79565</v>
+        <v>90469</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5162,38 +5143,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589643</v>
+        <v>589341</v>
       </c>
       <c r="R45" t="n">
-        <v>7031980</v>
+        <v>7031857</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5252,10 +5233,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118554450</v>
+        <v>118557661</v>
       </c>
       <c r="B46" t="n">
-        <v>90788</v>
+        <v>78484</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5268,34 +5249,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589392</v>
+        <v>589635</v>
       </c>
       <c r="R46" t="n">
-        <v>7031860</v>
+        <v>7032058</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5354,10 +5335,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118552111</v>
+        <v>118551885</v>
       </c>
       <c r="B47" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5370,21 +5351,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5394,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589317</v>
+        <v>589410</v>
       </c>
       <c r="R47" t="n">
-        <v>7032040</v>
+        <v>7032119</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5456,7 +5437,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118554797</v>
+        <v>118556365</v>
       </c>
       <c r="B48" t="n">
         <v>90504</v>
@@ -5496,10 +5477,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589358</v>
+        <v>589354</v>
       </c>
       <c r="R48" t="n">
-        <v>7031830</v>
+        <v>7031906</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5558,10 +5539,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118552278</v>
+        <v>118555302</v>
       </c>
       <c r="B49" t="n">
-        <v>90522</v>
+        <v>90788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5574,21 +5555,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5598,10 +5579,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589280</v>
+        <v>589472</v>
       </c>
       <c r="R49" t="n">
-        <v>7031985</v>
+        <v>7031796</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5660,10 +5641,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118551880</v>
+        <v>118557253</v>
       </c>
       <c r="B50" t="n">
-        <v>90469</v>
+        <v>58133</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5676,21 +5657,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>208249</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5700,10 +5681,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589417</v>
+        <v>589648</v>
       </c>
       <c r="R50" t="n">
-        <v>7032126</v>
+        <v>7031970</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5762,7 +5743,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118552985</v>
+        <v>118552498</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -5797,7 +5778,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5806,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589293</v>
+        <v>589280</v>
       </c>
       <c r="R51" t="n">
-        <v>7031918</v>
+        <v>7031976</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5868,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118555445</v>
+        <v>118555030</v>
       </c>
       <c r="B52" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5880,25 +5866,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5908,10 +5894,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589487</v>
+        <v>589414</v>
       </c>
       <c r="R52" t="n">
-        <v>7031784</v>
+        <v>7031799</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5970,10 +5956,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118552051</v>
+        <v>118551676</v>
       </c>
       <c r="B53" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5982,25 +5968,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6010,10 +5996,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589348</v>
+        <v>589418</v>
       </c>
       <c r="R53" t="n">
-        <v>7032078</v>
+        <v>7032144</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6072,10 +6058,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118552163</v>
+        <v>118552111</v>
       </c>
       <c r="B54" t="n">
-        <v>79594</v>
+        <v>90504</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6084,25 +6070,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,7 +6098,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589309</v>
+        <v>589317</v>
       </c>
       <c r="R54" t="n">
         <v>7032040</v>
@@ -6174,10 +6160,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118554978</v>
+        <v>118554910</v>
       </c>
       <c r="B55" t="n">
-        <v>90947</v>
+        <v>90788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6186,25 +6172,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6214,10 +6200,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589414</v>
+        <v>589428</v>
       </c>
       <c r="R55" t="n">
-        <v>7031799</v>
+        <v>7031801</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6276,7 +6262,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118555622</v>
+        <v>118557454</v>
       </c>
       <c r="B56" t="n">
         <v>78484</v>
@@ -6312,14 +6298,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589490</v>
+        <v>589632</v>
       </c>
       <c r="R56" t="n">
-        <v>7031668</v>
+        <v>7032019</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6378,10 +6364,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118556821</v>
+        <v>118551880</v>
       </c>
       <c r="B57" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6390,38 +6376,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589651</v>
+        <v>589417</v>
       </c>
       <c r="R57" t="n">
-        <v>7031856</v>
+        <v>7032126</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6480,10 +6466,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118555302</v>
+        <v>118554548</v>
       </c>
       <c r="B58" t="n">
-        <v>90788</v>
+        <v>90469</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6492,25 +6478,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6520,10 +6506,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589472</v>
+        <v>589348</v>
       </c>
       <c r="R58" t="n">
-        <v>7031796</v>
+        <v>7031858</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6582,10 +6568,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118554548</v>
+        <v>118557202</v>
       </c>
       <c r="B59" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6594,38 +6580,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589348</v>
+        <v>589643</v>
       </c>
       <c r="R59" t="n">
-        <v>7031858</v>
+        <v>7031980</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6684,7 +6670,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118552101</v>
+        <v>118552219</v>
       </c>
       <c r="B60" t="n">
         <v>90469</v>
@@ -6720,14 +6706,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589319</v>
+        <v>589268</v>
       </c>
       <c r="R60" t="n">
-        <v>7032043</v>
+        <v>7031998</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6786,10 +6772,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118554878</v>
+        <v>118555409</v>
       </c>
       <c r="B61" t="n">
-        <v>79525</v>
+        <v>90847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6798,25 +6784,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>2062</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6826,10 +6812,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589437</v>
+        <v>589487</v>
       </c>
       <c r="R61" t="n">
-        <v>7031771</v>
+        <v>7031784</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6888,10 +6874,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118555906</v>
+        <v>118552802</v>
       </c>
       <c r="B62" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6900,31 +6886,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6933,10 +6923,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589312</v>
+        <v>589313</v>
       </c>
       <c r="R62" t="n">
-        <v>7031697</v>
+        <v>7031955</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6995,10 +6985,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118558184</v>
+        <v>118557265</v>
       </c>
       <c r="B63" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7007,38 +6997,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589713</v>
+        <v>589642</v>
       </c>
       <c r="R63" t="n">
-        <v>7032063</v>
+        <v>7031970</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7097,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118551885</v>
+        <v>118554878</v>
       </c>
       <c r="B64" t="n">
-        <v>90788</v>
+        <v>79525</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7109,38 +7108,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589410</v>
+        <v>589437</v>
       </c>
       <c r="R64" t="n">
-        <v>7032119</v>
+        <v>7031771</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7199,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118554910</v>
+        <v>118554223</v>
       </c>
       <c r="B65" t="n">
-        <v>90788</v>
+        <v>90666</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7215,21 +7214,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1588</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7239,10 +7238,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589428</v>
+        <v>589368</v>
       </c>
       <c r="R65" t="n">
-        <v>7031801</v>
+        <v>7031862</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7301,7 +7300,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118551992</v>
+        <v>118552663</v>
       </c>
       <c r="B66" t="n">
         <v>90469</v>
@@ -7337,14 +7336,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589373</v>
+        <v>589275</v>
       </c>
       <c r="R66" t="n">
-        <v>7032142</v>
+        <v>7031984</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7403,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118554171</v>
+        <v>118555355</v>
       </c>
       <c r="B67" t="n">
-        <v>90522</v>
+        <v>90504</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7419,21 +7418,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7443,10 +7442,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589359</v>
+        <v>589463</v>
       </c>
       <c r="R67" t="n">
-        <v>7031858</v>
+        <v>7031785</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7505,10 +7504,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118553989</v>
+        <v>118552278</v>
       </c>
       <c r="B68" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7521,39 +7520,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589352</v>
+        <v>589280</v>
       </c>
       <c r="R68" t="n">
-        <v>7031849</v>
+        <v>7031985</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7612,10 +7606,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118552764</v>
+        <v>118553061</v>
       </c>
       <c r="B69" t="n">
-        <v>97846</v>
+        <v>86820</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7624,42 +7618,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589297</v>
+        <v>589254</v>
       </c>
       <c r="R69" t="n">
-        <v>7031952</v>
+        <v>7031953</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7718,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118552820</v>
+        <v>118555659</v>
       </c>
       <c r="B70" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7730,35 +7720,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7767,10 +7753,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589311</v>
+        <v>589466</v>
       </c>
       <c r="R70" t="n">
-        <v>7031954</v>
+        <v>7031640</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7829,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118555030</v>
+        <v>118554978</v>
       </c>
       <c r="B71" t="n">
-        <v>90504</v>
+        <v>90947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7841,25 +7827,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7931,10 +7917,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118554689</v>
+        <v>118558184</v>
       </c>
       <c r="B72" t="n">
-        <v>90469</v>
+        <v>97763</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7947,34 +7933,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589412</v>
+        <v>589713</v>
       </c>
       <c r="R72" t="n">
-        <v>7031811</v>
+        <v>7032063</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8033,10 +8019,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118552350</v>
+        <v>118552200</v>
       </c>
       <c r="B73" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8045,38 +8031,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589284</v>
+        <v>589314</v>
       </c>
       <c r="R73" t="n">
-        <v>7031972</v>
+        <v>7032037</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8135,7 +8130,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118551796</v>
+        <v>118555468</v>
       </c>
       <c r="B74" t="n">
         <v>90504</v>
@@ -8171,14 +8166,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589417</v>
+        <v>589488</v>
       </c>
       <c r="R74" t="n">
-        <v>7032141</v>
+        <v>7031771</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8237,7 +8232,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118555468</v>
+        <v>118552694</v>
       </c>
       <c r="B75" t="n">
         <v>90504</v>
@@ -8277,10 +8272,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589488</v>
+        <v>589282</v>
       </c>
       <c r="R75" t="n">
-        <v>7031771</v>
+        <v>7031935</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8339,10 +8334,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118552853</v>
+        <v>118557174</v>
       </c>
       <c r="B76" t="n">
-        <v>90469</v>
+        <v>79469</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8355,34 +8350,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589290</v>
+        <v>589654</v>
       </c>
       <c r="R76" t="n">
-        <v>7031929</v>
+        <v>7031957</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8441,10 +8436,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118551676</v>
+        <v>118554171</v>
       </c>
       <c r="B77" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8457,34 +8452,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589418</v>
+        <v>589359</v>
       </c>
       <c r="R77" t="n">
-        <v>7032144</v>
+        <v>7031858</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8543,10 +8538,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118554822</v>
+        <v>118555906</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8559,34 +8554,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589399</v>
+        <v>589312</v>
       </c>
       <c r="R78" t="n">
-        <v>7031814</v>
+        <v>7031697</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8645,10 +8645,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118551431</v>
+        <v>118554168</v>
       </c>
       <c r="B79" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8657,38 +8657,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589557</v>
+        <v>589359</v>
       </c>
       <c r="R79" t="n">
-        <v>7032281</v>
+        <v>7031857</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8747,10 +8747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118557940</v>
+        <v>118554450</v>
       </c>
       <c r="B80" t="n">
-        <v>79565</v>
+        <v>90788</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8763,34 +8763,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589730</v>
+        <v>589392</v>
       </c>
       <c r="R80" t="n">
-        <v>7032086</v>
+        <v>7031860</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118554252</v>
+        <v>118554797</v>
       </c>
       <c r="B81" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8865,21 +8865,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589368</v>
+        <v>589358</v>
       </c>
       <c r="R81" t="n">
-        <v>7031862</v>
+        <v>7031830</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8951,10 +8951,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118589537</v>
+        <v>118587872</v>
       </c>
       <c r="B82" t="n">
-        <v>86820</v>
+        <v>90469</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8963,25 +8963,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8991,10 +8991,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589709</v>
+        <v>589438</v>
       </c>
       <c r="R82" t="n">
-        <v>7031980</v>
+        <v>7032059</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118590971</v>
+        <v>118590255</v>
       </c>
       <c r="B83" t="n">
-        <v>82263</v>
+        <v>79565</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9069,34 +9069,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589691</v>
+        <v>589607</v>
       </c>
       <c r="R83" t="n">
-        <v>7031862</v>
+        <v>7032009</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9155,10 +9155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118591032</v>
+        <v>118587754</v>
       </c>
       <c r="B84" t="n">
-        <v>90522</v>
+        <v>90518</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9171,34 +9171,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589690</v>
+        <v>589443</v>
       </c>
       <c r="R84" t="n">
-        <v>7031882</v>
+        <v>7032086</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118596564</v>
+        <v>118594452</v>
       </c>
       <c r="B85" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9269,47 +9269,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589368</v>
+        <v>589534</v>
       </c>
       <c r="R85" t="n">
-        <v>7031833</v>
+        <v>7031791</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9368,10 +9359,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118587799</v>
+        <v>118587924</v>
       </c>
       <c r="B86" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9380,25 +9371,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9408,10 +9399,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589440</v>
+        <v>589445</v>
       </c>
       <c r="R86" t="n">
-        <v>7032089</v>
+        <v>7032073</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9470,10 +9461,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118597248</v>
+        <v>118588128</v>
       </c>
       <c r="B87" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9482,43 +9473,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589494</v>
+        <v>589428</v>
       </c>
       <c r="R87" t="n">
-        <v>7031972</v>
+        <v>7032108</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9577,7 +9563,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118588534</v>
+        <v>118589036</v>
       </c>
       <c r="B88" t="n">
         <v>90469</v>
@@ -9617,10 +9603,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589413</v>
+        <v>589506</v>
       </c>
       <c r="R88" t="n">
-        <v>7032084</v>
+        <v>7031977</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9679,10 +9665,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118587872</v>
+        <v>118589906</v>
       </c>
       <c r="B89" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9691,25 +9677,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9719,10 +9705,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589438</v>
+        <v>589676</v>
       </c>
       <c r="R89" t="n">
-        <v>7032059</v>
+        <v>7031963</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9781,10 +9767,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118590681</v>
+        <v>118588485</v>
       </c>
       <c r="B90" t="n">
-        <v>90469</v>
+        <v>90788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9793,38 +9779,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589668</v>
+        <v>589403</v>
       </c>
       <c r="R90" t="n">
-        <v>7031892</v>
+        <v>7032119</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9883,10 +9869,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118588485</v>
+        <v>118589093</v>
       </c>
       <c r="B91" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9899,34 +9885,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589403</v>
+        <v>589495</v>
       </c>
       <c r="R91" t="n">
-        <v>7032119</v>
+        <v>7031990</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9985,10 +9976,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118589486</v>
+        <v>118589918</v>
       </c>
       <c r="B92" t="n">
-        <v>78484</v>
+        <v>79469</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9997,25 +9988,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10025,10 +10016,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589657</v>
+        <v>589675</v>
       </c>
       <c r="R92" t="n">
-        <v>7031995</v>
+        <v>7031964</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10189,10 +10180,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118589338</v>
+        <v>118596822</v>
       </c>
       <c r="B94" t="n">
-        <v>79565</v>
+        <v>90788</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10205,34 +10196,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589593</v>
+        <v>589457</v>
       </c>
       <c r="R94" t="n">
-        <v>7032037</v>
+        <v>7031787</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10291,10 +10282,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118589918</v>
+        <v>118596461</v>
       </c>
       <c r="B95" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10303,38 +10294,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589675</v>
+        <v>589343</v>
       </c>
       <c r="R95" t="n">
-        <v>7031964</v>
+        <v>7031883</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10393,10 +10393,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118587901</v>
+        <v>118586696</v>
       </c>
       <c r="B96" t="n">
-        <v>90504</v>
+        <v>97763</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10405,25 +10405,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589438</v>
+        <v>589736</v>
       </c>
       <c r="R96" t="n">
-        <v>7032058</v>
+        <v>7032064</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10495,10 +10495,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118586696</v>
+        <v>118590971</v>
       </c>
       <c r="B97" t="n">
-        <v>97763</v>
+        <v>82263</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10507,38 +10507,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589736</v>
+        <v>589691</v>
       </c>
       <c r="R97" t="n">
-        <v>7032064</v>
+        <v>7031862</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10597,10 +10597,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118594520</v>
+        <v>118589537</v>
       </c>
       <c r="B98" t="n">
-        <v>97846</v>
+        <v>86820</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10609,47 +10609,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589534</v>
+        <v>589709</v>
       </c>
       <c r="R98" t="n">
-        <v>7031764</v>
+        <v>7031980</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10708,10 +10699,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118589400</v>
+        <v>118594407</v>
       </c>
       <c r="B99" t="n">
-        <v>90522</v>
+        <v>57306</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10724,34 +10715,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589614</v>
+        <v>589525</v>
       </c>
       <c r="R99" t="n">
-        <v>7032054</v>
+        <v>7031796</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10810,10 +10806,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118588128</v>
+        <v>118589486</v>
       </c>
       <c r="B100" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10822,25 +10818,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10850,10 +10846,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589428</v>
+        <v>589657</v>
       </c>
       <c r="R100" t="n">
-        <v>7032108</v>
+        <v>7031995</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10912,10 +10908,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118596031</v>
+        <v>118591032</v>
       </c>
       <c r="B101" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10928,21 +10924,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10952,10 +10948,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589279</v>
+        <v>589690</v>
       </c>
       <c r="R101" t="n">
-        <v>7031737</v>
+        <v>7031882</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11014,10 +11010,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118590215</v>
+        <v>118589613</v>
       </c>
       <c r="B102" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11026,31 +11022,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11059,10 +11054,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589598</v>
+        <v>589740</v>
       </c>
       <c r="R102" t="n">
-        <v>7031977</v>
+        <v>7032026</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11121,10 +11116,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118596677</v>
+        <v>118587901</v>
       </c>
       <c r="B103" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11133,42 +11128,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589425</v>
+        <v>589438</v>
       </c>
       <c r="R103" t="n">
-        <v>7031806</v>
+        <v>7032058</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11227,10 +11218,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118588420</v>
+        <v>118590215</v>
       </c>
       <c r="B104" t="n">
-        <v>90788</v>
+        <v>57306</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11243,34 +11234,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589421</v>
+        <v>589598</v>
       </c>
       <c r="R104" t="n">
-        <v>7032124</v>
+        <v>7031977</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11329,10 +11325,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118591019</v>
+        <v>118589400</v>
       </c>
       <c r="B105" t="n">
-        <v>86820</v>
+        <v>90522</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11345,34 +11341,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589686</v>
+        <v>589614</v>
       </c>
       <c r="R105" t="n">
-        <v>7031880</v>
+        <v>7032054</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11431,10 +11427,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118587924</v>
+        <v>118597176</v>
       </c>
       <c r="B106" t="n">
-        <v>90469</v>
+        <v>97763</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11447,34 +11443,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589445</v>
+        <v>589501</v>
       </c>
       <c r="R106" t="n">
-        <v>7032073</v>
+        <v>7031949</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11533,10 +11529,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118587967</v>
+        <v>118597248</v>
       </c>
       <c r="B107" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11545,38 +11541,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589432</v>
+        <v>589494</v>
       </c>
       <c r="R107" t="n">
-        <v>7032081</v>
+        <v>7031972</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11635,10 +11636,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118592076</v>
+        <v>118587667</v>
       </c>
       <c r="B108" t="n">
-        <v>56494</v>
+        <v>90469</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11647,43 +11648,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>589665</v>
+        <v>589455</v>
       </c>
       <c r="R108" t="n">
-        <v>7031798</v>
+        <v>7032096</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11844,10 +11840,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118594447</v>
+        <v>118596031</v>
       </c>
       <c r="B110" t="n">
-        <v>90847</v>
+        <v>78484</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11856,25 +11852,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11884,10 +11880,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589535</v>
+        <v>589279</v>
       </c>
       <c r="R110" t="n">
-        <v>7031791</v>
+        <v>7031737</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11946,10 +11942,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118594407</v>
+        <v>118588420</v>
       </c>
       <c r="B111" t="n">
-        <v>57306</v>
+        <v>90788</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11962,39 +11958,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589525</v>
+        <v>589421</v>
       </c>
       <c r="R111" t="n">
-        <v>7031796</v>
+        <v>7032124</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12053,10 +12044,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118586687</v>
+        <v>118588534</v>
       </c>
       <c r="B112" t="n">
-        <v>90522</v>
+        <v>90469</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12065,25 +12056,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12093,10 +12084,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>589736</v>
+        <v>589413</v>
       </c>
       <c r="R112" t="n">
-        <v>7032057</v>
+        <v>7032084</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12155,10 +12146,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118589036</v>
+        <v>118587799</v>
       </c>
       <c r="B113" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12167,25 +12158,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12195,10 +12186,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589506</v>
+        <v>589440</v>
       </c>
       <c r="R113" t="n">
-        <v>7031977</v>
+        <v>7032089</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12257,10 +12248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118590255</v>
+        <v>118590681</v>
       </c>
       <c r="B114" t="n">
-        <v>79565</v>
+        <v>90469</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12269,38 +12260,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589607</v>
+        <v>589668</v>
       </c>
       <c r="R114" t="n">
-        <v>7032009</v>
+        <v>7031892</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12359,10 +12350,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118596822</v>
+        <v>118590296</v>
       </c>
       <c r="B115" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12371,38 +12362,47 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589457</v>
+        <v>589588</v>
       </c>
       <c r="R115" t="n">
-        <v>7031787</v>
+        <v>7032008</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12461,10 +12461,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118587773</v>
+        <v>118596564</v>
       </c>
       <c r="B116" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12473,38 +12473,47 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>589442</v>
+        <v>589368</v>
       </c>
       <c r="R116" t="n">
-        <v>7032089</v>
+        <v>7031833</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12563,10 +12572,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118587499</v>
+        <v>118596677</v>
       </c>
       <c r="B117" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12575,38 +12584,42 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589524</v>
+        <v>589425</v>
       </c>
       <c r="R117" t="n">
-        <v>7032087</v>
+        <v>7031806</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12767,10 +12780,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118589093</v>
+        <v>118587632</v>
       </c>
       <c r="B119" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12783,39 +12796,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589495</v>
+        <v>589517</v>
       </c>
       <c r="R119" t="n">
-        <v>7031990</v>
+        <v>7032098</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12874,10 +12882,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118587632</v>
+        <v>118591019</v>
       </c>
       <c r="B120" t="n">
-        <v>78484</v>
+        <v>86820</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12890,34 +12898,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589517</v>
+        <v>589686</v>
       </c>
       <c r="R120" t="n">
-        <v>7032098</v>
+        <v>7031880</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -12976,10 +12984,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118587667</v>
+        <v>118589338</v>
       </c>
       <c r="B121" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12988,25 +12996,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13016,10 +13024,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>589455</v>
+        <v>589593</v>
       </c>
       <c r="R121" t="n">
-        <v>7032096</v>
+        <v>7032037</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13078,10 +13086,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118590334</v>
+        <v>118586687</v>
       </c>
       <c r="B122" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13090,42 +13098,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>589578</v>
+        <v>589736</v>
       </c>
       <c r="R122" t="n">
-        <v>7032004</v>
+        <v>7032057</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13184,10 +13188,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118597176</v>
+        <v>118587967</v>
       </c>
       <c r="B123" t="n">
-        <v>97763</v>
+        <v>90469</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13200,34 +13204,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589501</v>
+        <v>589432</v>
       </c>
       <c r="R123" t="n">
-        <v>7031949</v>
+        <v>7032081</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13286,10 +13290,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118587754</v>
+        <v>118594447</v>
       </c>
       <c r="B124" t="n">
-        <v>90518</v>
+        <v>90847</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13298,38 +13302,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589443</v>
+        <v>589535</v>
       </c>
       <c r="R124" t="n">
-        <v>7032086</v>
+        <v>7031791</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13388,10 +13392,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118594452</v>
+        <v>118590334</v>
       </c>
       <c r="B125" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13400,38 +13404,42 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589534</v>
+        <v>589578</v>
       </c>
       <c r="R125" t="n">
-        <v>7031791</v>
+        <v>7032004</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13490,10 +13498,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118589613</v>
+        <v>118587499</v>
       </c>
       <c r="B126" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13502,42 +13510,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589740</v>
+        <v>589524</v>
       </c>
       <c r="R126" t="n">
-        <v>7032026</v>
+        <v>7032087</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13596,10 +13600,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118597023</v>
+        <v>118592076</v>
       </c>
       <c r="B127" t="n">
-        <v>57443</v>
+        <v>56494</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13612,26 +13616,27 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13640,10 +13645,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>589517</v>
+        <v>589665</v>
       </c>
       <c r="R127" t="n">
-        <v>7031811</v>
+        <v>7031798</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13702,10 +13707,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118590296</v>
+        <v>118587773</v>
       </c>
       <c r="B128" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13714,47 +13719,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>589588</v>
+        <v>589442</v>
       </c>
       <c r="R128" t="n">
-        <v>7032008</v>
+        <v>7032089</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13813,10 +13809,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118586448</v>
+        <v>118597023</v>
       </c>
       <c r="B129" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13825,42 +13821,42 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589786</v>
+        <v>589517</v>
       </c>
       <c r="R129" t="n">
-        <v>7032053</v>
+        <v>7031811</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -13919,7 +13915,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118596461</v>
+        <v>118586448</v>
       </c>
       <c r="B130" t="n">
         <v>97846</v>
@@ -13954,24 +13950,19 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>589343</v>
+        <v>589786</v>
       </c>
       <c r="R130" t="n">
-        <v>7031883</v>
+        <v>7032053</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14030,10 +14021,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118589906</v>
+        <v>118594520</v>
       </c>
       <c r="B131" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14042,38 +14033,47 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>589676</v>
+        <v>589534</v>
       </c>
       <c r="R131" t="n">
-        <v>7031963</v>
+        <v>7031764</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -3792,10 +3792,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118552378</v>
+        <v>118553989</v>
       </c>
       <c r="B32" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3808,34 +3808,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589267</v>
+        <v>589352</v>
       </c>
       <c r="R32" t="n">
-        <v>7031984</v>
+        <v>7031849</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4302,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118553989</v>
+        <v>118552378</v>
       </c>
       <c r="B37" t="n">
-        <v>57290</v>
+        <v>90788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4318,39 +4323,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589352</v>
+        <v>589267</v>
       </c>
       <c r="R37" t="n">
-        <v>7031849</v>
+        <v>7031984</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118557154</v>
+        <v>118552985</v>
       </c>
       <c r="B38" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4421,38 +4421,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589647</v>
+        <v>589293</v>
       </c>
       <c r="R38" t="n">
-        <v>7031952</v>
+        <v>7031918</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4511,10 +4515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118554822</v>
+        <v>118557154</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4527,34 +4531,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589399</v>
+        <v>589647</v>
       </c>
       <c r="R39" t="n">
-        <v>7031814</v>
+        <v>7031952</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4613,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118551947</v>
+        <v>118554822</v>
       </c>
       <c r="B40" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4625,38 +4629,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589423</v>
+        <v>589399</v>
       </c>
       <c r="R40" t="n">
-        <v>7032113</v>
+        <v>7031814</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4715,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118552985</v>
+        <v>118551947</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4727,42 +4731,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589293</v>
+        <v>589423</v>
       </c>
       <c r="R41" t="n">
-        <v>7031918</v>
+        <v>7032113</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5956,10 +5956,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118551676</v>
+        <v>118552802</v>
       </c>
       <c r="B53" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5968,38 +5968,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589418</v>
+        <v>589313</v>
       </c>
       <c r="R53" t="n">
-        <v>7032144</v>
+        <v>7031955</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6058,10 +6067,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118552111</v>
+        <v>118557265</v>
       </c>
       <c r="B54" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6070,38 +6079,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589317</v>
+        <v>589642</v>
       </c>
       <c r="R54" t="n">
-        <v>7032040</v>
+        <v>7031970</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6160,10 +6178,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118554910</v>
+        <v>118554878</v>
       </c>
       <c r="B55" t="n">
-        <v>90788</v>
+        <v>79525</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6172,25 +6190,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6200,10 +6218,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589428</v>
+        <v>589437</v>
       </c>
       <c r="R55" t="n">
-        <v>7031801</v>
+        <v>7031771</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6262,10 +6280,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118557454</v>
+        <v>118551676</v>
       </c>
       <c r="B56" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6278,21 +6296,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6302,10 +6320,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589632</v>
+        <v>589418</v>
       </c>
       <c r="R56" t="n">
-        <v>7032019</v>
+        <v>7032144</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6364,10 +6382,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118551880</v>
+        <v>118552111</v>
       </c>
       <c r="B57" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6376,25 +6394,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6404,10 +6422,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589417</v>
+        <v>589317</v>
       </c>
       <c r="R57" t="n">
-        <v>7032126</v>
+        <v>7032040</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6466,10 +6484,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118554548</v>
+        <v>118554910</v>
       </c>
       <c r="B58" t="n">
-        <v>90469</v>
+        <v>90788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6478,25 +6496,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6506,10 +6524,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589348</v>
+        <v>589428</v>
       </c>
       <c r="R58" t="n">
-        <v>7031858</v>
+        <v>7031801</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6568,10 +6586,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118557202</v>
+        <v>118557454</v>
       </c>
       <c r="B59" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6584,21 +6602,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6608,10 +6626,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589643</v>
+        <v>589632</v>
       </c>
       <c r="R59" t="n">
-        <v>7031980</v>
+        <v>7032019</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6670,7 +6688,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118552219</v>
+        <v>118551880</v>
       </c>
       <c r="B60" t="n">
         <v>90469</v>
@@ -6706,14 +6724,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589268</v>
+        <v>589417</v>
       </c>
       <c r="R60" t="n">
-        <v>7031998</v>
+        <v>7032126</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6772,10 +6790,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118555409</v>
+        <v>118554548</v>
       </c>
       <c r="B61" t="n">
-        <v>90847</v>
+        <v>90469</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6784,25 +6802,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6812,10 +6830,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589487</v>
+        <v>589348</v>
       </c>
       <c r="R61" t="n">
-        <v>7031784</v>
+        <v>7031858</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6874,10 +6892,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118552802</v>
+        <v>118557202</v>
       </c>
       <c r="B62" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6886,47 +6904,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589313</v>
+        <v>589643</v>
       </c>
       <c r="R62" t="n">
-        <v>7031955</v>
+        <v>7031980</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6985,10 +6994,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118557265</v>
+        <v>118552219</v>
       </c>
       <c r="B63" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6997,47 +7006,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589642</v>
+        <v>589268</v>
       </c>
       <c r="R63" t="n">
-        <v>7031970</v>
+        <v>7031998</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7096,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118554878</v>
+        <v>118555409</v>
       </c>
       <c r="B64" t="n">
-        <v>79525</v>
+        <v>90847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7108,25 +7108,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>2062</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7136,10 +7136,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589437</v>
+        <v>589487</v>
       </c>
       <c r="R64" t="n">
-        <v>7031771</v>
+        <v>7031784</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7198,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118554223</v>
+        <v>118555355</v>
       </c>
       <c r="B65" t="n">
-        <v>90666</v>
+        <v>90504</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589368</v>
+        <v>589463</v>
       </c>
       <c r="R65" t="n">
-        <v>7031862</v>
+        <v>7031785</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118552663</v>
+        <v>118554223</v>
       </c>
       <c r="B66" t="n">
-        <v>90469</v>
+        <v>90666</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7312,25 +7312,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589275</v>
+        <v>589368</v>
       </c>
       <c r="R66" t="n">
-        <v>7031984</v>
+        <v>7031862</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7402,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118555355</v>
+        <v>118552663</v>
       </c>
       <c r="B67" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7414,25 +7414,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7442,10 +7442,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589463</v>
+        <v>589275</v>
       </c>
       <c r="R67" t="n">
-        <v>7031785</v>
+        <v>7031984</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7708,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118555659</v>
+        <v>118554978</v>
       </c>
       <c r="B70" t="n">
-        <v>57306</v>
+        <v>90947</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7720,43 +7720,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589466</v>
+        <v>589414</v>
       </c>
       <c r="R70" t="n">
-        <v>7031640</v>
+        <v>7031799</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7815,10 +7810,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118554978</v>
+        <v>118555659</v>
       </c>
       <c r="B71" t="n">
-        <v>90947</v>
+        <v>57306</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7827,38 +7822,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589414</v>
+        <v>589466</v>
       </c>
       <c r="R71" t="n">
-        <v>7031799</v>
+        <v>7031640</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8130,10 +8130,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118555468</v>
+        <v>118557174</v>
       </c>
       <c r="B74" t="n">
-        <v>90504</v>
+        <v>79469</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8142,38 +8142,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589488</v>
+        <v>589654</v>
       </c>
       <c r="R74" t="n">
-        <v>7031771</v>
+        <v>7031957</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8232,10 +8232,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118552694</v>
+        <v>118554171</v>
       </c>
       <c r="B75" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8248,21 +8248,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589282</v>
+        <v>589359</v>
       </c>
       <c r="R75" t="n">
-        <v>7031935</v>
+        <v>7031858</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8334,10 +8334,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118557174</v>
+        <v>118555906</v>
       </c>
       <c r="B76" t="n">
-        <v>79469</v>
+        <v>57290</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8346,38 +8346,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589654</v>
+        <v>589312</v>
       </c>
       <c r="R76" t="n">
-        <v>7031957</v>
+        <v>7031697</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8436,10 +8441,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118554171</v>
+        <v>118555468</v>
       </c>
       <c r="B77" t="n">
-        <v>90522</v>
+        <v>90504</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8452,21 +8457,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8476,10 +8481,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589359</v>
+        <v>589488</v>
       </c>
       <c r="R77" t="n">
-        <v>7031858</v>
+        <v>7031771</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8538,10 +8543,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118555906</v>
+        <v>118552694</v>
       </c>
       <c r="B78" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8554,39 +8559,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589312</v>
+        <v>589282</v>
       </c>
       <c r="R78" t="n">
-        <v>7031697</v>
+        <v>7031935</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9976,10 +9976,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118589918</v>
+        <v>118596461</v>
       </c>
       <c r="B92" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9988,38 +9988,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589675</v>
+        <v>589343</v>
       </c>
       <c r="R92" t="n">
-        <v>7031964</v>
+        <v>7031883</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10078,10 +10087,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118588515</v>
+        <v>118589918</v>
       </c>
       <c r="B93" t="n">
-        <v>90500</v>
+        <v>79469</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10090,25 +10099,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10118,10 +10127,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589417</v>
+        <v>589675</v>
       </c>
       <c r="R93" t="n">
-        <v>7032079</v>
+        <v>7031964</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10180,10 +10189,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118596822</v>
+        <v>118588515</v>
       </c>
       <c r="B94" t="n">
-        <v>90788</v>
+        <v>90500</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10196,34 +10205,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589457</v>
+        <v>589417</v>
       </c>
       <c r="R94" t="n">
-        <v>7031787</v>
+        <v>7032079</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10282,10 +10291,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118596461</v>
+        <v>118596822</v>
       </c>
       <c r="B95" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10294,47 +10303,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589343</v>
+        <v>589457</v>
       </c>
       <c r="R95" t="n">
-        <v>7031883</v>
+        <v>7031787</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10908,10 +10908,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118591032</v>
+        <v>118589613</v>
       </c>
       <c r="B101" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10920,38 +10920,42 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589690</v>
+        <v>589740</v>
       </c>
       <c r="R101" t="n">
-        <v>7031882</v>
+        <v>7032026</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11010,10 +11014,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118589613</v>
+        <v>118591032</v>
       </c>
       <c r="B102" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11022,42 +11026,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589740</v>
+        <v>589690</v>
       </c>
       <c r="R102" t="n">
-        <v>7032026</v>
+        <v>7031882</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11427,10 +11427,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118597176</v>
+        <v>118597248</v>
       </c>
       <c r="B106" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11439,38 +11439,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589501</v>
+        <v>589494</v>
       </c>
       <c r="R106" t="n">
-        <v>7031949</v>
+        <v>7031972</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11529,10 +11534,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118597248</v>
+        <v>118597176</v>
       </c>
       <c r="B107" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11541,43 +11546,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589494</v>
+        <v>589501</v>
       </c>
       <c r="R107" t="n">
-        <v>7031972</v>
+        <v>7031949</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -12146,10 +12146,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118587799</v>
+        <v>118590681</v>
       </c>
       <c r="B113" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12158,38 +12158,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589440</v>
+        <v>589668</v>
       </c>
       <c r="R113" t="n">
-        <v>7032089</v>
+        <v>7031892</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118590681</v>
+        <v>118587799</v>
       </c>
       <c r="B114" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12260,38 +12260,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589668</v>
+        <v>589440</v>
       </c>
       <c r="R114" t="n">
-        <v>7031892</v>
+        <v>7032089</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12572,10 +12572,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118596677</v>
+        <v>118587264</v>
       </c>
       <c r="B117" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12584,42 +12584,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589425</v>
+        <v>589634</v>
       </c>
       <c r="R117" t="n">
-        <v>7031806</v>
+        <v>7032061</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12678,10 +12674,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118587264</v>
+        <v>118596677</v>
       </c>
       <c r="B118" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12690,38 +12686,42 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589634</v>
+        <v>589425</v>
       </c>
       <c r="R118" t="n">
-        <v>7032061</v>
+        <v>7031806</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118552853</v>
+        <v>118557914</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589290</v>
+        <v>589694</v>
       </c>
       <c r="R4" t="n">
-        <v>7031929</v>
+        <v>7032099</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118552350</v>
+        <v>118553096</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>82263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589284</v>
+        <v>589204</v>
       </c>
       <c r="R5" t="n">
-        <v>7031972</v>
+        <v>7031942</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118551431</v>
+        <v>118556301</v>
       </c>
       <c r="B6" t="n">
         <v>78484</v>
@@ -1159,14 +1159,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589557</v>
+        <v>589298</v>
       </c>
       <c r="R6" t="n">
-        <v>7032281</v>
+        <v>7031829</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118551872</v>
+        <v>118557202</v>
       </c>
       <c r="B7" t="n">
-        <v>90788</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589417</v>
+        <v>589643</v>
       </c>
       <c r="R7" t="n">
-        <v>7032126</v>
+        <v>7031980</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118554689</v>
+        <v>118551771</v>
       </c>
       <c r="B8" t="n">
         <v>90469</v>
@@ -1363,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589412</v>
+        <v>589423</v>
       </c>
       <c r="R8" t="n">
-        <v>7031811</v>
+        <v>7032117</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118551796</v>
+        <v>118553989</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,34 +1445,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589417</v>
+        <v>589352</v>
       </c>
       <c r="R9" t="n">
-        <v>7032141</v>
+        <v>7031849</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1531,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118552748</v>
+        <v>118552985</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1566,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1575,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589291</v>
+        <v>589293</v>
       </c>
       <c r="R10" t="n">
-        <v>7031953</v>
+        <v>7031918</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118552820</v>
+        <v>118552657</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1672,12 +1677,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589311</v>
+        <v>589282</v>
       </c>
       <c r="R11" t="n">
-        <v>7031954</v>
+        <v>7031970</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118556301</v>
+        <v>118555030</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589298</v>
+        <v>589414</v>
       </c>
       <c r="R12" t="n">
-        <v>7031829</v>
+        <v>7031799</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118552051</v>
+        <v>118554184</v>
       </c>
       <c r="B13" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,38 +1862,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589348</v>
+        <v>589360</v>
       </c>
       <c r="R13" t="n">
-        <v>7032078</v>
+        <v>7031856</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118556472</v>
+        <v>118552031</v>
       </c>
       <c r="B14" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,38 +1964,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589408</v>
+        <v>589360</v>
       </c>
       <c r="R14" t="n">
-        <v>7031876</v>
+        <v>7032085</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118555622</v>
+        <v>118554168</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589490</v>
+        <v>589359</v>
       </c>
       <c r="R15" t="n">
-        <v>7031668</v>
+        <v>7031857</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118556986</v>
+        <v>118552498</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,38 +2168,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589680</v>
+        <v>589280</v>
       </c>
       <c r="R16" t="n">
-        <v>7031886</v>
+        <v>7031976</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2258,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118557914</v>
+        <v>118552802</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2270,38 +2279,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589694</v>
+        <v>589313</v>
       </c>
       <c r="R17" t="n">
-        <v>7032099</v>
+        <v>7031955</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2360,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118553615</v>
+        <v>118557265</v>
       </c>
       <c r="B18" t="n">
-        <v>79469</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,38 +2390,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589180</v>
+        <v>589642</v>
       </c>
       <c r="R18" t="n">
-        <v>7031880</v>
+        <v>7031970</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2462,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118556821</v>
+        <v>118551992</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,38 +2501,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589651</v>
+        <v>589373</v>
       </c>
       <c r="R19" t="n">
-        <v>7031856</v>
+        <v>7032142</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2564,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118552007</v>
+        <v>118556472</v>
       </c>
       <c r="B20" t="n">
-        <v>90504</v>
+        <v>79469</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2576,38 +2603,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589378</v>
+        <v>589408</v>
       </c>
       <c r="R20" t="n">
-        <v>7032143</v>
+        <v>7031876</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2666,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118552031</v>
+        <v>118551676</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2682,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589360</v>
+        <v>589418</v>
       </c>
       <c r="R21" t="n">
-        <v>7032085</v>
+        <v>7032144</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2768,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118557229</v>
+        <v>118556365</v>
       </c>
       <c r="B22" t="n">
-        <v>79469</v>
+        <v>90504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2780,38 +2807,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589650</v>
+        <v>589354</v>
       </c>
       <c r="R22" t="n">
-        <v>7031972</v>
+        <v>7031906</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2870,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118554184</v>
+        <v>118555445</v>
       </c>
       <c r="B23" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2882,25 +2909,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2910,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589360</v>
+        <v>589487</v>
       </c>
       <c r="R23" t="n">
-        <v>7031856</v>
+        <v>7031784</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2972,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118551992</v>
+        <v>118551880</v>
       </c>
       <c r="B24" t="n">
         <v>90469</v>
@@ -3012,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589373</v>
+        <v>589417</v>
       </c>
       <c r="R24" t="n">
-        <v>7032142</v>
+        <v>7032126</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3074,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118552992</v>
+        <v>118557940</v>
       </c>
       <c r="B25" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,34 +3117,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589298</v>
+        <v>589730</v>
       </c>
       <c r="R25" t="n">
-        <v>7031917</v>
+        <v>7032086</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3176,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118556574</v>
+        <v>118551972</v>
       </c>
       <c r="B26" t="n">
-        <v>90788</v>
+        <v>90504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3192,34 +3219,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589407</v>
+        <v>589404</v>
       </c>
       <c r="R26" t="n">
-        <v>7031827</v>
+        <v>7032115</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3278,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118552101</v>
+        <v>118555468</v>
       </c>
       <c r="B27" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3290,38 +3317,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589319</v>
+        <v>589488</v>
       </c>
       <c r="R27" t="n">
-        <v>7032043</v>
+        <v>7031771</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3380,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118553096</v>
+        <v>118555659</v>
       </c>
       <c r="B28" t="n">
-        <v>82263</v>
+        <v>57306</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3396,34 +3423,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589204</v>
+        <v>589466</v>
       </c>
       <c r="R28" t="n">
-        <v>7031942</v>
+        <v>7031640</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3482,7 +3514,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118552657</v>
+        <v>118552748</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3517,7 +3549,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3526,10 +3558,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589282</v>
+        <v>589291</v>
       </c>
       <c r="R29" t="n">
-        <v>7031970</v>
+        <v>7031953</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3588,10 +3620,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118552163</v>
+        <v>118554548</v>
       </c>
       <c r="B30" t="n">
-        <v>79594</v>
+        <v>90469</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,34 +3636,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589309</v>
+        <v>589348</v>
       </c>
       <c r="R30" t="n">
-        <v>7032040</v>
+        <v>7031858</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3690,10 +3722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118551972</v>
+        <v>118554978</v>
       </c>
       <c r="B31" t="n">
-        <v>90504</v>
+        <v>90947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3702,38 +3734,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589404</v>
+        <v>589414</v>
       </c>
       <c r="R31" t="n">
-        <v>7032115</v>
+        <v>7031799</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3792,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118553989</v>
+        <v>118551872</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>90788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3808,39 +3840,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589352</v>
+        <v>589417</v>
       </c>
       <c r="R32" t="n">
-        <v>7031849</v>
+        <v>7032126</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3899,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118553087</v>
+        <v>118554910</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>90788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3915,21 +3942,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3939,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589202</v>
+        <v>589428</v>
       </c>
       <c r="R33" t="n">
-        <v>7031945</v>
+        <v>7031801</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4001,10 +4028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118551771</v>
+        <v>118557174</v>
       </c>
       <c r="B34" t="n">
-        <v>90469</v>
+        <v>79469</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4017,21 +4044,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4041,10 +4068,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589423</v>
+        <v>589654</v>
       </c>
       <c r="R34" t="n">
-        <v>7032117</v>
+        <v>7031957</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4103,10 +4130,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118554252</v>
+        <v>118554223</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
+        <v>90666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4119,21 +4146,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4205,10 +4232,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118557448</v>
+        <v>118553087</v>
       </c>
       <c r="B36" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4217,38 +4244,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589632</v>
+        <v>589202</v>
       </c>
       <c r="R36" t="n">
-        <v>7032018</v>
+        <v>7031945</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4307,10 +4334,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118552378</v>
+        <v>118552278</v>
       </c>
       <c r="B37" t="n">
-        <v>90788</v>
+        <v>90522</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4323,21 +4350,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4347,10 +4374,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589267</v>
+        <v>589280</v>
       </c>
       <c r="R37" t="n">
-        <v>7031984</v>
+        <v>7031985</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4409,10 +4436,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118552985</v>
+        <v>118553615</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>79469</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4421,42 +4448,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589293</v>
+        <v>589180</v>
       </c>
       <c r="R38" t="n">
-        <v>7031918</v>
+        <v>7031880</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4515,10 +4538,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118557154</v>
+        <v>118554171</v>
       </c>
       <c r="B39" t="n">
-        <v>79565</v>
+        <v>90522</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4531,34 +4554,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589647</v>
+        <v>589359</v>
       </c>
       <c r="R39" t="n">
-        <v>7031952</v>
+        <v>7031858</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4617,7 +4640,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118554822</v>
+        <v>118551431</v>
       </c>
       <c r="B40" t="n">
         <v>78484</v>
@@ -4653,14 +4676,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589399</v>
+        <v>589557</v>
       </c>
       <c r="R40" t="n">
-        <v>7031814</v>
+        <v>7032281</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4719,7 +4742,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118551947</v>
+        <v>118557448</v>
       </c>
       <c r="B41" t="n">
         <v>90469</v>
@@ -4759,10 +4782,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589423</v>
+        <v>589632</v>
       </c>
       <c r="R41" t="n">
-        <v>7032113</v>
+        <v>7032018</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4821,10 +4844,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118555445</v>
+        <v>118555355</v>
       </c>
       <c r="B42" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4833,25 +4856,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4861,10 +4884,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589487</v>
+        <v>589463</v>
       </c>
       <c r="R42" t="n">
-        <v>7031784</v>
+        <v>7031785</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4923,10 +4946,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118557940</v>
+        <v>118556574</v>
       </c>
       <c r="B43" t="n">
-        <v>79565</v>
+        <v>90788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4939,34 +4962,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589730</v>
+        <v>589407</v>
       </c>
       <c r="R43" t="n">
-        <v>7032086</v>
+        <v>7031827</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5025,10 +5048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118552764</v>
+        <v>118552101</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5037,42 +5060,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589297</v>
+        <v>589319</v>
       </c>
       <c r="R44" t="n">
-        <v>7031952</v>
+        <v>7032043</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5131,10 +5150,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118554028</v>
+        <v>118555409</v>
       </c>
       <c r="B45" t="n">
-        <v>90469</v>
+        <v>90847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5143,25 +5162,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5171,10 +5190,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589341</v>
+        <v>589487</v>
       </c>
       <c r="R45" t="n">
-        <v>7031857</v>
+        <v>7031784</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5233,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118557661</v>
+        <v>118552820</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5245,38 +5264,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589635</v>
+        <v>589311</v>
       </c>
       <c r="R46" t="n">
-        <v>7032058</v>
+        <v>7031954</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5335,7 +5363,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118551885</v>
+        <v>118554450</v>
       </c>
       <c r="B47" t="n">
         <v>90788</v>
@@ -5371,14 +5399,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589410</v>
+        <v>589392</v>
       </c>
       <c r="R47" t="n">
-        <v>7032119</v>
+        <v>7031860</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5437,10 +5465,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118556365</v>
+        <v>118552200</v>
       </c>
       <c r="B48" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5449,38 +5477,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589354</v>
+        <v>589314</v>
       </c>
       <c r="R48" t="n">
-        <v>7031906</v>
+        <v>7032037</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5539,10 +5576,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118555302</v>
+        <v>118555906</v>
       </c>
       <c r="B49" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5555,34 +5592,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589472</v>
+        <v>589312</v>
       </c>
       <c r="R49" t="n">
-        <v>7031796</v>
+        <v>7031697</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5641,10 +5683,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118557253</v>
+        <v>118551796</v>
       </c>
       <c r="B50" t="n">
-        <v>58133</v>
+        <v>90504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5653,25 +5695,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>208249</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5681,10 +5723,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589648</v>
+        <v>589417</v>
       </c>
       <c r="R50" t="n">
-        <v>7031970</v>
+        <v>7032141</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5743,10 +5785,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118552498</v>
+        <v>118554028</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5755,47 +5797,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589280</v>
+        <v>589341</v>
       </c>
       <c r="R51" t="n">
-        <v>7031976</v>
+        <v>7031857</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5854,10 +5887,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118555030</v>
+        <v>118552350</v>
       </c>
       <c r="B52" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5870,21 +5903,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5894,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589414</v>
+        <v>589284</v>
       </c>
       <c r="R52" t="n">
-        <v>7031799</v>
+        <v>7031972</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5956,10 +5989,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118552802</v>
+        <v>118556986</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5968,47 +6001,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589313</v>
+        <v>589680</v>
       </c>
       <c r="R53" t="n">
-        <v>7031955</v>
+        <v>7031886</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6067,10 +6091,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118557265</v>
+        <v>118551947</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6079,47 +6103,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589642</v>
+        <v>589423</v>
       </c>
       <c r="R54" t="n">
-        <v>7031970</v>
+        <v>7032113</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6178,10 +6193,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118554878</v>
+        <v>118554252</v>
       </c>
       <c r="B55" t="n">
-        <v>79525</v>
+        <v>78484</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6190,25 +6205,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6218,10 +6233,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589437</v>
+        <v>589368</v>
       </c>
       <c r="R55" t="n">
-        <v>7031771</v>
+        <v>7031862</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6280,10 +6295,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118551676</v>
+        <v>118552663</v>
       </c>
       <c r="B56" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6292,38 +6307,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589418</v>
+        <v>589275</v>
       </c>
       <c r="R56" t="n">
-        <v>7032144</v>
+        <v>7031984</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6382,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118552111</v>
+        <v>118551885</v>
       </c>
       <c r="B57" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6398,21 +6413,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6422,10 +6437,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589317</v>
+        <v>589410</v>
       </c>
       <c r="R57" t="n">
-        <v>7032040</v>
+        <v>7032119</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6484,10 +6499,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118554910</v>
+        <v>118558184</v>
       </c>
       <c r="B58" t="n">
-        <v>90788</v>
+        <v>97763</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6496,38 +6511,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589428</v>
+        <v>589713</v>
       </c>
       <c r="R58" t="n">
-        <v>7031801</v>
+        <v>7032063</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6586,10 +6601,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118557454</v>
+        <v>118552378</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
+        <v>90788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6602,34 +6617,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589632</v>
+        <v>589267</v>
       </c>
       <c r="R59" t="n">
-        <v>7032019</v>
+        <v>7031984</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6688,10 +6703,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118551880</v>
+        <v>118552694</v>
       </c>
       <c r="B60" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6700,38 +6715,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589417</v>
+        <v>589282</v>
       </c>
       <c r="R60" t="n">
-        <v>7032126</v>
+        <v>7031935</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6790,10 +6805,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118554548</v>
+        <v>118555302</v>
       </c>
       <c r="B61" t="n">
-        <v>90469</v>
+        <v>90788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6802,25 +6817,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6830,10 +6845,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589348</v>
+        <v>589472</v>
       </c>
       <c r="R61" t="n">
-        <v>7031858</v>
+        <v>7031796</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6892,7 +6907,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118557202</v>
+        <v>118557154</v>
       </c>
       <c r="B62" t="n">
         <v>79565</v>
@@ -6932,10 +6947,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589643</v>
+        <v>589647</v>
       </c>
       <c r="R62" t="n">
-        <v>7031980</v>
+        <v>7031952</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6994,10 +7009,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118552219</v>
+        <v>118557454</v>
       </c>
       <c r="B63" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7006,38 +7021,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589268</v>
+        <v>589632</v>
       </c>
       <c r="R63" t="n">
-        <v>7031998</v>
+        <v>7032019</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7096,10 +7111,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118555409</v>
+        <v>118557661</v>
       </c>
       <c r="B64" t="n">
-        <v>90847</v>
+        <v>78484</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7108,38 +7123,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589487</v>
+        <v>589635</v>
       </c>
       <c r="R64" t="n">
-        <v>7031784</v>
+        <v>7032058</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7198,10 +7213,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118555355</v>
+        <v>118555622</v>
       </c>
       <c r="B65" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7214,21 +7229,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7238,10 +7253,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589463</v>
+        <v>589490</v>
       </c>
       <c r="R65" t="n">
-        <v>7031785</v>
+        <v>7031668</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7300,10 +7315,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118554223</v>
+        <v>118552111</v>
       </c>
       <c r="B66" t="n">
-        <v>90666</v>
+        <v>90504</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7316,34 +7331,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589368</v>
+        <v>589317</v>
       </c>
       <c r="R66" t="n">
-        <v>7031862</v>
+        <v>7032040</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7402,10 +7417,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118552663</v>
+        <v>118554797</v>
       </c>
       <c r="B67" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7414,25 +7429,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7442,10 +7457,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589275</v>
+        <v>589358</v>
       </c>
       <c r="R67" t="n">
-        <v>7031984</v>
+        <v>7031830</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7504,10 +7519,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118552278</v>
+        <v>118554878</v>
       </c>
       <c r="B68" t="n">
-        <v>90522</v>
+        <v>79525</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7516,25 +7531,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7544,10 +7559,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589280</v>
+        <v>589437</v>
       </c>
       <c r="R68" t="n">
-        <v>7031985</v>
+        <v>7031771</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7606,10 +7621,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118553061</v>
+        <v>118554822</v>
       </c>
       <c r="B69" t="n">
-        <v>86820</v>
+        <v>78484</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7622,21 +7637,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7646,10 +7661,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589254</v>
+        <v>589399</v>
       </c>
       <c r="R69" t="n">
-        <v>7031953</v>
+        <v>7031814</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7708,10 +7723,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118554978</v>
+        <v>118552051</v>
       </c>
       <c r="B70" t="n">
-        <v>90947</v>
+        <v>90469</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7720,38 +7735,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589414</v>
+        <v>589348</v>
       </c>
       <c r="R70" t="n">
-        <v>7031799</v>
+        <v>7032078</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7810,10 +7825,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118555659</v>
+        <v>118552163</v>
       </c>
       <c r="B71" t="n">
-        <v>57306</v>
+        <v>79594</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7822,43 +7837,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589466</v>
+        <v>589309</v>
       </c>
       <c r="R71" t="n">
-        <v>7031640</v>
+        <v>7032040</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7917,10 +7927,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118558184</v>
+        <v>118552219</v>
       </c>
       <c r="B72" t="n">
-        <v>97763</v>
+        <v>90469</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7933,34 +7943,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589713</v>
+        <v>589268</v>
       </c>
       <c r="R72" t="n">
-        <v>7032063</v>
+        <v>7031998</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8019,10 +8029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118552200</v>
+        <v>118557253</v>
       </c>
       <c r="B73" t="n">
-        <v>97846</v>
+        <v>58133</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8031,47 +8041,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589314</v>
+        <v>589648</v>
       </c>
       <c r="R73" t="n">
-        <v>7032037</v>
+        <v>7031970</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8130,10 +8131,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118557174</v>
+        <v>118552992</v>
       </c>
       <c r="B74" t="n">
-        <v>79469</v>
+        <v>90504</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8142,38 +8143,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589654</v>
+        <v>589298</v>
       </c>
       <c r="R74" t="n">
-        <v>7031957</v>
+        <v>7031917</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8232,10 +8233,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118554171</v>
+        <v>118553061</v>
       </c>
       <c r="B75" t="n">
-        <v>90522</v>
+        <v>86820</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8248,21 +8249,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8272,10 +8273,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589359</v>
+        <v>589254</v>
       </c>
       <c r="R75" t="n">
-        <v>7031858</v>
+        <v>7031953</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8334,10 +8335,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118555906</v>
+        <v>118554689</v>
       </c>
       <c r="B76" t="n">
-        <v>57290</v>
+        <v>90469</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8346,43 +8347,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589312</v>
+        <v>589412</v>
       </c>
       <c r="R76" t="n">
-        <v>7031697</v>
+        <v>7031811</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8441,10 +8437,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118555468</v>
+        <v>118557229</v>
       </c>
       <c r="B77" t="n">
-        <v>90504</v>
+        <v>79469</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8453,38 +8449,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589488</v>
+        <v>589650</v>
       </c>
       <c r="R77" t="n">
-        <v>7031771</v>
+        <v>7031972</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8543,7 +8539,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118552694</v>
+        <v>118552007</v>
       </c>
       <c r="B78" t="n">
         <v>90504</v>
@@ -8579,14 +8575,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589282</v>
+        <v>589378</v>
       </c>
       <c r="R78" t="n">
-        <v>7031935</v>
+        <v>7032143</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8645,7 +8641,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118554168</v>
+        <v>118552853</v>
       </c>
       <c r="B79" t="n">
         <v>90469</v>
@@ -8685,10 +8681,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589359</v>
+        <v>589290</v>
       </c>
       <c r="R79" t="n">
-        <v>7031857</v>
+        <v>7031929</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8747,10 +8743,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118554450</v>
+        <v>118556821</v>
       </c>
       <c r="B80" t="n">
-        <v>90788</v>
+        <v>78484</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8763,21 +8759,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8787,10 +8783,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589392</v>
+        <v>589651</v>
       </c>
       <c r="R80" t="n">
-        <v>7031860</v>
+        <v>7031856</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8849,10 +8845,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118554797</v>
+        <v>118552764</v>
       </c>
       <c r="B81" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8861,38 +8857,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589358</v>
+        <v>589297</v>
       </c>
       <c r="R81" t="n">
-        <v>7031830</v>
+        <v>7031952</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8951,10 +8951,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118587872</v>
+        <v>118591019</v>
       </c>
       <c r="B82" t="n">
-        <v>90469</v>
+        <v>86820</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8963,38 +8963,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589438</v>
+        <v>589686</v>
       </c>
       <c r="R82" t="n">
-        <v>7032059</v>
+        <v>7031880</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118590255</v>
+        <v>118587264</v>
       </c>
       <c r="B83" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9069,21 +9069,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589607</v>
+        <v>589634</v>
       </c>
       <c r="R83" t="n">
-        <v>7032009</v>
+        <v>7032061</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9155,10 +9155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118587754</v>
+        <v>118587632</v>
       </c>
       <c r="B84" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9171,21 +9171,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589443</v>
+        <v>589517</v>
       </c>
       <c r="R84" t="n">
-        <v>7032086</v>
+        <v>7032098</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118594452</v>
+        <v>118589486</v>
       </c>
       <c r="B85" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9269,38 +9269,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589534</v>
+        <v>589657</v>
       </c>
       <c r="R85" t="n">
-        <v>7031791</v>
+        <v>7031995</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118587924</v>
+        <v>118589338</v>
       </c>
       <c r="B86" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9371,25 +9371,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589445</v>
+        <v>589593</v>
       </c>
       <c r="R86" t="n">
-        <v>7032073</v>
+        <v>7032037</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118588128</v>
+        <v>118597023</v>
       </c>
       <c r="B87" t="n">
-        <v>90469</v>
+        <v>57443</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9473,38 +9473,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589428</v>
+        <v>589517</v>
       </c>
       <c r="R87" t="n">
-        <v>7032108</v>
+        <v>7031811</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9563,10 +9567,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118589036</v>
+        <v>118588515</v>
       </c>
       <c r="B88" t="n">
-        <v>90469</v>
+        <v>90500</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9575,25 +9579,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9603,10 +9607,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589506</v>
+        <v>589417</v>
       </c>
       <c r="R88" t="n">
-        <v>7031977</v>
+        <v>7032079</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9665,10 +9669,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118589906</v>
+        <v>118596031</v>
       </c>
       <c r="B89" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9681,34 +9685,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589676</v>
+        <v>589279</v>
       </c>
       <c r="R89" t="n">
-        <v>7031963</v>
+        <v>7031737</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9767,10 +9771,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118588485</v>
+        <v>118591032</v>
       </c>
       <c r="B90" t="n">
-        <v>90788</v>
+        <v>90522</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9783,34 +9787,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589403</v>
+        <v>589690</v>
       </c>
       <c r="R90" t="n">
-        <v>7032119</v>
+        <v>7031882</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9869,10 +9873,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118589093</v>
+        <v>118586687</v>
       </c>
       <c r="B91" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9885,39 +9889,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589495</v>
+        <v>589736</v>
       </c>
       <c r="R91" t="n">
-        <v>7031990</v>
+        <v>7032057</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9976,10 +9975,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118596461</v>
+        <v>118597248</v>
       </c>
       <c r="B92" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9988,47 +9987,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589343</v>
+        <v>589494</v>
       </c>
       <c r="R92" t="n">
-        <v>7031883</v>
+        <v>7031972</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10087,10 +10082,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118589918</v>
+        <v>118587499</v>
       </c>
       <c r="B93" t="n">
-        <v>79469</v>
+        <v>90522</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10099,25 +10094,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10127,10 +10122,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589675</v>
+        <v>589524</v>
       </c>
       <c r="R93" t="n">
-        <v>7031964</v>
+        <v>7032087</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10189,10 +10184,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118588515</v>
+        <v>118597134</v>
       </c>
       <c r="B94" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10205,34 +10200,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589417</v>
+        <v>589508</v>
       </c>
       <c r="R94" t="n">
-        <v>7032079</v>
+        <v>7031905</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10291,10 +10286,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118596822</v>
+        <v>118587799</v>
       </c>
       <c r="B95" t="n">
-        <v>90788</v>
+        <v>90504</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10307,34 +10302,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589457</v>
+        <v>589440</v>
       </c>
       <c r="R95" t="n">
-        <v>7031787</v>
+        <v>7032089</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10393,10 +10388,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118586696</v>
+        <v>118588534</v>
       </c>
       <c r="B96" t="n">
-        <v>97763</v>
+        <v>90469</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10409,21 +10404,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10433,10 +10428,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589736</v>
+        <v>589413</v>
       </c>
       <c r="R96" t="n">
-        <v>7032064</v>
+        <v>7032084</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10495,10 +10490,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118590971</v>
+        <v>118590296</v>
       </c>
       <c r="B97" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10507,38 +10502,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589691</v>
+        <v>589588</v>
       </c>
       <c r="R97" t="n">
-        <v>7031862</v>
+        <v>7032008</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10597,10 +10601,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118589537</v>
+        <v>118590334</v>
       </c>
       <c r="B98" t="n">
-        <v>86820</v>
+        <v>97846</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10609,38 +10613,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589709</v>
+        <v>589578</v>
       </c>
       <c r="R98" t="n">
-        <v>7031980</v>
+        <v>7032004</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10699,10 +10707,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118594407</v>
+        <v>118596822</v>
       </c>
       <c r="B99" t="n">
-        <v>57306</v>
+        <v>90788</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10715,39 +10723,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589525</v>
+        <v>589457</v>
       </c>
       <c r="R99" t="n">
-        <v>7031796</v>
+        <v>7031787</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10806,10 +10809,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118589486</v>
+        <v>118589906</v>
       </c>
       <c r="B100" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10822,21 +10825,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10846,10 +10849,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589657</v>
+        <v>589676</v>
       </c>
       <c r="R100" t="n">
-        <v>7031995</v>
+        <v>7031963</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10908,10 +10911,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118589613</v>
+        <v>118594452</v>
       </c>
       <c r="B101" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10920,42 +10923,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589740</v>
+        <v>589534</v>
       </c>
       <c r="R101" t="n">
-        <v>7032026</v>
+        <v>7031791</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11014,10 +11013,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118591032</v>
+        <v>118590681</v>
       </c>
       <c r="B102" t="n">
-        <v>90522</v>
+        <v>90469</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11026,25 +11025,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11054,10 +11053,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589690</v>
+        <v>589668</v>
       </c>
       <c r="R102" t="n">
-        <v>7031882</v>
+        <v>7031892</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11116,10 +11115,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118587901</v>
+        <v>118586448</v>
       </c>
       <c r="B103" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11128,38 +11127,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589438</v>
+        <v>589786</v>
       </c>
       <c r="R103" t="n">
-        <v>7032058</v>
+        <v>7032053</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11218,10 +11221,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118590215</v>
+        <v>118587773</v>
       </c>
       <c r="B104" t="n">
-        <v>57306</v>
+        <v>90469</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11230,43 +11233,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589598</v>
+        <v>589442</v>
       </c>
       <c r="R104" t="n">
-        <v>7031977</v>
+        <v>7032089</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11325,10 +11323,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118589400</v>
+        <v>118594407</v>
       </c>
       <c r="B105" t="n">
-        <v>90522</v>
+        <v>57306</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11341,34 +11339,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589614</v>
+        <v>589525</v>
       </c>
       <c r="R105" t="n">
-        <v>7032054</v>
+        <v>7031796</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11427,10 +11430,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118597248</v>
+        <v>118597176</v>
       </c>
       <c r="B106" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11439,43 +11442,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589494</v>
+        <v>589501</v>
       </c>
       <c r="R106" t="n">
-        <v>7031972</v>
+        <v>7031949</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11534,10 +11532,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118597176</v>
+        <v>118587872</v>
       </c>
       <c r="B107" t="n">
-        <v>97763</v>
+        <v>90469</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11550,34 +11548,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589501</v>
+        <v>589438</v>
       </c>
       <c r="R107" t="n">
-        <v>7031949</v>
+        <v>7032059</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11636,10 +11634,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118587667</v>
+        <v>118590971</v>
       </c>
       <c r="B108" t="n">
-        <v>90469</v>
+        <v>82263</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11648,38 +11646,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>589455</v>
+        <v>589691</v>
       </c>
       <c r="R108" t="n">
-        <v>7032096</v>
+        <v>7031862</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11738,10 +11736,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118597134</v>
+        <v>118589400</v>
       </c>
       <c r="B109" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11754,34 +11752,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>589508</v>
+        <v>589614</v>
       </c>
       <c r="R109" t="n">
-        <v>7031905</v>
+        <v>7032054</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11840,10 +11838,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118596031</v>
+        <v>118596677</v>
       </c>
       <c r="B110" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11852,38 +11850,42 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589279</v>
+        <v>589425</v>
       </c>
       <c r="R110" t="n">
-        <v>7031737</v>
+        <v>7031806</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11942,10 +11944,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118588420</v>
+        <v>118594520</v>
       </c>
       <c r="B111" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11954,38 +11956,47 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589421</v>
+        <v>589534</v>
       </c>
       <c r="R111" t="n">
-        <v>7032124</v>
+        <v>7031764</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12044,10 +12055,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118588534</v>
+        <v>118589093</v>
       </c>
       <c r="B112" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12056,38 +12067,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>589413</v>
+        <v>589495</v>
       </c>
       <c r="R112" t="n">
-        <v>7032084</v>
+        <v>7031990</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12146,10 +12162,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118590681</v>
+        <v>118589537</v>
       </c>
       <c r="B113" t="n">
-        <v>90469</v>
+        <v>86820</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12158,38 +12174,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589668</v>
+        <v>589709</v>
       </c>
       <c r="R113" t="n">
-        <v>7031892</v>
+        <v>7031980</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12248,10 +12264,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118587799</v>
+        <v>118587754</v>
       </c>
       <c r="B114" t="n">
-        <v>90504</v>
+        <v>90518</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12264,21 +12280,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12288,10 +12304,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589440</v>
+        <v>589443</v>
       </c>
       <c r="R114" t="n">
-        <v>7032089</v>
+        <v>7032086</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12350,10 +12366,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118590296</v>
+        <v>118587901</v>
       </c>
       <c r="B115" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12362,47 +12378,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589588</v>
+        <v>589438</v>
       </c>
       <c r="R115" t="n">
-        <v>7032008</v>
+        <v>7032058</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12461,10 +12468,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118596564</v>
+        <v>118587924</v>
       </c>
       <c r="B116" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12473,47 +12480,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>589368</v>
+        <v>589445</v>
       </c>
       <c r="R116" t="n">
-        <v>7031833</v>
+        <v>7032073</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12572,10 +12570,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118587264</v>
+        <v>118590255</v>
       </c>
       <c r="B117" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12588,21 +12586,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12612,10 +12610,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589634</v>
+        <v>589607</v>
       </c>
       <c r="R117" t="n">
-        <v>7032061</v>
+        <v>7032009</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12674,10 +12672,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118596677</v>
+        <v>118589036</v>
       </c>
       <c r="B118" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12686,42 +12684,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589425</v>
+        <v>589506</v>
       </c>
       <c r="R118" t="n">
-        <v>7031806</v>
+        <v>7031977</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12780,10 +12774,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118587632</v>
+        <v>118589613</v>
       </c>
       <c r="B119" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12792,38 +12786,42 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589517</v>
+        <v>589740</v>
       </c>
       <c r="R119" t="n">
-        <v>7032098</v>
+        <v>7032026</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12882,10 +12880,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118591019</v>
+        <v>118588420</v>
       </c>
       <c r="B120" t="n">
-        <v>86820</v>
+        <v>90788</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12898,34 +12896,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589686</v>
+        <v>589421</v>
       </c>
       <c r="R120" t="n">
-        <v>7031880</v>
+        <v>7032124</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -12984,10 +12982,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118589338</v>
+        <v>118586696</v>
       </c>
       <c r="B121" t="n">
-        <v>79565</v>
+        <v>97763</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12996,25 +12994,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13024,10 +13022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>589593</v>
+        <v>589736</v>
       </c>
       <c r="R121" t="n">
-        <v>7032037</v>
+        <v>7032064</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13086,10 +13084,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118586687</v>
+        <v>118596461</v>
       </c>
       <c r="B122" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13098,38 +13096,47 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>589736</v>
+        <v>589343</v>
       </c>
       <c r="R122" t="n">
-        <v>7032057</v>
+        <v>7031883</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13188,10 +13195,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118587967</v>
+        <v>118596564</v>
       </c>
       <c r="B123" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13200,38 +13207,47 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589432</v>
+        <v>589368</v>
       </c>
       <c r="R123" t="n">
-        <v>7032081</v>
+        <v>7031833</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13290,10 +13306,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118594447</v>
+        <v>118589918</v>
       </c>
       <c r="B124" t="n">
-        <v>90847</v>
+        <v>79469</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13302,38 +13318,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589535</v>
+        <v>589675</v>
       </c>
       <c r="R124" t="n">
-        <v>7031791</v>
+        <v>7031964</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13392,10 +13408,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118590334</v>
+        <v>118587967</v>
       </c>
       <c r="B125" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13404,42 +13420,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589578</v>
+        <v>589432</v>
       </c>
       <c r="R125" t="n">
-        <v>7032004</v>
+        <v>7032081</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13498,10 +13510,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118587499</v>
+        <v>118592076</v>
       </c>
       <c r="B126" t="n">
-        <v>90522</v>
+        <v>56494</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13514,34 +13526,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589524</v>
+        <v>589665</v>
       </c>
       <c r="R126" t="n">
-        <v>7032087</v>
+        <v>7031798</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13600,10 +13617,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118592076</v>
+        <v>118588485</v>
       </c>
       <c r="B127" t="n">
-        <v>56494</v>
+        <v>90788</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13616,39 +13633,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>589665</v>
+        <v>589403</v>
       </c>
       <c r="R127" t="n">
-        <v>7031798</v>
+        <v>7032119</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13707,10 +13719,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118587773</v>
+        <v>118590215</v>
       </c>
       <c r="B128" t="n">
-        <v>90469</v>
+        <v>57306</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13719,38 +13731,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>589442</v>
+        <v>589598</v>
       </c>
       <c r="R128" t="n">
-        <v>7032089</v>
+        <v>7031977</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13809,10 +13826,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118597023</v>
+        <v>118587667</v>
       </c>
       <c r="B129" t="n">
-        <v>57443</v>
+        <v>90469</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13821,42 +13838,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589517</v>
+        <v>589455</v>
       </c>
       <c r="R129" t="n">
-        <v>7031811</v>
+        <v>7032096</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -13915,10 +13928,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118586448</v>
+        <v>118594447</v>
       </c>
       <c r="B130" t="n">
-        <v>97846</v>
+        <v>90847</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13931,38 +13944,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>589786</v>
+        <v>589535</v>
       </c>
       <c r="R130" t="n">
-        <v>7032053</v>
+        <v>7031791</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14021,10 +14030,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118594520</v>
+        <v>118588128</v>
       </c>
       <c r="B131" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14033,47 +14042,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>589534</v>
+        <v>589428</v>
       </c>
       <c r="R131" t="n">
-        <v>7031764</v>
+        <v>7032108</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118557914</v>
+        <v>118552992</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589694</v>
+        <v>589298</v>
       </c>
       <c r="R4" t="n">
-        <v>7032099</v>
+        <v>7031917</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118553096</v>
+        <v>118552111</v>
       </c>
       <c r="B5" t="n">
-        <v>82263</v>
+        <v>90511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589204</v>
+        <v>589317</v>
       </c>
       <c r="R5" t="n">
-        <v>7031942</v>
+        <v>7032040</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118556301</v>
+        <v>118555445</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589298</v>
+        <v>589487</v>
       </c>
       <c r="R6" t="n">
-        <v>7031829</v>
+        <v>7031784</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118557202</v>
+        <v>118552219</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>90476</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,38 +1237,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589643</v>
+        <v>589268</v>
       </c>
       <c r="R7" t="n">
-        <v>7031980</v>
+        <v>7031998</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118551771</v>
+        <v>118557448</v>
       </c>
       <c r="B8" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589423</v>
+        <v>589632</v>
       </c>
       <c r="R8" t="n">
-        <v>7032117</v>
+        <v>7032018</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118553989</v>
+        <v>118552985</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,31 +1441,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1474,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589352</v>
+        <v>589293</v>
       </c>
       <c r="R9" t="n">
-        <v>7031849</v>
+        <v>7031918</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1536,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118552985</v>
+        <v>118552802</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,7 +1570,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1580,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589293</v>
+        <v>589313</v>
       </c>
       <c r="R10" t="n">
-        <v>7031918</v>
+        <v>7031955</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1642,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118552657</v>
+        <v>118552694</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,32 +1658,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
@@ -1689,7 +1689,7 @@
         <v>589282</v>
       </c>
       <c r="R11" t="n">
-        <v>7031970</v>
+        <v>7031935</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118555030</v>
+        <v>118557661</v>
       </c>
       <c r="B12" t="n">
-        <v>90504</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,34 +1764,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589414</v>
+        <v>589635</v>
       </c>
       <c r="R12" t="n">
-        <v>7031799</v>
+        <v>7032058</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118554184</v>
+        <v>118551771</v>
       </c>
       <c r="B13" t="n">
-        <v>90504</v>
+        <v>90476</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,38 +1862,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589360</v>
+        <v>589423</v>
       </c>
       <c r="R13" t="n">
-        <v>7031856</v>
+        <v>7032117</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118552031</v>
+        <v>118556301</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,14 +1988,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589360</v>
+        <v>589298</v>
       </c>
       <c r="R14" t="n">
-        <v>7032085</v>
+        <v>7031829</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118554168</v>
+        <v>118556472</v>
       </c>
       <c r="B15" t="n">
-        <v>90469</v>
+        <v>79476</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589359</v>
+        <v>589408</v>
       </c>
       <c r="R15" t="n">
-        <v>7031857</v>
+        <v>7031876</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118552498</v>
+        <v>118553096</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,47 +2168,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589280</v>
+        <v>589204</v>
       </c>
       <c r="R16" t="n">
-        <v>7031976</v>
+        <v>7031942</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2267,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118552802</v>
+        <v>118554184</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,47 +2270,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589313</v>
+        <v>589360</v>
       </c>
       <c r="R17" t="n">
-        <v>7031955</v>
+        <v>7031856</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2378,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118557265</v>
+        <v>118557454</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2390,47 +2372,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589642</v>
+        <v>589632</v>
       </c>
       <c r="R18" t="n">
-        <v>7031970</v>
+        <v>7032019</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2489,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118551992</v>
+        <v>118551431</v>
       </c>
       <c r="B19" t="n">
-        <v>90469</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,25 +2474,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589373</v>
+        <v>589557</v>
       </c>
       <c r="R19" t="n">
-        <v>7032142</v>
+        <v>7032281</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2591,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118556472</v>
+        <v>118551992</v>
       </c>
       <c r="B20" t="n">
-        <v>79469</v>
+        <v>90476</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,34 +2580,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589408</v>
+        <v>589373</v>
       </c>
       <c r="R20" t="n">
-        <v>7031876</v>
+        <v>7032142</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2693,10 +2666,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118551676</v>
+        <v>118552051</v>
       </c>
       <c r="B21" t="n">
-        <v>90504</v>
+        <v>90476</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,25 +2678,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589418</v>
+        <v>589348</v>
       </c>
       <c r="R21" t="n">
-        <v>7032144</v>
+        <v>7032078</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2795,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118556365</v>
+        <v>118554910</v>
       </c>
       <c r="B22" t="n">
-        <v>90504</v>
+        <v>90795</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2784,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589354</v>
+        <v>589428</v>
       </c>
       <c r="R22" t="n">
-        <v>7031906</v>
+        <v>7031801</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2897,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118555445</v>
+        <v>118552031</v>
       </c>
       <c r="B23" t="n">
-        <v>90469</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2909,38 +2882,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589487</v>
+        <v>589360</v>
       </c>
       <c r="R23" t="n">
-        <v>7031784</v>
+        <v>7032085</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2999,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118551880</v>
+        <v>118554822</v>
       </c>
       <c r="B24" t="n">
-        <v>90469</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,38 +2984,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589417</v>
+        <v>589399</v>
       </c>
       <c r="R24" t="n">
-        <v>7032126</v>
+        <v>7031814</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3101,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118557940</v>
+        <v>118557253</v>
       </c>
       <c r="B25" t="n">
-        <v>79565</v>
+        <v>58133</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,25 +3086,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589730</v>
+        <v>589648</v>
       </c>
       <c r="R25" t="n">
-        <v>7032086</v>
+        <v>7031970</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3203,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118551972</v>
+        <v>118557265</v>
       </c>
       <c r="B26" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,38 +3188,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589404</v>
+        <v>589642</v>
       </c>
       <c r="R26" t="n">
-        <v>7032115</v>
+        <v>7031970</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3305,10 +3287,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118555468</v>
+        <v>118551885</v>
       </c>
       <c r="B27" t="n">
-        <v>90504</v>
+        <v>90795</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,34 +3303,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589488</v>
+        <v>589410</v>
       </c>
       <c r="R27" t="n">
-        <v>7031771</v>
+        <v>7032119</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3407,10 +3389,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118555659</v>
+        <v>118555468</v>
       </c>
       <c r="B28" t="n">
-        <v>57306</v>
+        <v>90511</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,39 +3405,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589466</v>
+        <v>589488</v>
       </c>
       <c r="R28" t="n">
-        <v>7031640</v>
+        <v>7031771</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3514,10 +3491,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118552748</v>
+        <v>118553061</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>86827</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3526,39 +3503,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589291</v>
+        <v>589254</v>
       </c>
       <c r="R29" t="n">
         <v>7031953</v>
@@ -3620,10 +3593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118554548</v>
+        <v>118554689</v>
       </c>
       <c r="B30" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,10 +3633,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589348</v>
+        <v>589412</v>
       </c>
       <c r="R30" t="n">
-        <v>7031858</v>
+        <v>7031811</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3722,10 +3695,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118554978</v>
+        <v>118552378</v>
       </c>
       <c r="B31" t="n">
-        <v>90947</v>
+        <v>90795</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3734,25 +3707,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3762,10 +3735,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589414</v>
+        <v>589267</v>
       </c>
       <c r="R31" t="n">
-        <v>7031799</v>
+        <v>7031984</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3824,10 +3797,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118551872</v>
+        <v>118556574</v>
       </c>
       <c r="B32" t="n">
-        <v>90788</v>
+        <v>90795</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,14 +3833,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589417</v>
+        <v>589407</v>
       </c>
       <c r="R32" t="n">
-        <v>7032126</v>
+        <v>7031827</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3926,10 +3899,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118554910</v>
+        <v>118552200</v>
       </c>
       <c r="B33" t="n">
-        <v>90788</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,38 +3911,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589428</v>
+        <v>589314</v>
       </c>
       <c r="R33" t="n">
-        <v>7031801</v>
+        <v>7032037</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4028,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118557174</v>
+        <v>118552820</v>
       </c>
       <c r="B34" t="n">
-        <v>79469</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,38 +4022,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589654</v>
+        <v>589311</v>
       </c>
       <c r="R34" t="n">
-        <v>7031957</v>
+        <v>7031954</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4130,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118554223</v>
+        <v>118554168</v>
       </c>
       <c r="B35" t="n">
-        <v>90666</v>
+        <v>90476</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4142,25 +4133,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4170,10 +4161,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589368</v>
+        <v>589359</v>
       </c>
       <c r="R35" t="n">
-        <v>7031862</v>
+        <v>7031857</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4232,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118553087</v>
+        <v>118552007</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4248,34 +4239,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589202</v>
+        <v>589378</v>
       </c>
       <c r="R36" t="n">
-        <v>7031945</v>
+        <v>7032143</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4334,10 +4325,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118552278</v>
+        <v>118556365</v>
       </c>
       <c r="B37" t="n">
-        <v>90522</v>
+        <v>90511</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4350,21 +4341,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4374,10 +4365,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589280</v>
+        <v>589354</v>
       </c>
       <c r="R37" t="n">
-        <v>7031985</v>
+        <v>7031906</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4436,10 +4427,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118553615</v>
+        <v>118556986</v>
       </c>
       <c r="B38" t="n">
-        <v>79469</v>
+        <v>78491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4448,25 +4439,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4476,10 +4467,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589180</v>
+        <v>589680</v>
       </c>
       <c r="R38" t="n">
-        <v>7031880</v>
+        <v>7031886</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4538,10 +4529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118554171</v>
+        <v>118555906</v>
       </c>
       <c r="B39" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4554,34 +4545,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589359</v>
+        <v>589312</v>
       </c>
       <c r="R39" t="n">
-        <v>7031858</v>
+        <v>7031697</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4640,10 +4636,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118551431</v>
+        <v>118558184</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4652,25 +4648,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4680,10 +4676,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589557</v>
+        <v>589713</v>
       </c>
       <c r="R40" t="n">
-        <v>7032281</v>
+        <v>7032063</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4742,10 +4738,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118557448</v>
+        <v>118552657</v>
       </c>
       <c r="B41" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4754,38 +4750,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589632</v>
+        <v>589282</v>
       </c>
       <c r="R41" t="n">
-        <v>7032018</v>
+        <v>7031970</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118555355</v>
+        <v>118552853</v>
       </c>
       <c r="B42" t="n">
-        <v>90504</v>
+        <v>90476</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4856,25 +4856,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589463</v>
+        <v>589290</v>
       </c>
       <c r="R42" t="n">
-        <v>7031785</v>
+        <v>7031929</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4946,10 +4946,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118556574</v>
+        <v>118555355</v>
       </c>
       <c r="B43" t="n">
-        <v>90788</v>
+        <v>90511</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589407</v>
+        <v>589463</v>
       </c>
       <c r="R43" t="n">
-        <v>7031827</v>
+        <v>7031785</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5048,10 +5048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118552101</v>
+        <v>118555030</v>
       </c>
       <c r="B44" t="n">
-        <v>90469</v>
+        <v>90511</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5060,38 +5060,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589319</v>
+        <v>589414</v>
       </c>
       <c r="R44" t="n">
-        <v>7032043</v>
+        <v>7031799</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118555409</v>
+        <v>118557174</v>
       </c>
       <c r="B45" t="n">
-        <v>90847</v>
+        <v>79476</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5162,38 +5162,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589487</v>
+        <v>589654</v>
       </c>
       <c r="R45" t="n">
-        <v>7031784</v>
+        <v>7031957</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5252,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118552820</v>
+        <v>118557914</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5264,47 +5264,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589311</v>
+        <v>589694</v>
       </c>
       <c r="R46" t="n">
-        <v>7031954</v>
+        <v>7032099</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5363,10 +5354,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118554450</v>
+        <v>118553989</v>
       </c>
       <c r="B47" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5379,34 +5370,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589392</v>
+        <v>589352</v>
       </c>
       <c r="R47" t="n">
-        <v>7031860</v>
+        <v>7031849</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5465,10 +5461,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118552200</v>
+        <v>118552101</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>90476</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5477,47 +5473,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589314</v>
+        <v>589319</v>
       </c>
       <c r="R48" t="n">
-        <v>7032037</v>
+        <v>7032043</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5576,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118555906</v>
+        <v>118557229</v>
       </c>
       <c r="B49" t="n">
-        <v>57290</v>
+        <v>79476</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5588,43 +5575,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589312</v>
+        <v>589650</v>
       </c>
       <c r="R49" t="n">
-        <v>7031697</v>
+        <v>7031972</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5683,10 +5665,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118551796</v>
+        <v>118551947</v>
       </c>
       <c r="B50" t="n">
-        <v>90504</v>
+        <v>90476</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5695,25 +5677,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5723,10 +5705,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589417</v>
+        <v>589423</v>
       </c>
       <c r="R50" t="n">
-        <v>7032141</v>
+        <v>7032113</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5785,10 +5767,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118554028</v>
+        <v>118551880</v>
       </c>
       <c r="B51" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5821,14 +5803,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589341</v>
+        <v>589417</v>
       </c>
       <c r="R51" t="n">
-        <v>7031857</v>
+        <v>7032126</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5887,10 +5869,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118552350</v>
+        <v>118555302</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>90795</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5903,21 +5885,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5909,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589284</v>
+        <v>589472</v>
       </c>
       <c r="R52" t="n">
-        <v>7031972</v>
+        <v>7031796</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5989,10 +5971,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118556986</v>
+        <v>118557154</v>
       </c>
       <c r="B53" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6005,34 +5987,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589680</v>
+        <v>589647</v>
       </c>
       <c r="R53" t="n">
-        <v>7031886</v>
+        <v>7031952</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6091,10 +6073,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118551947</v>
+        <v>118551796</v>
       </c>
       <c r="B54" t="n">
-        <v>90469</v>
+        <v>90511</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6103,25 +6085,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6131,10 +6113,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589423</v>
+        <v>589417</v>
       </c>
       <c r="R54" t="n">
-        <v>7032113</v>
+        <v>7032141</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6193,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118554252</v>
+        <v>118551872</v>
       </c>
       <c r="B55" t="n">
-        <v>78484</v>
+        <v>90795</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6209,34 +6191,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589368</v>
+        <v>589417</v>
       </c>
       <c r="R55" t="n">
-        <v>7031862</v>
+        <v>7032126</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6295,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118552663</v>
+        <v>118554450</v>
       </c>
       <c r="B56" t="n">
-        <v>90469</v>
+        <v>90795</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6307,25 +6289,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6335,10 +6317,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589275</v>
+        <v>589392</v>
       </c>
       <c r="R56" t="n">
-        <v>7031984</v>
+        <v>7031860</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6397,10 +6379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118551885</v>
+        <v>118555622</v>
       </c>
       <c r="B57" t="n">
-        <v>90788</v>
+        <v>78491</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6413,34 +6395,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589410</v>
+        <v>589490</v>
       </c>
       <c r="R57" t="n">
-        <v>7032119</v>
+        <v>7031668</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6499,10 +6481,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118558184</v>
+        <v>118554223</v>
       </c>
       <c r="B58" t="n">
-        <v>97763</v>
+        <v>90673</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6511,38 +6493,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>1588</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589713</v>
+        <v>589368</v>
       </c>
       <c r="R58" t="n">
-        <v>7032063</v>
+        <v>7031862</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6601,10 +6583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118552378</v>
+        <v>118553087</v>
       </c>
       <c r="B59" t="n">
-        <v>90788</v>
+        <v>78491</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6617,21 +6599,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6641,10 +6623,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589267</v>
+        <v>589202</v>
       </c>
       <c r="R59" t="n">
-        <v>7031984</v>
+        <v>7031945</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6703,10 +6685,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118552694</v>
+        <v>118552498</v>
       </c>
       <c r="B60" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6715,38 +6697,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589282</v>
+        <v>589280</v>
       </c>
       <c r="R60" t="n">
-        <v>7031935</v>
+        <v>7031976</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6805,10 +6796,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118555302</v>
+        <v>118552163</v>
       </c>
       <c r="B61" t="n">
-        <v>90788</v>
+        <v>79601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6817,38 +6808,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589472</v>
+        <v>589309</v>
       </c>
       <c r="R61" t="n">
-        <v>7031796</v>
+        <v>7032040</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6907,10 +6898,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118557154</v>
+        <v>118552350</v>
       </c>
       <c r="B62" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6923,34 +6914,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589647</v>
+        <v>589284</v>
       </c>
       <c r="R62" t="n">
-        <v>7031952</v>
+        <v>7031972</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7009,10 +7000,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118557454</v>
+        <v>118554252</v>
       </c>
       <c r="B63" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7045,14 +7036,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589632</v>
+        <v>589368</v>
       </c>
       <c r="R63" t="n">
-        <v>7032019</v>
+        <v>7031862</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7111,10 +7102,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118557661</v>
+        <v>118551972</v>
       </c>
       <c r="B64" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7127,21 +7118,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7151,10 +7142,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589635</v>
+        <v>589404</v>
       </c>
       <c r="R64" t="n">
-        <v>7032058</v>
+        <v>7032115</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7213,10 +7204,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118555622</v>
+        <v>118556821</v>
       </c>
       <c r="B65" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7253,10 +7244,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589490</v>
+        <v>589651</v>
       </c>
       <c r="R65" t="n">
-        <v>7031668</v>
+        <v>7031856</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7315,10 +7306,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118552111</v>
+        <v>118554548</v>
       </c>
       <c r="B66" t="n">
-        <v>90504</v>
+        <v>90476</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7327,38 +7318,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589317</v>
+        <v>589348</v>
       </c>
       <c r="R66" t="n">
-        <v>7032040</v>
+        <v>7031858</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7417,10 +7408,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118554797</v>
+        <v>118554978</v>
       </c>
       <c r="B67" t="n">
-        <v>90504</v>
+        <v>90954</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7429,25 +7420,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7457,10 +7448,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589358</v>
+        <v>589414</v>
       </c>
       <c r="R67" t="n">
-        <v>7031830</v>
+        <v>7031799</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7519,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118554878</v>
+        <v>118555409</v>
       </c>
       <c r="B68" t="n">
-        <v>79525</v>
+        <v>90854</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7531,25 +7522,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>2062</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7559,10 +7550,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589437</v>
+        <v>589487</v>
       </c>
       <c r="R68" t="n">
-        <v>7031771</v>
+        <v>7031784</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7621,10 +7612,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118554822</v>
+        <v>118554028</v>
       </c>
       <c r="B69" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7633,25 +7624,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7661,10 +7652,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589399</v>
+        <v>589341</v>
       </c>
       <c r="R69" t="n">
-        <v>7031814</v>
+        <v>7031857</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7723,10 +7714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118552051</v>
+        <v>118552663</v>
       </c>
       <c r="B70" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7759,14 +7750,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589348</v>
+        <v>589275</v>
       </c>
       <c r="R70" t="n">
-        <v>7032078</v>
+        <v>7031984</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7825,10 +7816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118552163</v>
+        <v>118553615</v>
       </c>
       <c r="B71" t="n">
-        <v>79594</v>
+        <v>79476</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7841,34 +7832,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589309</v>
+        <v>589180</v>
       </c>
       <c r="R71" t="n">
-        <v>7032040</v>
+        <v>7031880</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7927,10 +7918,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118552219</v>
+        <v>118557940</v>
       </c>
       <c r="B72" t="n">
-        <v>90469</v>
+        <v>79572</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7939,38 +7930,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589268</v>
+        <v>589730</v>
       </c>
       <c r="R72" t="n">
-        <v>7031998</v>
+        <v>7032086</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8029,10 +8020,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118557253</v>
+        <v>118552748</v>
       </c>
       <c r="B73" t="n">
-        <v>58133</v>
+        <v>97853</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8041,38 +8032,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589648</v>
+        <v>589291</v>
       </c>
       <c r="R73" t="n">
-        <v>7031970</v>
+        <v>7031953</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8131,10 +8126,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118552992</v>
+        <v>118551676</v>
       </c>
       <c r="B74" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8167,14 +8162,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589298</v>
+        <v>589418</v>
       </c>
       <c r="R74" t="n">
-        <v>7031917</v>
+        <v>7032144</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8233,10 +8228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118553061</v>
+        <v>118554797</v>
       </c>
       <c r="B75" t="n">
-        <v>86820</v>
+        <v>90511</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8249,21 +8244,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8273,10 +8268,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589254</v>
+        <v>589358</v>
       </c>
       <c r="R75" t="n">
-        <v>7031953</v>
+        <v>7031830</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8335,10 +8330,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118554689</v>
+        <v>118557202</v>
       </c>
       <c r="B76" t="n">
-        <v>90469</v>
+        <v>79572</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8347,38 +8342,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589412</v>
+        <v>589643</v>
       </c>
       <c r="R76" t="n">
-        <v>7031811</v>
+        <v>7031980</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8437,10 +8432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118557229</v>
+        <v>118552278</v>
       </c>
       <c r="B77" t="n">
-        <v>79469</v>
+        <v>90529</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8449,38 +8444,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589650</v>
+        <v>589280</v>
       </c>
       <c r="R77" t="n">
-        <v>7031972</v>
+        <v>7031985</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8539,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118552007</v>
+        <v>118554171</v>
       </c>
       <c r="B78" t="n">
-        <v>90504</v>
+        <v>90529</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8555,34 +8550,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589378</v>
+        <v>589359</v>
       </c>
       <c r="R78" t="n">
-        <v>7032143</v>
+        <v>7031858</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8641,10 +8636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118552853</v>
+        <v>118552764</v>
       </c>
       <c r="B79" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8653,38 +8648,42 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589290</v>
+        <v>589297</v>
       </c>
       <c r="R79" t="n">
-        <v>7031929</v>
+        <v>7031952</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8743,10 +8742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118556821</v>
+        <v>118554878</v>
       </c>
       <c r="B80" t="n">
-        <v>78484</v>
+        <v>79532</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8755,25 +8754,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8783,10 +8782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589651</v>
+        <v>589437</v>
       </c>
       <c r="R80" t="n">
-        <v>7031856</v>
+        <v>7031771</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8845,10 +8844,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118552764</v>
+        <v>118555659</v>
       </c>
       <c r="B81" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8857,30 +8856,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589297</v>
+        <v>589466</v>
       </c>
       <c r="R81" t="n">
-        <v>7031952</v>
+        <v>7031640</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8951,10 +8951,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118591019</v>
+        <v>118590971</v>
       </c>
       <c r="B82" t="n">
-        <v>86820</v>
+        <v>82270</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8967,21 +8967,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8991,10 +8991,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589686</v>
+        <v>589691</v>
       </c>
       <c r="R82" t="n">
-        <v>7031880</v>
+        <v>7031862</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118587264</v>
+        <v>118587924</v>
       </c>
       <c r="B83" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9065,25 +9065,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589634</v>
+        <v>589445</v>
       </c>
       <c r="R83" t="n">
-        <v>7032061</v>
+        <v>7032073</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9155,10 +9155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118587632</v>
+        <v>118594452</v>
       </c>
       <c r="B84" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9167,38 +9167,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589517</v>
+        <v>589534</v>
       </c>
       <c r="R84" t="n">
-        <v>7032098</v>
+        <v>7031791</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118589486</v>
+        <v>118587967</v>
       </c>
       <c r="B85" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9269,25 +9269,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589657</v>
+        <v>589432</v>
       </c>
       <c r="R85" t="n">
-        <v>7031995</v>
+        <v>7032081</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118589338</v>
+        <v>118594447</v>
       </c>
       <c r="B86" t="n">
-        <v>79565</v>
+        <v>90854</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9371,38 +9371,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589593</v>
+        <v>589535</v>
       </c>
       <c r="R86" t="n">
-        <v>7032037</v>
+        <v>7031791</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118597023</v>
+        <v>118587799</v>
       </c>
       <c r="B87" t="n">
-        <v>57443</v>
+        <v>90511</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9477,38 +9477,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589517</v>
+        <v>589440</v>
       </c>
       <c r="R87" t="n">
-        <v>7031811</v>
+        <v>7032089</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9567,10 +9563,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118588515</v>
+        <v>118596031</v>
       </c>
       <c r="B88" t="n">
-        <v>90500</v>
+        <v>78491</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9583,34 +9579,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589417</v>
+        <v>589279</v>
       </c>
       <c r="R88" t="n">
-        <v>7032079</v>
+        <v>7031737</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9669,10 +9665,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118596031</v>
+        <v>118590215</v>
       </c>
       <c r="B89" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9685,34 +9681,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589279</v>
+        <v>589598</v>
       </c>
       <c r="R89" t="n">
-        <v>7031737</v>
+        <v>7031977</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9771,10 +9772,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118591032</v>
+        <v>118586696</v>
       </c>
       <c r="B90" t="n">
-        <v>90522</v>
+        <v>97770</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9783,38 +9784,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589690</v>
+        <v>589736</v>
       </c>
       <c r="R90" t="n">
-        <v>7031882</v>
+        <v>7032064</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9873,10 +9874,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118586687</v>
+        <v>118590296</v>
       </c>
       <c r="B91" t="n">
-        <v>90522</v>
+        <v>97853</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9885,38 +9886,47 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589736</v>
+        <v>589588</v>
       </c>
       <c r="R91" t="n">
-        <v>7032057</v>
+        <v>7032008</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9975,10 +9985,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118597248</v>
+        <v>118597023</v>
       </c>
       <c r="B92" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9991,39 +10001,38 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589494</v>
+        <v>589517</v>
       </c>
       <c r="R92" t="n">
-        <v>7031972</v>
+        <v>7031811</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10082,10 +10091,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118587499</v>
+        <v>118596461</v>
       </c>
       <c r="B93" t="n">
-        <v>90522</v>
+        <v>97853</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10094,38 +10103,47 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589524</v>
+        <v>589343</v>
       </c>
       <c r="R93" t="n">
-        <v>7032087</v>
+        <v>7031883</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10184,10 +10202,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118597134</v>
+        <v>118587901</v>
       </c>
       <c r="B94" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10200,34 +10218,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589508</v>
+        <v>589438</v>
       </c>
       <c r="R94" t="n">
-        <v>7031905</v>
+        <v>7032058</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10286,10 +10304,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118587799</v>
+        <v>118587264</v>
       </c>
       <c r="B95" t="n">
-        <v>90504</v>
+        <v>78491</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10302,21 +10320,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10326,10 +10344,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589440</v>
+        <v>589634</v>
       </c>
       <c r="R95" t="n">
-        <v>7032089</v>
+        <v>7032061</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10388,10 +10406,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118588534</v>
+        <v>118589906</v>
       </c>
       <c r="B96" t="n">
-        <v>90469</v>
+        <v>79572</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10400,25 +10418,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10428,10 +10446,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589413</v>
+        <v>589676</v>
       </c>
       <c r="R96" t="n">
-        <v>7032084</v>
+        <v>7031963</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10490,10 +10508,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118590296</v>
+        <v>118591032</v>
       </c>
       <c r="B97" t="n">
-        <v>97846</v>
+        <v>90529</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10502,47 +10520,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589588</v>
+        <v>589690</v>
       </c>
       <c r="R97" t="n">
-        <v>7032008</v>
+        <v>7031882</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10601,10 +10610,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118590334</v>
+        <v>118586687</v>
       </c>
       <c r="B98" t="n">
-        <v>97846</v>
+        <v>90529</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10613,42 +10622,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589578</v>
+        <v>589736</v>
       </c>
       <c r="R98" t="n">
-        <v>7032004</v>
+        <v>7032057</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10707,10 +10712,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118596822</v>
+        <v>118594407</v>
       </c>
       <c r="B99" t="n">
-        <v>90788</v>
+        <v>57306</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10723,34 +10728,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589457</v>
+        <v>589525</v>
       </c>
       <c r="R99" t="n">
-        <v>7031787</v>
+        <v>7031796</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10809,10 +10819,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118589906</v>
+        <v>118587632</v>
       </c>
       <c r="B100" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10825,21 +10835,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10849,10 +10859,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589676</v>
+        <v>589517</v>
       </c>
       <c r="R100" t="n">
-        <v>7031963</v>
+        <v>7032098</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10911,10 +10921,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118594452</v>
+        <v>118587754</v>
       </c>
       <c r="B101" t="n">
-        <v>90469</v>
+        <v>90525</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10923,38 +10933,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589534</v>
+        <v>589443</v>
       </c>
       <c r="R101" t="n">
-        <v>7031791</v>
+        <v>7032086</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11013,10 +11023,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118590681</v>
+        <v>118589537</v>
       </c>
       <c r="B102" t="n">
-        <v>90469</v>
+        <v>86827</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11025,38 +11035,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589668</v>
+        <v>589709</v>
       </c>
       <c r="R102" t="n">
-        <v>7031892</v>
+        <v>7031980</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11115,10 +11125,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118586448</v>
+        <v>118590681</v>
       </c>
       <c r="B103" t="n">
-        <v>97846</v>
+        <v>90476</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11127,42 +11137,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589786</v>
+        <v>589668</v>
       </c>
       <c r="R103" t="n">
-        <v>7032053</v>
+        <v>7031892</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11221,10 +11227,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118587773</v>
+        <v>118597176</v>
       </c>
       <c r="B104" t="n">
-        <v>90469</v>
+        <v>97770</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11237,34 +11243,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589442</v>
+        <v>589501</v>
       </c>
       <c r="R104" t="n">
-        <v>7032089</v>
+        <v>7031949</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11323,10 +11329,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118594407</v>
+        <v>118590334</v>
       </c>
       <c r="B105" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11335,43 +11341,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589525</v>
+        <v>589578</v>
       </c>
       <c r="R105" t="n">
-        <v>7031796</v>
+        <v>7032004</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11430,10 +11435,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118597176</v>
+        <v>118596677</v>
       </c>
       <c r="B106" t="n">
-        <v>97763</v>
+        <v>97853</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11442,38 +11447,42 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589501</v>
+        <v>589425</v>
       </c>
       <c r="R106" t="n">
-        <v>7031949</v>
+        <v>7031806</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11532,10 +11541,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118587872</v>
+        <v>118588534</v>
       </c>
       <c r="B107" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11572,10 +11581,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589438</v>
+        <v>589413</v>
       </c>
       <c r="R107" t="n">
-        <v>7032059</v>
+        <v>7032084</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11634,10 +11643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118590971</v>
+        <v>118587872</v>
       </c>
       <c r="B108" t="n">
-        <v>82263</v>
+        <v>90476</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11646,38 +11655,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>589691</v>
+        <v>589438</v>
       </c>
       <c r="R108" t="n">
-        <v>7031862</v>
+        <v>7032059</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11736,10 +11745,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118589400</v>
+        <v>118591019</v>
       </c>
       <c r="B109" t="n">
-        <v>90522</v>
+        <v>86827</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11752,34 +11761,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>589614</v>
+        <v>589686</v>
       </c>
       <c r="R109" t="n">
-        <v>7032054</v>
+        <v>7031880</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11838,10 +11847,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118596677</v>
+        <v>118587499</v>
       </c>
       <c r="B110" t="n">
-        <v>97846</v>
+        <v>90529</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11850,42 +11859,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589425</v>
+        <v>589524</v>
       </c>
       <c r="R110" t="n">
-        <v>7031806</v>
+        <v>7032087</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11944,10 +11949,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118594520</v>
+        <v>118589400</v>
       </c>
       <c r="B111" t="n">
-        <v>97846</v>
+        <v>90529</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11956,47 +11961,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589534</v>
+        <v>589614</v>
       </c>
       <c r="R111" t="n">
-        <v>7031764</v>
+        <v>7032054</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12055,10 +12051,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118589093</v>
+        <v>118586448</v>
       </c>
       <c r="B112" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12067,31 +12063,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12100,10 +12095,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>589495</v>
+        <v>589786</v>
       </c>
       <c r="R112" t="n">
-        <v>7031990</v>
+        <v>7032053</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12162,10 +12157,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118589537</v>
+        <v>118589486</v>
       </c>
       <c r="B113" t="n">
-        <v>86820</v>
+        <v>78491</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12178,21 +12173,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12202,10 +12197,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589709</v>
+        <v>589657</v>
       </c>
       <c r="R113" t="n">
-        <v>7031980</v>
+        <v>7031995</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12264,10 +12259,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118587754</v>
+        <v>118587667</v>
       </c>
       <c r="B114" t="n">
-        <v>90518</v>
+        <v>90476</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12276,25 +12271,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12304,10 +12299,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589443</v>
+        <v>589455</v>
       </c>
       <c r="R114" t="n">
-        <v>7032086</v>
+        <v>7032096</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12366,10 +12361,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118587901</v>
+        <v>118588420</v>
       </c>
       <c r="B115" t="n">
-        <v>90504</v>
+        <v>90795</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12382,21 +12377,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12406,10 +12401,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589438</v>
+        <v>589421</v>
       </c>
       <c r="R115" t="n">
-        <v>7032058</v>
+        <v>7032124</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12468,10 +12463,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118587924</v>
+        <v>118588515</v>
       </c>
       <c r="B116" t="n">
-        <v>90469</v>
+        <v>90507</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12480,25 +12475,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12508,10 +12503,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>589445</v>
+        <v>589417</v>
       </c>
       <c r="R116" t="n">
-        <v>7032073</v>
+        <v>7032079</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12570,10 +12565,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118590255</v>
+        <v>118589613</v>
       </c>
       <c r="B117" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12582,38 +12577,42 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589607</v>
+        <v>589740</v>
       </c>
       <c r="R117" t="n">
-        <v>7032009</v>
+        <v>7032026</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12672,10 +12671,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118589036</v>
+        <v>118589918</v>
       </c>
       <c r="B118" t="n">
-        <v>90469</v>
+        <v>79476</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12688,21 +12687,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12712,10 +12711,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589506</v>
+        <v>589675</v>
       </c>
       <c r="R118" t="n">
-        <v>7031977</v>
+        <v>7031964</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12774,10 +12773,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118589613</v>
+        <v>118597134</v>
       </c>
       <c r="B119" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12786,42 +12785,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589740</v>
+        <v>589508</v>
       </c>
       <c r="R119" t="n">
-        <v>7032026</v>
+        <v>7031905</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12880,10 +12875,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118588420</v>
+        <v>118588128</v>
       </c>
       <c r="B120" t="n">
-        <v>90788</v>
+        <v>90476</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12892,25 +12887,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12920,10 +12915,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589421</v>
+        <v>589428</v>
       </c>
       <c r="R120" t="n">
-        <v>7032124</v>
+        <v>7032108</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -12982,10 +12977,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118586696</v>
+        <v>118587773</v>
       </c>
       <c r="B121" t="n">
-        <v>97763</v>
+        <v>90476</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12998,21 +12993,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13022,10 +13017,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>589736</v>
+        <v>589442</v>
       </c>
       <c r="R121" t="n">
-        <v>7032064</v>
+        <v>7032089</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13084,10 +13079,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118596461</v>
+        <v>118597248</v>
       </c>
       <c r="B122" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13096,47 +13091,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>589343</v>
+        <v>589494</v>
       </c>
       <c r="R122" t="n">
-        <v>7031883</v>
+        <v>7031972</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13195,10 +13186,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118596564</v>
+        <v>118594520</v>
       </c>
       <c r="B123" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13230,7 +13221,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -13244,10 +13235,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589368</v>
+        <v>589534</v>
       </c>
       <c r="R123" t="n">
-        <v>7031833</v>
+        <v>7031764</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13306,10 +13297,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118589918</v>
+        <v>118589338</v>
       </c>
       <c r="B124" t="n">
-        <v>79469</v>
+        <v>79572</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13318,25 +13309,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13346,10 +13337,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589675</v>
+        <v>589593</v>
       </c>
       <c r="R124" t="n">
-        <v>7031964</v>
+        <v>7032037</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13408,10 +13399,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118587967</v>
+        <v>118592076</v>
       </c>
       <c r="B125" t="n">
-        <v>90469</v>
+        <v>56494</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13420,38 +13411,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589432</v>
+        <v>589665</v>
       </c>
       <c r="R125" t="n">
-        <v>7032081</v>
+        <v>7031798</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13510,10 +13506,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118592076</v>
+        <v>118589036</v>
       </c>
       <c r="B126" t="n">
-        <v>56494</v>
+        <v>90476</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13522,43 +13518,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589665</v>
+        <v>589506</v>
       </c>
       <c r="R126" t="n">
-        <v>7031798</v>
+        <v>7031977</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13617,10 +13608,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118588485</v>
+        <v>118589093</v>
       </c>
       <c r="B127" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13633,34 +13624,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>589403</v>
+        <v>589495</v>
       </c>
       <c r="R127" t="n">
-        <v>7032119</v>
+        <v>7031990</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13719,10 +13715,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118590215</v>
+        <v>118596822</v>
       </c>
       <c r="B128" t="n">
-        <v>57306</v>
+        <v>90795</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13735,39 +13731,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>589598</v>
+        <v>589457</v>
       </c>
       <c r="R128" t="n">
-        <v>7031977</v>
+        <v>7031787</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13826,10 +13817,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118587667</v>
+        <v>118596564</v>
       </c>
       <c r="B129" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13838,38 +13829,47 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589455</v>
+        <v>589368</v>
       </c>
       <c r="R129" t="n">
-        <v>7032096</v>
+        <v>7031833</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -13928,10 +13928,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118594447</v>
+        <v>118590255</v>
       </c>
       <c r="B130" t="n">
-        <v>90847</v>
+        <v>79572</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13940,38 +13940,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>589535</v>
+        <v>589607</v>
       </c>
       <c r="R130" t="n">
-        <v>7031791</v>
+        <v>7032009</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14030,10 +14030,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118588128</v>
+        <v>118588485</v>
       </c>
       <c r="B131" t="n">
-        <v>90469</v>
+        <v>90795</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14042,25 +14042,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>589428</v>
+        <v>589403</v>
       </c>
       <c r="R131" t="n">
-        <v>7032108</v>
+        <v>7032119</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -3695,10 +3695,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118552378</v>
+        <v>118554168</v>
       </c>
       <c r="B31" t="n">
-        <v>90795</v>
+        <v>90476</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3707,25 +3707,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589267</v>
+        <v>589359</v>
       </c>
       <c r="R31" t="n">
-        <v>7031984</v>
+        <v>7031857</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118556574</v>
+        <v>118552378</v>
       </c>
       <c r="B32" t="n">
         <v>90795</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589407</v>
+        <v>589267</v>
       </c>
       <c r="R32" t="n">
-        <v>7031827</v>
+        <v>7031984</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118552200</v>
+        <v>118556574</v>
       </c>
       <c r="B33" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3911,47 +3911,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589314</v>
+        <v>589407</v>
       </c>
       <c r="R33" t="n">
-        <v>7032037</v>
+        <v>7031827</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4010,7 +4001,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118552820</v>
+        <v>118552200</v>
       </c>
       <c r="B34" t="n">
         <v>97853</v>
@@ -4045,7 +4036,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4055,14 +4046,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589311</v>
+        <v>589314</v>
       </c>
       <c r="R34" t="n">
-        <v>7031954</v>
+        <v>7032037</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4121,10 +4112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118554168</v>
+        <v>118552820</v>
       </c>
       <c r="B35" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4133,38 +4124,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589359</v>
+        <v>589311</v>
       </c>
       <c r="R35" t="n">
-        <v>7031857</v>
+        <v>7031954</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -5767,10 +5767,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118551880</v>
+        <v>118557154</v>
       </c>
       <c r="B51" t="n">
-        <v>90476</v>
+        <v>79572</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5779,25 +5779,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589417</v>
+        <v>589647</v>
       </c>
       <c r="R51" t="n">
-        <v>7032126</v>
+        <v>7031952</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118555302</v>
+        <v>118551880</v>
       </c>
       <c r="B52" t="n">
-        <v>90795</v>
+        <v>90476</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5881,38 +5881,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589472</v>
+        <v>589417</v>
       </c>
       <c r="R52" t="n">
-        <v>7031796</v>
+        <v>7032126</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5971,10 +5971,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118557154</v>
+        <v>118555302</v>
       </c>
       <c r="B53" t="n">
-        <v>79572</v>
+        <v>90795</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5987,34 +5987,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589647</v>
+        <v>589472</v>
       </c>
       <c r="R53" t="n">
-        <v>7031952</v>
+        <v>7031796</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6073,10 +6073,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118551796</v>
+        <v>118554223</v>
       </c>
       <c r="B54" t="n">
-        <v>90511</v>
+        <v>90673</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6089,34 +6089,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589417</v>
+        <v>589368</v>
       </c>
       <c r="R54" t="n">
-        <v>7032141</v>
+        <v>7031862</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118551872</v>
+        <v>118555622</v>
       </c>
       <c r="B55" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6191,34 +6191,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589417</v>
+        <v>589490</v>
       </c>
       <c r="R55" t="n">
-        <v>7032126</v>
+        <v>7031668</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118554450</v>
+        <v>118551796</v>
       </c>
       <c r="B56" t="n">
-        <v>90795</v>
+        <v>90511</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6293,34 +6293,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589392</v>
+        <v>589417</v>
       </c>
       <c r="R56" t="n">
-        <v>7031860</v>
+        <v>7032141</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6379,10 +6379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118555622</v>
+        <v>118551872</v>
       </c>
       <c r="B57" t="n">
-        <v>78491</v>
+        <v>90795</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6395,34 +6395,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589490</v>
+        <v>589417</v>
       </c>
       <c r="R57" t="n">
-        <v>7031668</v>
+        <v>7032126</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6481,10 +6481,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118554223</v>
+        <v>118554450</v>
       </c>
       <c r="B58" t="n">
-        <v>90673</v>
+        <v>90795</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589368</v>
+        <v>589392</v>
       </c>
       <c r="R58" t="n">
-        <v>7031862</v>
+        <v>7031860</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6583,10 +6583,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118553087</v>
+        <v>118552498</v>
       </c>
       <c r="B59" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6595,38 +6595,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589202</v>
+        <v>589280</v>
       </c>
       <c r="R59" t="n">
-        <v>7031945</v>
+        <v>7031976</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6685,10 +6694,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118552498</v>
+        <v>118553087</v>
       </c>
       <c r="B60" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6697,47 +6706,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589280</v>
+        <v>589202</v>
       </c>
       <c r="R60" t="n">
-        <v>7031976</v>
+        <v>7031945</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7714,10 +7714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118552663</v>
+        <v>118552748</v>
       </c>
       <c r="B70" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,38 +7726,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589275</v>
+        <v>589291</v>
       </c>
       <c r="R70" t="n">
-        <v>7031984</v>
+        <v>7031953</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8020,10 +8024,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118552748</v>
+        <v>118552663</v>
       </c>
       <c r="B73" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8032,42 +8036,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589291</v>
+        <v>589275</v>
       </c>
       <c r="R73" t="n">
-        <v>7031953</v>
+        <v>7031984</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8126,10 +8126,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118551676</v>
+        <v>118552764</v>
       </c>
       <c r="B74" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8138,38 +8138,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589418</v>
+        <v>589297</v>
       </c>
       <c r="R74" t="n">
-        <v>7032144</v>
+        <v>7031952</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8228,10 +8232,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118554797</v>
+        <v>118554878</v>
       </c>
       <c r="B75" t="n">
-        <v>90511</v>
+        <v>79532</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8240,25 +8244,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8268,10 +8272,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589358</v>
+        <v>589437</v>
       </c>
       <c r="R75" t="n">
-        <v>7031830</v>
+        <v>7031771</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8330,10 +8334,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118557202</v>
+        <v>118554171</v>
       </c>
       <c r="B76" t="n">
-        <v>79572</v>
+        <v>90529</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8346,34 +8350,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589643</v>
+        <v>589359</v>
       </c>
       <c r="R76" t="n">
-        <v>7031980</v>
+        <v>7031858</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8534,10 +8538,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118554171</v>
+        <v>118555659</v>
       </c>
       <c r="B78" t="n">
-        <v>90529</v>
+        <v>57306</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8550,34 +8554,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589359</v>
+        <v>589466</v>
       </c>
       <c r="R78" t="n">
-        <v>7031858</v>
+        <v>7031640</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8636,10 +8645,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118552764</v>
+        <v>118551676</v>
       </c>
       <c r="B79" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8648,42 +8657,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589297</v>
+        <v>589418</v>
       </c>
       <c r="R79" t="n">
-        <v>7031952</v>
+        <v>7032144</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8742,10 +8747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118554878</v>
+        <v>118554797</v>
       </c>
       <c r="B80" t="n">
-        <v>79532</v>
+        <v>90511</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8754,25 +8759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8782,10 +8787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589437</v>
+        <v>589358</v>
       </c>
       <c r="R80" t="n">
-        <v>7031771</v>
+        <v>7031830</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8844,10 +8849,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118555659</v>
+        <v>118557202</v>
       </c>
       <c r="B81" t="n">
-        <v>57306</v>
+        <v>79572</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8860,39 +8865,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589466</v>
+        <v>589643</v>
       </c>
       <c r="R81" t="n">
-        <v>7031640</v>
+        <v>7031980</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -11023,10 +11023,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118589537</v>
+        <v>118590681</v>
       </c>
       <c r="B102" t="n">
-        <v>86827</v>
+        <v>90476</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11035,38 +11035,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589709</v>
+        <v>589668</v>
       </c>
       <c r="R102" t="n">
-        <v>7031980</v>
+        <v>7031892</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11125,10 +11125,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118590681</v>
+        <v>118589537</v>
       </c>
       <c r="B103" t="n">
-        <v>90476</v>
+        <v>86827</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11137,38 +11137,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589668</v>
+        <v>589709</v>
       </c>
       <c r="R103" t="n">
-        <v>7031892</v>
+        <v>7031980</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11227,10 +11227,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118597176</v>
+        <v>118590334</v>
       </c>
       <c r="B104" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11239,38 +11239,42 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589501</v>
+        <v>589578</v>
       </c>
       <c r="R104" t="n">
-        <v>7031949</v>
+        <v>7032004</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11329,10 +11333,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118590334</v>
+        <v>118597176</v>
       </c>
       <c r="B105" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11341,42 +11345,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589578</v>
+        <v>589501</v>
       </c>
       <c r="R105" t="n">
-        <v>7032004</v>
+        <v>7031949</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118596677</v>
+        <v>118588534</v>
       </c>
       <c r="B106" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11447,42 +11447,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589425</v>
+        <v>589413</v>
       </c>
       <c r="R106" t="n">
-        <v>7031806</v>
+        <v>7032084</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11541,7 +11537,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118588534</v>
+        <v>118587872</v>
       </c>
       <c r="B107" t="n">
         <v>90476</v>
@@ -11581,10 +11577,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589413</v>
+        <v>589438</v>
       </c>
       <c r="R107" t="n">
-        <v>7032084</v>
+        <v>7032059</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11643,10 +11639,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118587872</v>
+        <v>118596677</v>
       </c>
       <c r="B108" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11655,38 +11651,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>589438</v>
+        <v>589425</v>
       </c>
       <c r="R108" t="n">
-        <v>7032059</v>
+        <v>7031806</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11745,10 +11745,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118591019</v>
+        <v>118587499</v>
       </c>
       <c r="B109" t="n">
-        <v>86827</v>
+        <v>90529</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11761,34 +11761,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>589686</v>
+        <v>589524</v>
       </c>
       <c r="R109" t="n">
-        <v>7031880</v>
+        <v>7032087</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11847,7 +11847,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118587499</v>
+        <v>118589400</v>
       </c>
       <c r="B110" t="n">
         <v>90529</v>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589524</v>
+        <v>589614</v>
       </c>
       <c r="R110" t="n">
-        <v>7032087</v>
+        <v>7032054</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11949,10 +11949,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118589400</v>
+        <v>118591019</v>
       </c>
       <c r="B111" t="n">
-        <v>90529</v>
+        <v>86827</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11965,34 +11965,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589614</v>
+        <v>589686</v>
       </c>
       <c r="R111" t="n">
-        <v>7032054</v>
+        <v>7031880</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118589486</v>
+        <v>118587667</v>
       </c>
       <c r="B113" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12169,25 +12169,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589657</v>
+        <v>589455</v>
       </c>
       <c r="R113" t="n">
-        <v>7031995</v>
+        <v>7032096</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118587667</v>
+        <v>118588420</v>
       </c>
       <c r="B114" t="n">
-        <v>90476</v>
+        <v>90795</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12271,25 +12271,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589455</v>
+        <v>589421</v>
       </c>
       <c r="R114" t="n">
-        <v>7032096</v>
+        <v>7032124</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12361,10 +12361,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118588420</v>
+        <v>118588515</v>
       </c>
       <c r="B115" t="n">
-        <v>90795</v>
+        <v>90507</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12377,21 +12377,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589421</v>
+        <v>589417</v>
       </c>
       <c r="R115" t="n">
-        <v>7032124</v>
+        <v>7032079</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12463,10 +12463,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118588515</v>
+        <v>118589486</v>
       </c>
       <c r="B116" t="n">
-        <v>90507</v>
+        <v>78491</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12479,21 +12479,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12503,10 +12503,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>589417</v>
+        <v>589657</v>
       </c>
       <c r="R116" t="n">
-        <v>7032079</v>
+        <v>7031995</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12565,10 +12565,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118589613</v>
+        <v>118588128</v>
       </c>
       <c r="B117" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12577,42 +12577,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589740</v>
+        <v>589428</v>
       </c>
       <c r="R117" t="n">
-        <v>7032026</v>
+        <v>7032108</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12671,10 +12667,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118589918</v>
+        <v>118589613</v>
       </c>
       <c r="B118" t="n">
-        <v>79476</v>
+        <v>97853</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12683,38 +12679,42 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589675</v>
+        <v>589740</v>
       </c>
       <c r="R118" t="n">
-        <v>7031964</v>
+        <v>7032026</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12773,10 +12773,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118597134</v>
+        <v>118589918</v>
       </c>
       <c r="B119" t="n">
-        <v>78491</v>
+        <v>79476</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12785,38 +12785,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589508</v>
+        <v>589675</v>
       </c>
       <c r="R119" t="n">
-        <v>7031905</v>
+        <v>7031964</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12875,10 +12875,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118588128</v>
+        <v>118597134</v>
       </c>
       <c r="B120" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12887,38 +12887,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589428</v>
+        <v>589508</v>
       </c>
       <c r="R120" t="n">
-        <v>7032108</v>
+        <v>7031905</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -13399,10 +13399,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118592076</v>
+        <v>118589093</v>
       </c>
       <c r="B125" t="n">
-        <v>56494</v>
+        <v>57290</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13415,16 +13415,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -13435,19 +13435,19 @@
       <c r="I125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589665</v>
+        <v>589495</v>
       </c>
       <c r="R125" t="n">
-        <v>7031798</v>
+        <v>7031990</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13506,10 +13506,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118589036</v>
+        <v>118592076</v>
       </c>
       <c r="B126" t="n">
-        <v>90476</v>
+        <v>56494</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13518,38 +13518,43 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589506</v>
+        <v>589665</v>
       </c>
       <c r="R126" t="n">
-        <v>7031977</v>
+        <v>7031798</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13608,10 +13613,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118589093</v>
+        <v>118589036</v>
       </c>
       <c r="B127" t="n">
-        <v>57290</v>
+        <v>90476</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13620,43 +13625,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>589495</v>
+        <v>589506</v>
       </c>
       <c r="R127" t="n">
-        <v>7031990</v>
+        <v>7031977</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13817,10 +13817,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118596564</v>
+        <v>118588485</v>
       </c>
       <c r="B129" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13829,47 +13829,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589368</v>
+        <v>589403</v>
       </c>
       <c r="R129" t="n">
-        <v>7031833</v>
+        <v>7032119</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -14030,10 +14021,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118588485</v>
+        <v>118596564</v>
       </c>
       <c r="B131" t="n">
-        <v>90795</v>
+        <v>97853</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14042,38 +14033,47 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>589403</v>
+        <v>589368</v>
       </c>
       <c r="R131" t="n">
-        <v>7032119</v>
+        <v>7031833</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118552992</v>
+        <v>118554978</v>
       </c>
       <c r="B4" t="n">
-        <v>90511</v>
+        <v>90954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589298</v>
+        <v>589414</v>
       </c>
       <c r="R4" t="n">
-        <v>7031917</v>
+        <v>7031799</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118552111</v>
+        <v>118557229</v>
       </c>
       <c r="B5" t="n">
-        <v>90511</v>
+        <v>79476</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589317</v>
+        <v>589650</v>
       </c>
       <c r="R5" t="n">
-        <v>7032040</v>
+        <v>7031972</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118555445</v>
+        <v>118554252</v>
       </c>
       <c r="B6" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589487</v>
+        <v>589368</v>
       </c>
       <c r="R6" t="n">
-        <v>7031784</v>
+        <v>7031862</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118552219</v>
+        <v>118553989</v>
       </c>
       <c r="B7" t="n">
-        <v>90476</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,38 +1237,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589268</v>
+        <v>589352</v>
       </c>
       <c r="R7" t="n">
-        <v>7031998</v>
+        <v>7031849</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1327,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118557448</v>
+        <v>118552007</v>
       </c>
       <c r="B8" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589632</v>
+        <v>589378</v>
       </c>
       <c r="R8" t="n">
-        <v>7032018</v>
+        <v>7032143</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118552985</v>
+        <v>118552663</v>
       </c>
       <c r="B9" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,42 +1446,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589293</v>
+        <v>589275</v>
       </c>
       <c r="R9" t="n">
-        <v>7031918</v>
+        <v>7031984</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118552802</v>
+        <v>118557448</v>
       </c>
       <c r="B10" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,47 +1548,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589313</v>
+        <v>589632</v>
       </c>
       <c r="R10" t="n">
-        <v>7031955</v>
+        <v>7032018</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118552694</v>
+        <v>118552200</v>
       </c>
       <c r="B11" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,38 +1650,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589282</v>
+        <v>589314</v>
       </c>
       <c r="R11" t="n">
-        <v>7031935</v>
+        <v>7032037</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1748,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118557661</v>
+        <v>118555355</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,34 +1765,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589635</v>
+        <v>589463</v>
       </c>
       <c r="R12" t="n">
-        <v>7032058</v>
+        <v>7031785</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1850,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118551771</v>
+        <v>118554184</v>
       </c>
       <c r="B13" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,38 +1863,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589423</v>
+        <v>589360</v>
       </c>
       <c r="R13" t="n">
-        <v>7032117</v>
+        <v>7031856</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1952,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118556301</v>
+        <v>118554223</v>
       </c>
       <c r="B14" t="n">
-        <v>78491</v>
+        <v>90673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1969,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589298</v>
+        <v>589368</v>
       </c>
       <c r="R14" t="n">
-        <v>7031829</v>
+        <v>7031862</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2054,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118556472</v>
+        <v>118556301</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2067,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589408</v>
+        <v>589298</v>
       </c>
       <c r="R15" t="n">
-        <v>7031876</v>
+        <v>7031829</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2156,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118553096</v>
+        <v>118552853</v>
       </c>
       <c r="B16" t="n">
-        <v>82270</v>
+        <v>90476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,25 +2169,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589204</v>
+        <v>589290</v>
       </c>
       <c r="R16" t="n">
-        <v>7031942</v>
+        <v>7031929</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2258,10 +2259,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118554184</v>
+        <v>118553061</v>
       </c>
       <c r="B17" t="n">
-        <v>90511</v>
+        <v>86827</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2298,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589360</v>
+        <v>589254</v>
       </c>
       <c r="R17" t="n">
-        <v>7031856</v>
+        <v>7031953</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2360,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118557454</v>
+        <v>118552764</v>
       </c>
       <c r="B18" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,38 +2373,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589632</v>
+        <v>589297</v>
       </c>
       <c r="R18" t="n">
-        <v>7032019</v>
+        <v>7031952</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2462,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118551431</v>
+        <v>118552820</v>
       </c>
       <c r="B19" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,38 +2479,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589557</v>
+        <v>589311</v>
       </c>
       <c r="R19" t="n">
-        <v>7032281</v>
+        <v>7031954</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2564,10 +2578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118551992</v>
+        <v>118557253</v>
       </c>
       <c r="B20" t="n">
-        <v>90476</v>
+        <v>58133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589373</v>
+        <v>589648</v>
       </c>
       <c r="R20" t="n">
-        <v>7032142</v>
+        <v>7031970</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2666,7 +2680,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118552051</v>
+        <v>118551992</v>
       </c>
       <c r="B21" t="n">
         <v>90476</v>
@@ -2706,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589348</v>
+        <v>589373</v>
       </c>
       <c r="R21" t="n">
-        <v>7032078</v>
+        <v>7032142</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2768,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118554910</v>
+        <v>118552031</v>
       </c>
       <c r="B22" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2784,34 +2798,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589428</v>
+        <v>589360</v>
       </c>
       <c r="R22" t="n">
-        <v>7031801</v>
+        <v>7032085</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2870,10 +2884,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118552031</v>
+        <v>118551972</v>
       </c>
       <c r="B23" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2886,21 +2900,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2910,10 +2924,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589360</v>
+        <v>589404</v>
       </c>
       <c r="R23" t="n">
-        <v>7032085</v>
+        <v>7032115</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2972,10 +2986,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118554822</v>
+        <v>118551796</v>
       </c>
       <c r="B24" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,34 +3002,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589399</v>
+        <v>589417</v>
       </c>
       <c r="R24" t="n">
-        <v>7031814</v>
+        <v>7032141</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3074,10 +3088,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118557253</v>
+        <v>118552051</v>
       </c>
       <c r="B25" t="n">
-        <v>58133</v>
+        <v>90476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,21 +3104,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208249</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589648</v>
+        <v>589348</v>
       </c>
       <c r="R25" t="n">
-        <v>7031970</v>
+        <v>7032078</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3176,10 +3190,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118557265</v>
+        <v>118556472</v>
       </c>
       <c r="B26" t="n">
-        <v>97853</v>
+        <v>79476</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3188,47 +3202,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589642</v>
+        <v>589408</v>
       </c>
       <c r="R26" t="n">
-        <v>7031970</v>
+        <v>7031876</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3287,10 +3292,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118551885</v>
+        <v>118557174</v>
       </c>
       <c r="B27" t="n">
-        <v>90795</v>
+        <v>79476</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3299,25 +3304,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3327,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589410</v>
+        <v>589654</v>
       </c>
       <c r="R27" t="n">
-        <v>7032119</v>
+        <v>7031957</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3389,10 +3394,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118555468</v>
+        <v>118551880</v>
       </c>
       <c r="B28" t="n">
-        <v>90511</v>
+        <v>90476</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3401,38 +3406,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589488</v>
+        <v>589417</v>
       </c>
       <c r="R28" t="n">
-        <v>7031771</v>
+        <v>7032126</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3491,10 +3496,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118553061</v>
+        <v>118551947</v>
       </c>
       <c r="B29" t="n">
-        <v>86827</v>
+        <v>90476</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3503,38 +3508,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589254</v>
+        <v>589423</v>
       </c>
       <c r="R29" t="n">
-        <v>7031953</v>
+        <v>7032113</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3593,10 +3598,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118554689</v>
+        <v>118556986</v>
       </c>
       <c r="B30" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3605,25 +3610,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3633,10 +3638,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589412</v>
+        <v>589680</v>
       </c>
       <c r="R30" t="n">
-        <v>7031811</v>
+        <v>7031886</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3695,10 +3700,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118554168</v>
+        <v>118558184</v>
       </c>
       <c r="B31" t="n">
-        <v>90476</v>
+        <v>97770</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3711,34 +3716,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589359</v>
+        <v>589713</v>
       </c>
       <c r="R31" t="n">
-        <v>7031857</v>
+        <v>7032063</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3797,10 +3802,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118552378</v>
+        <v>118553087</v>
       </c>
       <c r="B32" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3813,21 +3818,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3837,10 +3842,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589267</v>
+        <v>589202</v>
       </c>
       <c r="R32" t="n">
-        <v>7031984</v>
+        <v>7031945</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3899,10 +3904,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118556574</v>
+        <v>118552163</v>
       </c>
       <c r="B33" t="n">
-        <v>90795</v>
+        <v>79601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3911,38 +3916,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589407</v>
+        <v>589309</v>
       </c>
       <c r="R33" t="n">
-        <v>7031827</v>
+        <v>7032040</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4001,10 +4006,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118552200</v>
+        <v>118557940</v>
       </c>
       <c r="B34" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4013,47 +4018,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589314</v>
+        <v>589730</v>
       </c>
       <c r="R34" t="n">
-        <v>7032037</v>
+        <v>7032086</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4112,10 +4108,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118552820</v>
+        <v>118552378</v>
       </c>
       <c r="B35" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4124,47 +4120,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589311</v>
+        <v>589267</v>
       </c>
       <c r="R35" t="n">
-        <v>7031954</v>
+        <v>7031984</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4223,10 +4210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118552007</v>
+        <v>118555906</v>
       </c>
       <c r="B36" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4239,34 +4226,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589378</v>
+        <v>589312</v>
       </c>
       <c r="R36" t="n">
-        <v>7032143</v>
+        <v>7031697</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4325,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118556365</v>
+        <v>118555622</v>
       </c>
       <c r="B37" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4341,21 +4333,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4365,10 +4357,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589354</v>
+        <v>589490</v>
       </c>
       <c r="R37" t="n">
-        <v>7031906</v>
+        <v>7031668</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4427,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118556986</v>
+        <v>118557202</v>
       </c>
       <c r="B38" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4443,34 +4435,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589680</v>
+        <v>589643</v>
       </c>
       <c r="R38" t="n">
-        <v>7031886</v>
+        <v>7031980</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4529,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118555906</v>
+        <v>118551431</v>
       </c>
       <c r="B39" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4545,39 +4537,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589312</v>
+        <v>589557</v>
       </c>
       <c r="R39" t="n">
-        <v>7031697</v>
+        <v>7032281</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4636,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118558184</v>
+        <v>118552748</v>
       </c>
       <c r="B40" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4648,38 +4635,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589713</v>
+        <v>589291</v>
       </c>
       <c r="R40" t="n">
-        <v>7032063</v>
+        <v>7031953</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4738,10 +4729,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118552657</v>
+        <v>118554548</v>
       </c>
       <c r="B41" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4750,42 +4741,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589282</v>
+        <v>589348</v>
       </c>
       <c r="R41" t="n">
-        <v>7031970</v>
+        <v>7031858</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4844,10 +4831,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118552853</v>
+        <v>118555302</v>
       </c>
       <c r="B42" t="n">
-        <v>90476</v>
+        <v>90795</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4856,25 +4843,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4884,10 +4871,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589290</v>
+        <v>589472</v>
       </c>
       <c r="R42" t="n">
-        <v>7031929</v>
+        <v>7031796</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4946,10 +4933,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118555355</v>
+        <v>118552657</v>
       </c>
       <c r="B43" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4958,38 +4945,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589463</v>
+        <v>589282</v>
       </c>
       <c r="R43" t="n">
-        <v>7031785</v>
+        <v>7031970</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5048,10 +5039,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118555030</v>
+        <v>118557265</v>
       </c>
       <c r="B44" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5060,38 +5051,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589414</v>
+        <v>589642</v>
       </c>
       <c r="R44" t="n">
-        <v>7031799</v>
+        <v>7031970</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118557174</v>
+        <v>118552111</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>90511</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5162,25 +5162,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589654</v>
+        <v>589317</v>
       </c>
       <c r="R45" t="n">
-        <v>7031957</v>
+        <v>7032040</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5252,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118557914</v>
+        <v>118554171</v>
       </c>
       <c r="B46" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5268,34 +5268,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589694</v>
+        <v>589359</v>
       </c>
       <c r="R46" t="n">
-        <v>7032099</v>
+        <v>7031858</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5354,10 +5354,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118553989</v>
+        <v>118552992</v>
       </c>
       <c r="B47" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5370,39 +5370,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589352</v>
+        <v>589298</v>
       </c>
       <c r="R47" t="n">
-        <v>7031849</v>
+        <v>7031917</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5461,10 +5456,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118552101</v>
+        <v>118554797</v>
       </c>
       <c r="B48" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5473,38 +5468,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589319</v>
+        <v>589358</v>
       </c>
       <c r="R48" t="n">
-        <v>7032043</v>
+        <v>7031830</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5563,10 +5558,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118557229</v>
+        <v>118554689</v>
       </c>
       <c r="B49" t="n">
-        <v>79476</v>
+        <v>90476</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5579,34 +5574,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589650</v>
+        <v>589412</v>
       </c>
       <c r="R49" t="n">
-        <v>7031972</v>
+        <v>7031811</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5665,10 +5660,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118551947</v>
+        <v>118551872</v>
       </c>
       <c r="B50" t="n">
-        <v>90476</v>
+        <v>90795</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5677,25 +5672,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5705,10 +5700,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589423</v>
+        <v>589417</v>
       </c>
       <c r="R50" t="n">
-        <v>7032113</v>
+        <v>7032126</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5767,10 +5762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118557154</v>
+        <v>118555030</v>
       </c>
       <c r="B51" t="n">
-        <v>79572</v>
+        <v>90511</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5783,34 +5778,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589647</v>
+        <v>589414</v>
       </c>
       <c r="R51" t="n">
-        <v>7031952</v>
+        <v>7031799</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5869,10 +5864,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118551880</v>
+        <v>118551885</v>
       </c>
       <c r="B52" t="n">
-        <v>90476</v>
+        <v>90795</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5881,25 +5876,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5909,10 +5904,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589417</v>
+        <v>589410</v>
       </c>
       <c r="R52" t="n">
-        <v>7032126</v>
+        <v>7032119</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5971,10 +5966,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118555302</v>
+        <v>118552278</v>
       </c>
       <c r="B53" t="n">
-        <v>90795</v>
+        <v>90529</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5987,21 +5982,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6011,10 +6006,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589472</v>
+        <v>589280</v>
       </c>
       <c r="R53" t="n">
-        <v>7031796</v>
+        <v>7031985</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6073,10 +6068,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118554223</v>
+        <v>118552694</v>
       </c>
       <c r="B54" t="n">
-        <v>90673</v>
+        <v>90511</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6089,21 +6084,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6113,10 +6108,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589368</v>
+        <v>589282</v>
       </c>
       <c r="R54" t="n">
-        <v>7031862</v>
+        <v>7031935</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6175,7 +6170,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118555622</v>
+        <v>118554822</v>
       </c>
       <c r="B55" t="n">
         <v>78491</v>
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589490</v>
+        <v>589399</v>
       </c>
       <c r="R55" t="n">
-        <v>7031668</v>
+        <v>7031814</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6277,10 +6272,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118551796</v>
+        <v>118557661</v>
       </c>
       <c r="B56" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6293,21 +6288,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6317,10 +6312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589417</v>
+        <v>589635</v>
       </c>
       <c r="R56" t="n">
-        <v>7032141</v>
+        <v>7032058</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6379,10 +6374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118551872</v>
+        <v>118556821</v>
       </c>
       <c r="B57" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6395,34 +6390,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589417</v>
+        <v>589651</v>
       </c>
       <c r="R57" t="n">
-        <v>7032126</v>
+        <v>7031856</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6481,7 +6476,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118554450</v>
+        <v>118556574</v>
       </c>
       <c r="B58" t="n">
         <v>90795</v>
@@ -6521,10 +6516,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589392</v>
+        <v>589407</v>
       </c>
       <c r="R58" t="n">
-        <v>7031860</v>
+        <v>7031827</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6583,7 +6578,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118552498</v>
+        <v>118552985</v>
       </c>
       <c r="B59" t="n">
         <v>97853</v>
@@ -6618,12 +6613,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6632,10 +6622,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589280</v>
+        <v>589293</v>
       </c>
       <c r="R59" t="n">
-        <v>7031976</v>
+        <v>7031918</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6694,10 +6684,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118553087</v>
+        <v>118552802</v>
       </c>
       <c r="B60" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6706,38 +6696,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589202</v>
+        <v>589313</v>
       </c>
       <c r="R60" t="n">
-        <v>7031945</v>
+        <v>7031955</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6796,10 +6795,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118552163</v>
+        <v>118556365</v>
       </c>
       <c r="B61" t="n">
-        <v>79601</v>
+        <v>90511</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6808,38 +6807,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589309</v>
+        <v>589354</v>
       </c>
       <c r="R61" t="n">
-        <v>7032040</v>
+        <v>7031906</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6898,10 +6897,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118552350</v>
+        <v>118554168</v>
       </c>
       <c r="B62" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6910,25 +6909,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6938,10 +6937,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589284</v>
+        <v>589359</v>
       </c>
       <c r="R62" t="n">
-        <v>7031972</v>
+        <v>7031857</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7000,10 +6999,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118554252</v>
+        <v>118552219</v>
       </c>
       <c r="B63" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7012,25 +7011,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7040,10 +7039,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589368</v>
+        <v>589268</v>
       </c>
       <c r="R63" t="n">
-        <v>7031862</v>
+        <v>7031998</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7102,10 +7101,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118551972</v>
+        <v>118555409</v>
       </c>
       <c r="B64" t="n">
-        <v>90511</v>
+        <v>90854</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7114,38 +7113,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589404</v>
+        <v>589487</v>
       </c>
       <c r="R64" t="n">
-        <v>7032115</v>
+        <v>7031784</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7204,7 +7203,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118556821</v>
+        <v>118557454</v>
       </c>
       <c r="B65" t="n">
         <v>78491</v>
@@ -7240,14 +7239,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589651</v>
+        <v>589632</v>
       </c>
       <c r="R65" t="n">
-        <v>7031856</v>
+        <v>7032019</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7306,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118554548</v>
+        <v>118551676</v>
       </c>
       <c r="B66" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7318,38 +7317,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589348</v>
+        <v>589418</v>
       </c>
       <c r="R66" t="n">
-        <v>7031858</v>
+        <v>7032144</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7408,10 +7407,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118554978</v>
+        <v>118555468</v>
       </c>
       <c r="B67" t="n">
-        <v>90954</v>
+        <v>90511</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7420,25 +7419,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7448,10 +7447,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589414</v>
+        <v>589488</v>
       </c>
       <c r="R67" t="n">
-        <v>7031799</v>
+        <v>7031771</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7510,10 +7509,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118555409</v>
+        <v>118552350</v>
       </c>
       <c r="B68" t="n">
-        <v>90854</v>
+        <v>78491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7522,25 +7521,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7550,10 +7549,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589487</v>
+        <v>589284</v>
       </c>
       <c r="R68" t="n">
-        <v>7031784</v>
+        <v>7031972</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7612,10 +7611,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118554028</v>
+        <v>118557154</v>
       </c>
       <c r="B69" t="n">
-        <v>90476</v>
+        <v>79572</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7624,38 +7623,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589341</v>
+        <v>589647</v>
       </c>
       <c r="R69" t="n">
-        <v>7031857</v>
+        <v>7031952</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7714,10 +7713,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118552748</v>
+        <v>118554450</v>
       </c>
       <c r="B70" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,42 +7725,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589291</v>
+        <v>589392</v>
       </c>
       <c r="R70" t="n">
-        <v>7031953</v>
+        <v>7031860</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7820,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118553615</v>
+        <v>118554910</v>
       </c>
       <c r="B71" t="n">
-        <v>79476</v>
+        <v>90795</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7832,25 +7827,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7860,10 +7855,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589180</v>
+        <v>589428</v>
       </c>
       <c r="R71" t="n">
-        <v>7031880</v>
+        <v>7031801</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7922,10 +7917,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118557940</v>
+        <v>118554878</v>
       </c>
       <c r="B72" t="n">
-        <v>79572</v>
+        <v>79532</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7934,38 +7929,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589730</v>
+        <v>589437</v>
       </c>
       <c r="R72" t="n">
-        <v>7032086</v>
+        <v>7031771</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8024,10 +8019,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118552663</v>
+        <v>118555659</v>
       </c>
       <c r="B73" t="n">
-        <v>90476</v>
+        <v>57306</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8036,38 +8031,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589275</v>
+        <v>589466</v>
       </c>
       <c r="R73" t="n">
-        <v>7031984</v>
+        <v>7031640</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8126,10 +8126,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118552764</v>
+        <v>118555445</v>
       </c>
       <c r="B74" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8138,42 +8138,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589297</v>
+        <v>589487</v>
       </c>
       <c r="R74" t="n">
-        <v>7031952</v>
+        <v>7031784</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8232,10 +8228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118554878</v>
+        <v>118554028</v>
       </c>
       <c r="B75" t="n">
-        <v>79532</v>
+        <v>90476</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8248,21 +8244,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8272,10 +8268,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589437</v>
+        <v>589341</v>
       </c>
       <c r="R75" t="n">
-        <v>7031771</v>
+        <v>7031857</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8334,10 +8330,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118554171</v>
+        <v>118552101</v>
       </c>
       <c r="B76" t="n">
-        <v>90529</v>
+        <v>90476</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8346,38 +8342,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589359</v>
+        <v>589319</v>
       </c>
       <c r="R76" t="n">
-        <v>7031858</v>
+        <v>7032043</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8436,10 +8432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118552278</v>
+        <v>118551771</v>
       </c>
       <c r="B77" t="n">
-        <v>90529</v>
+        <v>90476</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8448,38 +8444,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589280</v>
+        <v>589423</v>
       </c>
       <c r="R77" t="n">
-        <v>7031985</v>
+        <v>7032117</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8538,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118555659</v>
+        <v>118553615</v>
       </c>
       <c r="B78" t="n">
-        <v>57306</v>
+        <v>79476</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8550,43 +8546,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589466</v>
+        <v>589180</v>
       </c>
       <c r="R78" t="n">
-        <v>7031640</v>
+        <v>7031880</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8645,10 +8636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118551676</v>
+        <v>118553096</v>
       </c>
       <c r="B79" t="n">
-        <v>90511</v>
+        <v>82270</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8661,34 +8652,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589418</v>
+        <v>589204</v>
       </c>
       <c r="R79" t="n">
-        <v>7032144</v>
+        <v>7031942</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8747,10 +8738,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118554797</v>
+        <v>118557914</v>
       </c>
       <c r="B80" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8763,34 +8754,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589358</v>
+        <v>589694</v>
       </c>
       <c r="R80" t="n">
-        <v>7031830</v>
+        <v>7032099</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8849,10 +8840,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118557202</v>
+        <v>118552498</v>
       </c>
       <c r="B81" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8861,38 +8852,47 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589643</v>
+        <v>589280</v>
       </c>
       <c r="R81" t="n">
-        <v>7031980</v>
+        <v>7031976</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8951,10 +8951,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118590971</v>
+        <v>118588485</v>
       </c>
       <c r="B82" t="n">
-        <v>82270</v>
+        <v>90795</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8967,34 +8967,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589691</v>
+        <v>589403</v>
       </c>
       <c r="R82" t="n">
-        <v>7031862</v>
+        <v>7032119</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118587924</v>
+        <v>118591019</v>
       </c>
       <c r="B83" t="n">
-        <v>90476</v>
+        <v>86827</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9065,38 +9065,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589445</v>
+        <v>589686</v>
       </c>
       <c r="R83" t="n">
-        <v>7032073</v>
+        <v>7031880</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9155,10 +9155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118594452</v>
+        <v>118597176</v>
       </c>
       <c r="B84" t="n">
-        <v>90476</v>
+        <v>97770</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9171,21 +9171,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589534</v>
+        <v>589501</v>
       </c>
       <c r="R84" t="n">
-        <v>7031791</v>
+        <v>7031949</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9257,7 +9257,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118587967</v>
+        <v>118587667</v>
       </c>
       <c r="B85" t="n">
         <v>90476</v>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589432</v>
+        <v>589455</v>
       </c>
       <c r="R85" t="n">
-        <v>7032081</v>
+        <v>7032096</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118594447</v>
+        <v>118596822</v>
       </c>
       <c r="B86" t="n">
-        <v>90854</v>
+        <v>90795</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9371,25 +9371,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589535</v>
+        <v>589457</v>
       </c>
       <c r="R86" t="n">
-        <v>7031791</v>
+        <v>7031787</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118587799</v>
+        <v>118589613</v>
       </c>
       <c r="B87" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9473,38 +9473,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589440</v>
+        <v>589740</v>
       </c>
       <c r="R87" t="n">
-        <v>7032089</v>
+        <v>7032026</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9563,10 +9567,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118596031</v>
+        <v>118590334</v>
       </c>
       <c r="B88" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9575,38 +9579,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589279</v>
+        <v>589578</v>
       </c>
       <c r="R88" t="n">
-        <v>7031737</v>
+        <v>7032004</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9665,10 +9673,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118590215</v>
+        <v>118590681</v>
       </c>
       <c r="B89" t="n">
-        <v>57306</v>
+        <v>90476</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9677,43 +9685,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589598</v>
+        <v>589668</v>
       </c>
       <c r="R89" t="n">
-        <v>7031977</v>
+        <v>7031892</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9772,10 +9775,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118586696</v>
+        <v>118589906</v>
       </c>
       <c r="B90" t="n">
-        <v>97770</v>
+        <v>79572</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9784,25 +9787,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9812,10 +9815,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589736</v>
+        <v>589676</v>
       </c>
       <c r="R90" t="n">
-        <v>7032064</v>
+        <v>7031963</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9874,10 +9877,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118590296</v>
+        <v>118588420</v>
       </c>
       <c r="B91" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9886,47 +9889,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589588</v>
+        <v>589421</v>
       </c>
       <c r="R91" t="n">
-        <v>7032008</v>
+        <v>7032124</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9985,10 +9979,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118597023</v>
+        <v>118587872</v>
       </c>
       <c r="B92" t="n">
-        <v>57443</v>
+        <v>90476</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9997,42 +9991,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589517</v>
+        <v>589438</v>
       </c>
       <c r="R92" t="n">
-        <v>7031811</v>
+        <v>7032059</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10091,10 +10081,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118596461</v>
+        <v>118587632</v>
       </c>
       <c r="B93" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10103,47 +10093,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589343</v>
+        <v>589517</v>
       </c>
       <c r="R93" t="n">
-        <v>7031883</v>
+        <v>7032098</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10202,10 +10183,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118587901</v>
+        <v>118590255</v>
       </c>
       <c r="B94" t="n">
-        <v>90511</v>
+        <v>79572</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10218,21 +10199,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10242,10 +10223,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589438</v>
+        <v>589607</v>
       </c>
       <c r="R94" t="n">
-        <v>7032058</v>
+        <v>7032009</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10406,10 +10387,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118589906</v>
+        <v>118588128</v>
       </c>
       <c r="B96" t="n">
-        <v>79572</v>
+        <v>90476</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10418,25 +10399,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10446,10 +10427,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589676</v>
+        <v>589428</v>
       </c>
       <c r="R96" t="n">
-        <v>7031963</v>
+        <v>7032108</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10508,10 +10489,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118591032</v>
+        <v>118596461</v>
       </c>
       <c r="B97" t="n">
-        <v>90529</v>
+        <v>97853</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10520,38 +10501,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589690</v>
+        <v>589343</v>
       </c>
       <c r="R97" t="n">
-        <v>7031882</v>
+        <v>7031883</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10610,10 +10600,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118586687</v>
+        <v>118587754</v>
       </c>
       <c r="B98" t="n">
-        <v>90529</v>
+        <v>90525</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10626,21 +10616,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10650,10 +10640,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589736</v>
+        <v>589443</v>
       </c>
       <c r="R98" t="n">
-        <v>7032057</v>
+        <v>7032086</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10712,10 +10702,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118594407</v>
+        <v>118586448</v>
       </c>
       <c r="B99" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10724,43 +10714,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589525</v>
+        <v>589786</v>
       </c>
       <c r="R99" t="n">
-        <v>7031796</v>
+        <v>7032053</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10819,10 +10808,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118587632</v>
+        <v>118590296</v>
       </c>
       <c r="B100" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10831,38 +10820,47 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589517</v>
+        <v>589588</v>
       </c>
       <c r="R100" t="n">
-        <v>7032098</v>
+        <v>7032008</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10921,10 +10919,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118587754</v>
+        <v>118594447</v>
       </c>
       <c r="B101" t="n">
-        <v>90525</v>
+        <v>90854</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10933,38 +10931,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589443</v>
+        <v>589535</v>
       </c>
       <c r="R101" t="n">
-        <v>7032086</v>
+        <v>7031791</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11023,10 +11021,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118590681</v>
+        <v>118597023</v>
       </c>
       <c r="B102" t="n">
-        <v>90476</v>
+        <v>57443</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11035,38 +11033,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589668</v>
+        <v>589517</v>
       </c>
       <c r="R102" t="n">
-        <v>7031892</v>
+        <v>7031811</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11125,10 +11127,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118589537</v>
+        <v>118589338</v>
       </c>
       <c r="B103" t="n">
-        <v>86827</v>
+        <v>79572</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11141,21 +11143,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11165,10 +11167,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589709</v>
+        <v>589593</v>
       </c>
       <c r="R103" t="n">
-        <v>7031980</v>
+        <v>7032037</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11227,10 +11229,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118590334</v>
+        <v>118597134</v>
       </c>
       <c r="B104" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11239,42 +11241,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589578</v>
+        <v>589508</v>
       </c>
       <c r="R104" t="n">
-        <v>7032004</v>
+        <v>7031905</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11333,10 +11331,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118597176</v>
+        <v>118589036</v>
       </c>
       <c r="B105" t="n">
-        <v>97770</v>
+        <v>90476</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11349,34 +11347,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589501</v>
+        <v>589506</v>
       </c>
       <c r="R105" t="n">
-        <v>7031949</v>
+        <v>7031977</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11435,10 +11433,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118588534</v>
+        <v>118587799</v>
       </c>
       <c r="B106" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11447,25 +11445,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11475,10 +11473,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589413</v>
+        <v>589440</v>
       </c>
       <c r="R106" t="n">
-        <v>7032084</v>
+        <v>7032089</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11537,10 +11535,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118587872</v>
+        <v>118587901</v>
       </c>
       <c r="B107" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11549,25 +11547,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11580,7 +11578,7 @@
         <v>589438</v>
       </c>
       <c r="R107" t="n">
-        <v>7032059</v>
+        <v>7032058</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11639,10 +11637,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118596677</v>
+        <v>118587499</v>
       </c>
       <c r="B108" t="n">
-        <v>97853</v>
+        <v>90529</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11651,42 +11649,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>589425</v>
+        <v>589524</v>
       </c>
       <c r="R108" t="n">
-        <v>7031806</v>
+        <v>7032087</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11745,7 +11739,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118587499</v>
+        <v>118591032</v>
       </c>
       <c r="B109" t="n">
         <v>90529</v>
@@ -11781,14 +11775,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>589524</v>
+        <v>589690</v>
       </c>
       <c r="R109" t="n">
-        <v>7032087</v>
+        <v>7031882</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11847,10 +11841,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118589400</v>
+        <v>118594520</v>
       </c>
       <c r="B110" t="n">
-        <v>90529</v>
+        <v>97853</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11859,38 +11853,47 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589614</v>
+        <v>589534</v>
       </c>
       <c r="R110" t="n">
-        <v>7032054</v>
+        <v>7031764</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11949,10 +11952,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118591019</v>
+        <v>118594407</v>
       </c>
       <c r="B111" t="n">
-        <v>86827</v>
+        <v>57306</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11965,34 +11968,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589686</v>
+        <v>589525</v>
       </c>
       <c r="R111" t="n">
-        <v>7031880</v>
+        <v>7031796</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12051,10 +12059,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118586448</v>
+        <v>118597248</v>
       </c>
       <c r="B112" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12063,30 +12071,31 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12095,10 +12104,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>589786</v>
+        <v>589494</v>
       </c>
       <c r="R112" t="n">
-        <v>7032053</v>
+        <v>7031972</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12157,7 +12166,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118587667</v>
+        <v>118594452</v>
       </c>
       <c r="B113" t="n">
         <v>90476</v>
@@ -12193,14 +12202,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589455</v>
+        <v>589534</v>
       </c>
       <c r="R113" t="n">
-        <v>7032096</v>
+        <v>7031791</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12259,10 +12268,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118588420</v>
+        <v>118589486</v>
       </c>
       <c r="B114" t="n">
-        <v>90795</v>
+        <v>78491</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12275,21 +12284,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12299,10 +12308,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589421</v>
+        <v>589657</v>
       </c>
       <c r="R114" t="n">
-        <v>7032124</v>
+        <v>7031995</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12361,10 +12370,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118588515</v>
+        <v>118590215</v>
       </c>
       <c r="B115" t="n">
-        <v>90507</v>
+        <v>57306</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12377,34 +12386,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589417</v>
+        <v>589598</v>
       </c>
       <c r="R115" t="n">
-        <v>7032079</v>
+        <v>7031977</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12463,10 +12477,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118589486</v>
+        <v>118587967</v>
       </c>
       <c r="B116" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12475,25 +12489,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12503,10 +12517,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>589657</v>
+        <v>589432</v>
       </c>
       <c r="R116" t="n">
-        <v>7031995</v>
+        <v>7032081</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12565,10 +12579,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118588128</v>
+        <v>118589400</v>
       </c>
       <c r="B117" t="n">
-        <v>90476</v>
+        <v>90529</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12577,25 +12591,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12605,10 +12619,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589428</v>
+        <v>589614</v>
       </c>
       <c r="R117" t="n">
-        <v>7032108</v>
+        <v>7032054</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12667,10 +12681,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118589613</v>
+        <v>118586687</v>
       </c>
       <c r="B118" t="n">
-        <v>97853</v>
+        <v>90529</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12679,42 +12693,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589740</v>
+        <v>589736</v>
       </c>
       <c r="R118" t="n">
-        <v>7032026</v>
+        <v>7032057</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12773,10 +12783,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118589918</v>
+        <v>118587924</v>
       </c>
       <c r="B119" t="n">
-        <v>79476</v>
+        <v>90476</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12789,21 +12799,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12813,10 +12823,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589675</v>
+        <v>589445</v>
       </c>
       <c r="R119" t="n">
-        <v>7031964</v>
+        <v>7032073</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12875,10 +12885,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118597134</v>
+        <v>118588515</v>
       </c>
       <c r="B120" t="n">
-        <v>78491</v>
+        <v>90507</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12891,34 +12901,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589508</v>
+        <v>589417</v>
       </c>
       <c r="R120" t="n">
-        <v>7031905</v>
+        <v>7032079</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -12977,10 +12987,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118587773</v>
+        <v>118586696</v>
       </c>
       <c r="B121" t="n">
-        <v>90476</v>
+        <v>97770</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12993,21 +13003,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13017,10 +13027,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>589442</v>
+        <v>589736</v>
       </c>
       <c r="R121" t="n">
-        <v>7032089</v>
+        <v>7032064</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13079,10 +13089,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118597248</v>
+        <v>118596564</v>
       </c>
       <c r="B122" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13091,43 +13101,47 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>589494</v>
+        <v>589368</v>
       </c>
       <c r="R122" t="n">
-        <v>7031972</v>
+        <v>7031833</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13186,10 +13200,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118594520</v>
+        <v>118588534</v>
       </c>
       <c r="B123" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13198,47 +13212,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589534</v>
+        <v>589413</v>
       </c>
       <c r="R123" t="n">
-        <v>7031764</v>
+        <v>7032084</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13297,10 +13302,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118589338</v>
+        <v>118589918</v>
       </c>
       <c r="B124" t="n">
-        <v>79572</v>
+        <v>79476</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13309,25 +13314,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13337,10 +13342,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589593</v>
+        <v>589675</v>
       </c>
       <c r="R124" t="n">
-        <v>7032037</v>
+        <v>7031964</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13399,10 +13404,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118589093</v>
+        <v>118596031</v>
       </c>
       <c r="B125" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13415,39 +13420,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589495</v>
+        <v>589279</v>
       </c>
       <c r="R125" t="n">
-        <v>7031990</v>
+        <v>7031737</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13506,10 +13506,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118592076</v>
+        <v>118587773</v>
       </c>
       <c r="B126" t="n">
-        <v>56494</v>
+        <v>90476</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13518,43 +13518,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589665</v>
+        <v>589442</v>
       </c>
       <c r="R126" t="n">
-        <v>7031798</v>
+        <v>7032089</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13613,10 +13608,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118589036</v>
+        <v>118590971</v>
       </c>
       <c r="B127" t="n">
-        <v>90476</v>
+        <v>82270</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13625,38 +13620,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>589506</v>
+        <v>589691</v>
       </c>
       <c r="R127" t="n">
-        <v>7031977</v>
+        <v>7031862</v>
       </c>
       <c r="S127" t="n">
         <v>20</v>
@@ -13715,10 +13710,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118596822</v>
+        <v>118589093</v>
       </c>
       <c r="B128" t="n">
-        <v>90795</v>
+        <v>57290</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>589457</v>
+        <v>589495</v>
       </c>
       <c r="R128" t="n">
-        <v>7031787</v>
+        <v>7031990</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13817,10 +13817,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118588485</v>
+        <v>118589537</v>
       </c>
       <c r="B129" t="n">
-        <v>90795</v>
+        <v>86827</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13833,21 +13833,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13857,10 +13857,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589403</v>
+        <v>589709</v>
       </c>
       <c r="R129" t="n">
-        <v>7032119</v>
+        <v>7031980</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -13919,10 +13919,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118590255</v>
+        <v>118592076</v>
       </c>
       <c r="B130" t="n">
-        <v>79572</v>
+        <v>56494</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13935,34 +13935,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>589607</v>
+        <v>589665</v>
       </c>
       <c r="R130" t="n">
-        <v>7032009</v>
+        <v>7031798</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14021,7 +14026,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118596564</v>
+        <v>118596677</v>
       </c>
       <c r="B131" t="n">
         <v>97853</v>
@@ -14056,12 +14061,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>589368</v>
+        <v>589425</v>
       </c>
       <c r="R131" t="n">
-        <v>7031833</v>
+        <v>7031806</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95883045</v>
+        <v>118555622</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr Hållmyrflon, Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589396.8806728834</v>
+        <v>589490</v>
       </c>
       <c r="R2" t="n">
-        <v>7032042.137310704</v>
+        <v>7031668</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,75 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95882598</v>
+        <v>118556218</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr Hållmyrflon, Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589295.5790266658</v>
+        <v>589235</v>
       </c>
       <c r="R3" t="n">
-        <v>7031924.091246746</v>
+        <v>7031740</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118557154</v>
+        <v>118596031</v>
       </c>
       <c r="B4" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589647</v>
+        <v>589279</v>
       </c>
       <c r="R4" t="n">
-        <v>7031952</v>
+        <v>7031737</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,50 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118557914</v>
+        <v>118555659</v>
       </c>
       <c r="B5" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589694</v>
+        <v>589466</v>
       </c>
       <c r="R5" t="n">
-        <v>7032099</v>
+        <v>7031640</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1123,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118553061</v>
+        <v>118555906</v>
       </c>
       <c r="B6" t="n">
-        <v>86829</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589254</v>
+        <v>589312</v>
       </c>
       <c r="R6" t="n">
-        <v>7031953</v>
+        <v>7031697</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,62 +1170,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118552802</v>
+        <v>110398808</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589313</v>
+        <v>589668</v>
       </c>
       <c r="R7" t="n">
-        <v>7031955</v>
+        <v>7031756</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1235,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-05-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket spillning under natträd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,65 +1260,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118553087</v>
+        <v>110398811</v>
       </c>
       <c r="B8" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589202</v>
+        <v>589669</v>
       </c>
       <c r="R8" t="n">
-        <v>7031945</v>
+        <v>7031755</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,12 +1337,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,62 +1357,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118552278</v>
+        <v>118594520</v>
       </c>
       <c r="B9" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589280</v>
+        <v>589534</v>
       </c>
       <c r="R9" t="n">
-        <v>7031985</v>
+        <v>7031764</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1508,12 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,15 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118551431</v>
+        <v>118553061</v>
       </c>
       <c r="B10" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,34 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589557</v>
+        <v>589254</v>
       </c>
       <c r="R10" t="n">
-        <v>7032281</v>
+        <v>7031953</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1642,50 +1572,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118552101</v>
+        <v>118589537</v>
       </c>
       <c r="B11" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589319</v>
+        <v>589709</v>
       </c>
       <c r="R11" t="n">
-        <v>7032043</v>
+        <v>7031980</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1712,12 +1637,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,59 +1669,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118552631</v>
+        <v>118591019</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589282</v>
+        <v>589686</v>
       </c>
       <c r="R12" t="n">
-        <v>7031970</v>
+        <v>7031880</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1823,12 +1734,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,59 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118552200</v>
+        <v>118551872</v>
       </c>
       <c r="B13" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589314</v>
+        <v>589417</v>
       </c>
       <c r="R13" t="n">
-        <v>7032037</v>
+        <v>7032126</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1966,15 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118557454</v>
+        <v>118551885</v>
       </c>
       <c r="B14" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,34 +1874,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589632</v>
+        <v>589410</v>
       </c>
       <c r="R14" t="n">
-        <v>7032019</v>
+        <v>7032119</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2068,50 +1960,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118552051</v>
+        <v>118552378</v>
       </c>
       <c r="B15" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589348</v>
+        <v>589267</v>
       </c>
       <c r="R15" t="n">
-        <v>7032078</v>
+        <v>7031984</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2170,15 +2057,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118556986</v>
+        <v>118554450</v>
       </c>
       <c r="B16" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,34 +2068,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589680</v>
+        <v>589392</v>
       </c>
       <c r="R16" t="n">
-        <v>7031886</v>
+        <v>7031860</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2272,50 +2154,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118551880</v>
+        <v>118554910</v>
       </c>
       <c r="B17" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589417</v>
+        <v>589428</v>
       </c>
       <c r="R17" t="n">
-        <v>7032126</v>
+        <v>7031801</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2374,15 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118551796</v>
+        <v>118555302</v>
       </c>
       <c r="B18" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,34 +2262,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589417</v>
+        <v>589472</v>
       </c>
       <c r="R18" t="n">
-        <v>7032141</v>
+        <v>7031796</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2476,15 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118554223</v>
+        <v>118556574</v>
       </c>
       <c r="B19" t="n">
-        <v>90675</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,34 +2359,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589368</v>
+        <v>589407</v>
       </c>
       <c r="R19" t="n">
-        <v>7031862</v>
+        <v>7031827</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2578,50 +2445,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118552663</v>
+        <v>118588420</v>
       </c>
       <c r="B20" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589275</v>
+        <v>589421</v>
       </c>
       <c r="R20" t="n">
-        <v>7031984</v>
+        <v>7032124</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2648,12 +2510,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2680,15 +2542,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118554822</v>
+        <v>118588485</v>
       </c>
       <c r="B21" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2696,34 +2553,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589399</v>
+        <v>589403</v>
       </c>
       <c r="R21" t="n">
-        <v>7031814</v>
+        <v>7032119</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2750,12 +2607,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,15 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118555468</v>
+        <v>118596822</v>
       </c>
       <c r="B22" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2798,34 +2650,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589488</v>
+        <v>589457</v>
       </c>
       <c r="R22" t="n">
-        <v>7031771</v>
+        <v>7031787</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2852,12 +2704,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2884,15 +2736,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118554797</v>
+        <v>118588515</v>
       </c>
       <c r="B23" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,34 +2747,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589358</v>
+        <v>589417</v>
       </c>
       <c r="R23" t="n">
-        <v>7031830</v>
+        <v>7032079</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2954,12 +2801,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2986,15 +2833,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118556574</v>
+        <v>95882109</v>
       </c>
       <c r="B24" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3002,37 +2844,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589407</v>
+        <v>589216</v>
       </c>
       <c r="R24" t="n">
-        <v>7031827</v>
+        <v>7032029</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,12 +2908,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3076,62 +2928,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118558184</v>
+        <v>118551676</v>
       </c>
       <c r="B25" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589713</v>
+        <v>589418</v>
       </c>
       <c r="R25" t="n">
-        <v>7032063</v>
+        <v>7032144</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3190,15 +3037,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118554171</v>
+        <v>118551796</v>
       </c>
       <c r="B26" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3206,34 +3048,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589359</v>
+        <v>589417</v>
       </c>
       <c r="R26" t="n">
-        <v>7031858</v>
+        <v>7032141</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3292,15 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118557940</v>
+        <v>118551972</v>
       </c>
       <c r="B27" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,34 +3145,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589730</v>
+        <v>589404</v>
       </c>
       <c r="R27" t="n">
-        <v>7032086</v>
+        <v>7032115</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3394,15 +3231,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118551676</v>
+        <v>118552007</v>
       </c>
       <c r="B28" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3430,14 +3262,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589418</v>
+        <v>589378</v>
       </c>
       <c r="R28" t="n">
-        <v>7032144</v>
+        <v>7032143</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3496,15 +3328,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118555622</v>
+        <v>118552111</v>
       </c>
       <c r="B29" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3512,34 +3339,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589490</v>
+        <v>589317</v>
       </c>
       <c r="R29" t="n">
-        <v>7031668</v>
+        <v>7032040</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3598,50 +3425,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118554548</v>
+        <v>118552694</v>
       </c>
       <c r="B30" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589348</v>
+        <v>589282</v>
       </c>
       <c r="R30" t="n">
-        <v>7031858</v>
+        <v>7031935</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3700,15 +3522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118554252</v>
+        <v>118552992</v>
       </c>
       <c r="B31" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,34 +3533,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589368</v>
+        <v>589298</v>
       </c>
       <c r="R31" t="n">
-        <v>7031862</v>
+        <v>7031917</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3802,50 +3619,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118555409</v>
+        <v>118554184</v>
       </c>
       <c r="B32" t="n">
-        <v>90856</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589487</v>
+        <v>589360</v>
       </c>
       <c r="R32" t="n">
-        <v>7031784</v>
+        <v>7031856</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3904,15 +3716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118552992</v>
+        <v>118554797</v>
       </c>
       <c r="B33" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,14 +3747,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589298</v>
+        <v>589358</v>
       </c>
       <c r="R33" t="n">
-        <v>7031917</v>
+        <v>7031830</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4006,15 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118555302</v>
+        <v>118555030</v>
       </c>
       <c r="B34" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4022,34 +3824,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589472</v>
+        <v>589414</v>
       </c>
       <c r="R34" t="n">
-        <v>7031796</v>
+        <v>7031799</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4108,50 +3910,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118552853</v>
+        <v>118555355</v>
       </c>
       <c r="B35" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589290</v>
+        <v>589463</v>
       </c>
       <c r="R35" t="n">
-        <v>7031929</v>
+        <v>7031785</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4210,15 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118552350</v>
+        <v>118555468</v>
       </c>
       <c r="B36" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4226,34 +4018,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589284</v>
+        <v>589488</v>
       </c>
       <c r="R36" t="n">
-        <v>7031972</v>
+        <v>7031771</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4312,15 +4104,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118556821</v>
+        <v>118556365</v>
       </c>
       <c r="B37" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4328,34 +4115,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589651</v>
+        <v>589354</v>
       </c>
       <c r="R37" t="n">
-        <v>7031856</v>
+        <v>7031906</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4414,15 +4201,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118552031</v>
+        <v>118587799</v>
       </c>
       <c r="B38" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4430,34 +4212,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589360</v>
+        <v>589440</v>
       </c>
       <c r="R38" t="n">
-        <v>7032085</v>
+        <v>7032089</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4484,12 +4266,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4516,50 +4298,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118557174</v>
+        <v>118587901</v>
       </c>
       <c r="B39" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589654</v>
+        <v>589438</v>
       </c>
       <c r="R39" t="n">
-        <v>7031957</v>
+        <v>7032058</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4586,12 +4363,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4618,50 +4395,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118551947</v>
+        <v>118587754</v>
       </c>
       <c r="B40" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589423</v>
+        <v>589443</v>
       </c>
       <c r="R40" t="n">
-        <v>7032113</v>
+        <v>7032086</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4688,12 +4460,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4720,53 +4492,58 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118557448</v>
+        <v>95882132</v>
       </c>
       <c r="B41" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589632</v>
+        <v>589216</v>
       </c>
       <c r="R41" t="n">
-        <v>7032018</v>
+        <v>7032029</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4790,12 +4567,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4810,27 +4587,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118551972</v>
+        <v>95883045</v>
       </c>
       <c r="B42" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,37 +4610,47 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589404</v>
+        <v>589397</v>
       </c>
       <c r="R42" t="n">
-        <v>7032115</v>
+        <v>7032042</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4892,12 +4674,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4912,27 +4694,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118554450</v>
+        <v>118554978</v>
       </c>
       <c r="B43" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4940,34 +4717,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589392</v>
+        <v>589414</v>
       </c>
       <c r="R43" t="n">
-        <v>7031860</v>
+        <v>7031799</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5026,54 +4803,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118552985</v>
+        <v>118553096</v>
       </c>
       <c r="B44" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589293</v>
+        <v>589204</v>
       </c>
       <c r="R44" t="n">
-        <v>7031918</v>
+        <v>7031942</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5132,50 +4900,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118554978</v>
+        <v>118590971</v>
       </c>
       <c r="B45" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589414</v>
+        <v>589691</v>
       </c>
       <c r="R45" t="n">
-        <v>7031799</v>
+        <v>7031862</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5202,12 +4965,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5234,50 +4997,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118552219</v>
+        <v>118554223</v>
       </c>
       <c r="B46" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589268</v>
+        <v>589368</v>
       </c>
       <c r="R46" t="n">
-        <v>7031998</v>
+        <v>7031862</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5336,50 +5094,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118551771</v>
+        <v>118555409</v>
       </c>
       <c r="B47" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589423</v>
+        <v>589487</v>
       </c>
       <c r="R47" t="n">
-        <v>7032117</v>
+        <v>7031784</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5438,50 +5191,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118555030</v>
+        <v>118594447</v>
       </c>
       <c r="B48" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589414</v>
+        <v>589535</v>
       </c>
       <c r="R48" t="n">
-        <v>7031799</v>
+        <v>7031791</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5508,12 +5256,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5540,53 +5288,58 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118551885</v>
+        <v>95882598</v>
       </c>
       <c r="B49" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589410</v>
+        <v>589296</v>
       </c>
       <c r="R49" t="n">
-        <v>7032119</v>
+        <v>7031924</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5610,12 +5363,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5630,62 +5383,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118556365</v>
+        <v>118551771</v>
       </c>
       <c r="B50" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589354</v>
+        <v>589423</v>
       </c>
       <c r="R50" t="n">
-        <v>7031906</v>
+        <v>7032117</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5744,15 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118557253</v>
+        <v>118551880</v>
       </c>
       <c r="B51" t="n">
-        <v>58135</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5760,34 +5503,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>208249</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589648</v>
+        <v>589417</v>
       </c>
       <c r="R51" t="n">
-        <v>7031970</v>
+        <v>7032126</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5846,50 +5589,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118556301</v>
+        <v>118551947</v>
       </c>
       <c r="B52" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589298</v>
+        <v>589423</v>
       </c>
       <c r="R52" t="n">
-        <v>7031829</v>
+        <v>7032113</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5951,12 +5689,7 @@
         <v>118551992</v>
       </c>
       <c r="B53" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5984,7 +5717,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -6050,15 +5783,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118556472</v>
+        <v>118552051</v>
       </c>
       <c r="B54" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6066,34 +5794,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589408</v>
+        <v>589348</v>
       </c>
       <c r="R54" t="n">
-        <v>7031876</v>
+        <v>7032078</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6152,55 +5880,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118553989</v>
+        <v>118552101</v>
       </c>
       <c r="B55" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589352</v>
+        <v>589319</v>
       </c>
       <c r="R55" t="n">
-        <v>7031849</v>
+        <v>7032043</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6259,50 +5977,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118553096</v>
+        <v>118552219</v>
       </c>
       <c r="B56" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589204</v>
+        <v>589268</v>
       </c>
       <c r="R56" t="n">
-        <v>7031942</v>
+        <v>7031998</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6361,59 +6074,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118557265</v>
+        <v>118552663</v>
       </c>
       <c r="B57" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589642</v>
+        <v>589275</v>
       </c>
       <c r="R57" t="n">
-        <v>7031970</v>
+        <v>7031984</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6472,54 +6171,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118552748</v>
+        <v>118552853</v>
       </c>
       <c r="B58" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589291</v>
+        <v>589290</v>
       </c>
       <c r="R58" t="n">
-        <v>7031953</v>
+        <v>7031929</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6578,15 +6268,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118553615</v>
+        <v>118554028</v>
       </c>
       <c r="B59" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6594,34 +6279,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589180</v>
+        <v>589341</v>
       </c>
       <c r="R59" t="n">
-        <v>7031880</v>
+        <v>7031857</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6680,50 +6365,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118554184</v>
+        <v>118554168</v>
       </c>
       <c r="B60" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589360</v>
+        <v>589359</v>
       </c>
       <c r="R60" t="n">
-        <v>7031856</v>
+        <v>7031857</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6782,50 +6462,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118552111</v>
+        <v>118554548</v>
       </c>
       <c r="B61" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589317</v>
+        <v>589348</v>
       </c>
       <c r="R61" t="n">
-        <v>7032040</v>
+        <v>7031858</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6884,50 +6559,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118554910</v>
+        <v>118554689</v>
       </c>
       <c r="B62" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589428</v>
+        <v>589412</v>
       </c>
       <c r="R62" t="n">
-        <v>7031801</v>
+        <v>7031811</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6989,12 +6659,7 @@
         <v>118555445</v>
       </c>
       <c r="B63" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7022,7 +6687,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -7088,15 +6753,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118552163</v>
+        <v>118557448</v>
       </c>
       <c r="B64" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7104,34 +6764,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589309</v>
+        <v>589632</v>
       </c>
       <c r="R64" t="n">
-        <v>7032040</v>
+        <v>7032018</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7190,50 +6850,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118552378</v>
+        <v>118587667</v>
       </c>
       <c r="B65" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589267</v>
+        <v>589455</v>
       </c>
       <c r="R65" t="n">
-        <v>7031984</v>
+        <v>7032096</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7260,12 +6915,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,50 +6947,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118552007</v>
+        <v>118587773</v>
       </c>
       <c r="B66" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589378</v>
+        <v>589442</v>
       </c>
       <c r="R66" t="n">
-        <v>7032143</v>
+        <v>7032089</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7362,12 +7012,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7394,15 +7044,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118554168</v>
+        <v>118587872</v>
       </c>
       <c r="B67" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7430,14 +7075,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589359</v>
+        <v>589438</v>
       </c>
       <c r="R67" t="n">
-        <v>7031857</v>
+        <v>7032058</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7464,12 +7109,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7496,15 +7141,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118554689</v>
+        <v>118587924</v>
       </c>
       <c r="B68" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7532,14 +7172,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589412</v>
+        <v>589445</v>
       </c>
       <c r="R68" t="n">
-        <v>7031811</v>
+        <v>7032073</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7566,12 +7206,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7598,15 +7238,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118557229</v>
+        <v>118587967</v>
       </c>
       <c r="B69" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7614,34 +7249,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589650</v>
+        <v>589432</v>
       </c>
       <c r="R69" t="n">
-        <v>7031972</v>
+        <v>7032081</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7668,12 +7303,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7700,15 +7335,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118554878</v>
+        <v>118588128</v>
       </c>
       <c r="B70" t="n">
-        <v>79534</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7716,34 +7346,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589437</v>
+        <v>589428</v>
       </c>
       <c r="R70" t="n">
-        <v>7031771</v>
+        <v>7032108</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7770,12 +7400,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7802,59 +7432,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118552498</v>
+        <v>118588534</v>
       </c>
       <c r="B71" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589280</v>
+        <v>589413</v>
       </c>
       <c r="R71" t="n">
-        <v>7031976</v>
+        <v>7032084</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7881,12 +7497,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7913,50 +7529,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118555355</v>
+        <v>118589036</v>
       </c>
       <c r="B72" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589463</v>
+        <v>589506</v>
       </c>
       <c r="R72" t="n">
-        <v>7031785</v>
+        <v>7031977</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -7983,12 +7594,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8015,50 +7626,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118552694</v>
+        <v>118590681</v>
       </c>
       <c r="B73" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589282</v>
+        <v>589668</v>
       </c>
       <c r="R73" t="n">
-        <v>7031935</v>
+        <v>7031892</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8085,12 +7691,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8117,55 +7723,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118555906</v>
+        <v>118594452</v>
       </c>
       <c r="B74" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589312</v>
+        <v>589534</v>
       </c>
       <c r="R74" t="n">
-        <v>7031697</v>
+        <v>7031791</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8192,12 +7788,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8224,15 +7820,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118552764</v>
+        <v>118551431</v>
       </c>
       <c r="B75" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8240,38 +7831,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589297</v>
+        <v>589557</v>
       </c>
       <c r="R75" t="n">
-        <v>7031952</v>
+        <v>7032281</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8330,15 +7917,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118552820</v>
+        <v>118552031</v>
       </c>
       <c r="B76" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8346,43 +7928,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589311</v>
+        <v>589360</v>
       </c>
       <c r="R76" t="n">
-        <v>7031954</v>
+        <v>7032085</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8441,50 +8014,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118554028</v>
+        <v>118552350</v>
       </c>
       <c r="B77" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589341</v>
+        <v>589284</v>
       </c>
       <c r="R77" t="n">
-        <v>7031857</v>
+        <v>7031972</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8543,50 +8111,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118557202</v>
+        <v>118553087</v>
       </c>
       <c r="B78" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589643</v>
+        <v>589202</v>
       </c>
       <c r="R78" t="n">
-        <v>7031980</v>
+        <v>7031945</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8645,19 +8208,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118557661</v>
+        <v>118554252</v>
       </c>
       <c r="B79" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -8681,14 +8239,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589635</v>
+        <v>589368</v>
       </c>
       <c r="R79" t="n">
-        <v>7032058</v>
+        <v>7031862</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8747,55 +8305,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118555659</v>
+        <v>118554822</v>
       </c>
       <c r="B80" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589466</v>
+        <v>589399</v>
       </c>
       <c r="R80" t="n">
-        <v>7031640</v>
+        <v>7031814</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8854,50 +8402,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118551872</v>
+        <v>118556301</v>
       </c>
       <c r="B81" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589417</v>
+        <v>589298</v>
       </c>
       <c r="R81" t="n">
-        <v>7032126</v>
+        <v>7031829</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8956,15 +8499,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118590334</v>
+        <v>118556821</v>
       </c>
       <c r="B82" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8972,38 +8510,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589578</v>
+        <v>589651</v>
       </c>
       <c r="R82" t="n">
-        <v>7032004</v>
+        <v>7031856</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9030,12 +8564,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9062,50 +8596,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118590255</v>
+        <v>118556986</v>
       </c>
       <c r="B83" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589607</v>
+        <v>589680</v>
       </c>
       <c r="R83" t="n">
-        <v>7032009</v>
+        <v>7031886</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9132,12 +8661,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9164,55 +8693,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118592076</v>
+        <v>118557454</v>
       </c>
       <c r="B84" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589665</v>
+        <v>589632</v>
       </c>
       <c r="R84" t="n">
-        <v>7031798</v>
+        <v>7032019</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9239,12 +8758,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9271,50 +8790,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118591032</v>
+        <v>118557661</v>
       </c>
       <c r="B85" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589690</v>
+        <v>589635</v>
       </c>
       <c r="R85" t="n">
-        <v>7031882</v>
+        <v>7032058</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9341,12 +8855,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9373,50 +8887,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118596822</v>
+        <v>118557914</v>
       </c>
       <c r="B86" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589457</v>
+        <v>589694</v>
       </c>
       <c r="R86" t="n">
-        <v>7031787</v>
+        <v>7032099</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9443,12 +8952,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9475,15 +8984,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118596564</v>
+        <v>118587264</v>
       </c>
       <c r="B87" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9491,43 +8995,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589368</v>
+        <v>589634</v>
       </c>
       <c r="R87" t="n">
-        <v>7031833</v>
+        <v>7032061</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9586,50 +9081,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118588515</v>
+        <v>118587632</v>
       </c>
       <c r="B88" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589417</v>
+        <v>589517</v>
       </c>
       <c r="R88" t="n">
-        <v>7032079</v>
+        <v>7032098</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9688,50 +9178,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118587667</v>
+        <v>118589486</v>
       </c>
       <c r="B89" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589455</v>
+        <v>589657</v>
       </c>
       <c r="R89" t="n">
-        <v>7032096</v>
+        <v>7031995</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9790,50 +9275,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118590681</v>
+        <v>118590539</v>
       </c>
       <c r="B90" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589668</v>
+        <v>589605</v>
       </c>
       <c r="R90" t="n">
-        <v>7031892</v>
+        <v>7031935</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9892,50 +9372,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118589918</v>
+        <v>118597134</v>
       </c>
       <c r="B91" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589675</v>
+        <v>589508</v>
       </c>
       <c r="R91" t="n">
-        <v>7031964</v>
+        <v>7031905</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9994,50 +9469,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118586696</v>
+        <v>118597248</v>
       </c>
       <c r="B92" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589736</v>
+        <v>589494</v>
       </c>
       <c r="R92" t="n">
-        <v>7032064</v>
+        <v>7031972</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10096,54 +9571,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118589613</v>
+        <v>118553615</v>
       </c>
       <c r="B93" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589740</v>
+        <v>589180</v>
       </c>
       <c r="R93" t="n">
-        <v>7032026</v>
+        <v>7031880</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10170,12 +9636,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10202,50 +9668,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118587799</v>
+        <v>118556472</v>
       </c>
       <c r="B94" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589440</v>
+        <v>589408</v>
       </c>
       <c r="R94" t="n">
-        <v>7032089</v>
+        <v>7031876</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10272,12 +9733,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10304,54 +9765,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118597023</v>
+        <v>118557174</v>
       </c>
       <c r="B95" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589517</v>
+        <v>589654</v>
       </c>
       <c r="R95" t="n">
-        <v>7031811</v>
+        <v>7031957</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10378,12 +9830,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10410,52 +9862,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118597248</v>
+        <v>118557229</v>
       </c>
       <c r="B96" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589494</v>
+        <v>589650</v>
       </c>
       <c r="R96" t="n">
         <v>7031972</v>
@@ -10485,12 +9927,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10517,50 +9959,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118588420</v>
+        <v>118589918</v>
       </c>
       <c r="B97" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589421</v>
+        <v>589675</v>
       </c>
       <c r="R97" t="n">
-        <v>7032124</v>
+        <v>7031964</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10619,50 +10056,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118587924</v>
+        <v>118557154</v>
       </c>
       <c r="B98" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589445</v>
+        <v>589647</v>
       </c>
       <c r="R98" t="n">
-        <v>7032073</v>
+        <v>7031952</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10689,12 +10121,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10721,15 +10153,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118590971</v>
+        <v>118557202</v>
       </c>
       <c r="B99" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10737,34 +10164,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589691</v>
+        <v>589643</v>
       </c>
       <c r="R99" t="n">
-        <v>7031862</v>
+        <v>7031980</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10791,12 +10218,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10823,15 +10250,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118589093</v>
+        <v>118557940</v>
       </c>
       <c r="B100" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10839,39 +10261,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589495</v>
+        <v>589730</v>
       </c>
       <c r="R100" t="n">
-        <v>7031990</v>
+        <v>7032086</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10898,12 +10315,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10930,15 +10347,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118587499</v>
+        <v>118589338</v>
       </c>
       <c r="B101" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10946,34 +10358,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589524</v>
+        <v>589593</v>
       </c>
       <c r="R101" t="n">
-        <v>7032087</v>
+        <v>7032037</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -11032,15 +10444,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118589338</v>
+        <v>118589906</v>
       </c>
       <c r="B102" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11068,14 +10475,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589593</v>
+        <v>589676</v>
       </c>
       <c r="R102" t="n">
-        <v>7032037</v>
+        <v>7031963</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11134,15 +10541,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118589906</v>
+        <v>118590255</v>
       </c>
       <c r="B103" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11170,14 +10572,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589676</v>
+        <v>589607</v>
       </c>
       <c r="R103" t="n">
-        <v>7031963</v>
+        <v>7032009</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11236,50 +10638,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118588485</v>
+        <v>118552163</v>
       </c>
       <c r="B104" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589403</v>
+        <v>589309</v>
       </c>
       <c r="R104" t="n">
-        <v>7032119</v>
+        <v>7032040</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11306,12 +10703,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11338,50 +10735,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118586687</v>
+        <v>118590215</v>
       </c>
       <c r="B105" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589736</v>
+        <v>589598</v>
       </c>
       <c r="R105" t="n">
-        <v>7032057</v>
+        <v>7031977</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11440,15 +10837,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118588128</v>
+        <v>118594407</v>
       </c>
       <c r="B106" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11456,34 +10848,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589428</v>
+        <v>589525</v>
       </c>
       <c r="R106" t="n">
-        <v>7032108</v>
+        <v>7031796</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11542,50 +10939,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118587773</v>
+        <v>118553989</v>
       </c>
       <c r="B107" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589442</v>
+        <v>589352</v>
       </c>
       <c r="R107" t="n">
-        <v>7032089</v>
+        <v>7031849</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11612,12 +11009,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11644,15 +11041,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118594407</v>
+        <v>118589093</v>
       </c>
       <c r="B108" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11660,16 +11052,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11685,14 +11077,14 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>589525</v>
+        <v>589495</v>
       </c>
       <c r="R108" t="n">
-        <v>7031796</v>
+        <v>7031990</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11751,53 +11143,57 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118587632</v>
+        <v>110398772</v>
       </c>
       <c r="B109" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>589517</v>
+        <v>589710</v>
       </c>
       <c r="R109" t="n">
-        <v>7032098</v>
+        <v>7031932</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11821,12 +11217,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2022-05-05</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Uppflog tjäderhona.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11841,62 +11242,62 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118597134</v>
+        <v>118588929</v>
       </c>
       <c r="B110" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589508</v>
+        <v>589421</v>
       </c>
       <c r="R110" t="n">
-        <v>7031905</v>
+        <v>7031998</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11955,15 +11356,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118597176</v>
+        <v>118592076</v>
       </c>
       <c r="B111" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11971,34 +11367,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589501</v>
+        <v>589665</v>
       </c>
       <c r="R111" t="n">
-        <v>7031949</v>
+        <v>7031798</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12057,54 +11458,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118596677</v>
+        <v>118593307</v>
       </c>
       <c r="B112" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>589425</v>
+        <v>589598</v>
       </c>
       <c r="R112" t="n">
-        <v>7031806</v>
+        <v>7031837</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12163,50 +11555,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118587872</v>
+        <v>118597023</v>
       </c>
       <c r="B113" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589438</v>
+        <v>589517</v>
       </c>
       <c r="R113" t="n">
-        <v>7032059</v>
+        <v>7031811</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -12265,50 +11656,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118589400</v>
+        <v>118557253</v>
       </c>
       <c r="B114" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>208249</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589614</v>
+        <v>589648</v>
       </c>
       <c r="R114" t="n">
-        <v>7032054</v>
+        <v>7031970</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12335,12 +11721,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12367,50 +11753,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118587901</v>
+        <v>118558184</v>
       </c>
       <c r="B115" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589438</v>
+        <v>589713</v>
       </c>
       <c r="R115" t="n">
-        <v>7032058</v>
+        <v>7032063</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>
@@ -12437,12 +11818,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12469,50 +11850,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118596031</v>
+        <v>118586696</v>
       </c>
       <c r="B116" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>589279</v>
+        <v>589736</v>
       </c>
       <c r="R116" t="n">
-        <v>7031737</v>
+        <v>7032064</v>
       </c>
       <c r="S116" t="n">
         <v>20</v>
@@ -12571,50 +11947,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118589486</v>
+        <v>118597176</v>
       </c>
       <c r="B117" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>589657</v>
+        <v>589501</v>
       </c>
       <c r="R117" t="n">
-        <v>7031995</v>
+        <v>7031949</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12673,50 +12044,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118587967</v>
+        <v>118552200</v>
       </c>
       <c r="B118" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589432</v>
+        <v>589314</v>
       </c>
       <c r="R118" t="n">
-        <v>7032081</v>
+        <v>7032037</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -12743,12 +12118,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12775,50 +12150,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118591019</v>
+        <v>118552498</v>
       </c>
       <c r="B119" t="n">
-        <v>86829</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589686</v>
+        <v>589280</v>
       </c>
       <c r="R119" t="n">
-        <v>7031880</v>
+        <v>7031976</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12845,12 +12224,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12877,50 +12256,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118587264</v>
+        <v>118552631</v>
       </c>
       <c r="B120" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589634</v>
+        <v>589282</v>
       </c>
       <c r="R120" t="n">
-        <v>7032061</v>
+        <v>7031970</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -12947,12 +12330,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12979,15 +12362,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118596461</v>
+        <v>118552748</v>
       </c>
       <c r="B121" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13014,24 +12392,19 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>589343</v>
+        <v>589291</v>
       </c>
       <c r="R121" t="n">
-        <v>7031883</v>
+        <v>7031953</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13058,12 +12431,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13090,50 +12463,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118587754</v>
+        <v>118552764</v>
       </c>
       <c r="B122" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>589443</v>
+        <v>589297</v>
       </c>
       <c r="R122" t="n">
-        <v>7032086</v>
+        <v>7031952</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -13160,12 +12532,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13192,15 +12564,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118594520</v>
+        <v>118552802</v>
       </c>
       <c r="B123" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13227,7 +12594,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -13237,14 +12604,14 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>589534</v>
+        <v>589313</v>
       </c>
       <c r="R123" t="n">
-        <v>7031764</v>
+        <v>7031955</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13271,12 +12638,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13303,50 +12670,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118594452</v>
+        <v>118552820</v>
       </c>
       <c r="B124" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589534</v>
+        <v>589311</v>
       </c>
       <c r="R124" t="n">
-        <v>7031791</v>
+        <v>7031954</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -13373,12 +12744,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13405,50 +12776,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118588534</v>
+        <v>118552985</v>
       </c>
       <c r="B125" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589413</v>
+        <v>589293</v>
       </c>
       <c r="R125" t="n">
-        <v>7032084</v>
+        <v>7031918</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -13475,12 +12845,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13507,50 +12877,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118589036</v>
+        <v>118557265</v>
       </c>
       <c r="B126" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589506</v>
+        <v>589642</v>
       </c>
       <c r="R126" t="n">
-        <v>7031977</v>
+        <v>7031970</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13577,12 +12951,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13612,12 +12986,7 @@
         <v>118586448</v>
       </c>
       <c r="B127" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13649,7 +13018,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
@@ -13715,15 +13084,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118590296</v>
+        <v>118589613</v>
       </c>
       <c r="B128" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13750,24 +13114,19 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>589588</v>
+        <v>589740</v>
       </c>
       <c r="R128" t="n">
-        <v>7032008</v>
+        <v>7032026</v>
       </c>
       <c r="S128" t="n">
         <v>20</v>
@@ -13826,15 +13185,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118594447</v>
+        <v>118590296</v>
       </c>
       <c r="B129" t="n">
-        <v>90856</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13842,34 +13196,43 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sör-Hållmyrflon (Sör-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589535</v>
+        <v>589588</v>
       </c>
       <c r="R129" t="n">
-        <v>7031791</v>
+        <v>7032008</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -13928,50 +13291,49 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118589537</v>
+        <v>118590334</v>
       </c>
       <c r="B130" t="n">
-        <v>86829</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>589709</v>
+        <v>589578</v>
       </c>
       <c r="R130" t="n">
-        <v>7031980</v>
+        <v>7032004</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14030,55 +13392,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118590215</v>
+        <v>118596461</v>
       </c>
       <c r="B131" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>589598</v>
+        <v>589343</v>
       </c>
       <c r="R131" t="n">
-        <v>7031977</v>
+        <v>7031883</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14134,6 +13495,411 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>118596564</v>
+      </c>
+      <c r="B132" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>589368</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7031833</v>
+      </c>
+      <c r="S132" t="n">
+        <v>20</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>118596677</v>
+      </c>
+      <c r="B133" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>589425</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7031806</v>
+      </c>
+      <c r="S133" t="n">
+        <v>20</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>122217858</v>
+      </c>
+      <c r="B134" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>589680</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7032243</v>
+      </c>
+      <c r="S134" t="n">
+        <v>15</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>118554878</v>
+      </c>
+      <c r="B135" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Sör-Hållmyrflon, Sör-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>589437</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7031771</v>
+      </c>
+      <c r="S135" t="n">
+        <v>20</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29100-2024 artfynd.xlsx
+++ b/artfynd/A 29100-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AZ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553061</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551885</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552378</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554910</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555302</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118588420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118588485</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118596822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118588515</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95882109</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551676</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551796</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551972</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552007</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552111</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552694</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552992</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554184</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554797</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555030</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555355</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555468</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556365</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587799</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3398,6 +3538,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587901</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587754</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95882132</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883045</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3806,6 +3966,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554978</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3903,6 +4068,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553096</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4000,6 +4170,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554223</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4097,6 +4272,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555409</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4194,6 +4374,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118594447</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4301,6 +4486,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95882598</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4398,6 +4588,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551771</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4495,6 +4690,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551880</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4592,6 +4792,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551947</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4689,6 +4894,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551992</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4786,6 +4996,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552051</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4883,6 +5098,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552101</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4980,6 +5200,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552219</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5077,6 +5302,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552663</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5174,6 +5404,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552853</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5271,6 +5506,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554028</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5368,6 +5608,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554168</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5465,6 +5710,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554548</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5562,6 +5812,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554689</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5659,6 +5914,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555445</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5756,6 +6016,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557448</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5853,6 +6118,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587667</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5950,6 +6220,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587773</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6047,6 +6322,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587872</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6144,6 +6424,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587924</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6241,6 +6526,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587967</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6338,6 +6628,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118588128</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6435,6 +6730,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118588534</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6532,6 +6832,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589036</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6629,6 +6934,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118594452</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6726,6 +7036,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551431</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6823,6 +7138,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552031</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6920,6 +7240,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552350</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7017,6 +7342,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553087</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7114,6 +7444,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554252</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7211,6 +7546,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554822</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7308,6 +7648,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555622</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7405,6 +7750,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556218</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7502,6 +7852,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556301</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7599,6 +7954,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557454</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7696,6 +8056,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557661</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7793,6 +8158,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587264</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7890,6 +8260,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118587632</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7987,6 +8362,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590539</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8084,6 +8464,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118596031</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8181,6 +8566,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118597134</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8283,6 +8673,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118597248</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8380,6 +8775,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553615</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8477,6 +8877,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556472</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8574,6 +8979,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557154</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8671,6 +9081,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557202</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8768,6 +9183,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589338</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8865,6 +9285,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590255</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8962,6 +9387,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552163</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9064,6 +9494,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555659</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9166,6 +9601,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590215</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9268,6 +9708,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118594407</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9370,6 +9815,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553989</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9472,6 +9922,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118555906</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9574,6 +10029,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589093</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9676,6 +10136,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118588929</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9773,6 +10238,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118593307</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9874,6 +10344,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118597023</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9971,6 +10446,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557253</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10068,6 +10548,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118597176</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10174,6 +10659,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552200</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10280,6 +10770,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552498</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10386,6 +10881,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552631</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10487,6 +10987,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552748</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10588,6 +11093,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552764</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10694,6 +11204,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552802</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10800,6 +11315,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552820</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10901,6 +11421,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552985</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11007,6 +11532,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557265</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11113,6 +11643,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590296</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11214,6 +11749,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590334</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11320,6 +11860,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118594520</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11426,6 +11971,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118596461</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11532,6 +12082,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118596564</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11633,6 +12188,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118596677</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11730,6 +12290,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118554878</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11827,6 +12392,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589537</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11924,6 +12494,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118591019</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12021,6 +12596,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590971</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12118,6 +12698,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118590681</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12215,6 +12800,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556821</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12312,6 +12902,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118556986</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12409,6 +13004,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557914</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12506,6 +13106,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589486</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12603,6 +13208,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557174</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12700,6 +13310,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557229</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12797,6 +13412,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589918</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12894,6 +13514,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118557940</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12991,6 +13616,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589906</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13102,6 +13732,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398772</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13204,6 +13839,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398808</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13301,6 +13941,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398811</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13403,6 +14048,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118592076</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13500,6 +14150,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118558184</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13597,6 +14252,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118586696</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13698,6 +14358,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118586448</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13799,6 +14464,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118589613</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13900,8 +14570,149 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122217858</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>